--- a/sofood/ABSTRACT.xlsx
+++ b/sofood/ABSTRACT.xlsx
@@ -5,22 +5,27 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baron\LAVORO\PRODOTTI SOFOOD\sofood\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baron\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29691F7-DC62-4108-9CA0-926CEE91D0A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE5630E-C72C-4C46-A5BD-25E68FAEAF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Abstract Database" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="534">
   <si>
     <t>an_forn</t>
   </si>
@@ -914,6 +919,12 @@
     <t>19010692</t>
   </si>
   <si>
+    <t>CAPRIZ</t>
+  </si>
+  <si>
+    <t>CAPRIZ SRL SOCIO UNICO</t>
+  </si>
+  <si>
     <t>Eccellenza casearia situata nel cuore della Val Pusteria, nata dalla visione pionieristica di Heiner Oberrauch. Un caseificio privato che si pone come vero e proprio tempio della cultura del formaggio, esaltando i sapori genuini dei pascoli altoatesini.</t>
   </si>
   <si>
@@ -937,6 +948,12 @@
     <t>19010808</t>
   </si>
   <si>
+    <t>CARPINELLO</t>
+  </si>
+  <si>
+    <t>T.F.A. SRL</t>
+  </si>
+  <si>
     <t>Un'azienda a conduzione familiare specializzata nella trasformazione e lavorazione artigianale dei formaggi, pioniera e celebre per aver creato la prima crema spalmabile a base del formaggio stagionato italiano più amato al mondo.</t>
   </si>
   <si>
@@ -957,7 +974,16 @@
     <t>19010485</t>
   </si>
   <si>
+    <t xml:space="preserve">CRUCOLO </t>
+  </si>
+  <si>
+    <t>CRUCOLO S.R.L</t>
+  </si>
+  <si>
     <t>Storica realtà agroalimentare e osteria di montagna situata nel cuore del Trentino, in Valsugana. Un vero e proprio emblema della convivialità e della più genuina tradizione gastronomica locale.</t>
+  </si>
+  <si>
+    <t>FORMAGGI/SALUMI</t>
   </si>
   <si>
     <t>Dal 1782, la famiglia Purin gestisce il Rifugio Crucolo a oltre 1.100 metri di altitudine, accogliendo viaggiatori ed escursionisti da ben 9 generazioni. Iscritta nel registro delle imprese storiche, l'azienda si è evoluta nel tempo, passando dalla stagionatura dei prodotti nella cantina del rifugio all'apertura di un moderno impianto agroalimentare, portando i propri sapori sui mercati nazionali e internazionali.</t>
@@ -977,6 +1003,12 @@
     <t>19010417</t>
   </si>
   <si>
+    <t xml:space="preserve">FORMAGGERIA TOSCANA </t>
+  </si>
+  <si>
+    <t>FORMAGGERIA TOSCANA S.R.L.</t>
+  </si>
+  <si>
     <t>Realtà nata nel 2014 da un'idea innovativa, capace in pochi anni di portare le proprie eccellenze sulle tavole di migliaia di consumatori. Si tratta di una piccola azienda con grandi obiettivi che punta sulla massima qualità del lavoro e del prodotto, offrendo un'ampia gamma di formaggi che spaziano dal fresco allo stagionato.</t>
   </si>
   <si>
@@ -997,6 +1029,12 @@
     <t>19010071</t>
   </si>
   <si>
+    <t>LA CASERA</t>
+  </si>
+  <si>
+    <t>LA CASERA S.R.L</t>
+  </si>
+  <si>
     <t>Nata come piccola bottega a Verbania, oggi l'azienda è un vero e proprio "cerchio magico" del gusto: uno spazio amplificato dedicato alla continua ricerca dei migliori prodotti caseari locali e nazionali, arricchito da una cantina di stagionatura e da un'esclusiva area degustazione.</t>
   </si>
   <si>
@@ -1020,6 +1058,9 @@
     <t>La Ghianda</t>
   </si>
   <si>
+    <t>MASSERIA LA GHIANDA DI DIGREGORIO ANTONIO</t>
+  </si>
+  <si>
     <t>Masseria a conduzione familiare situata nelle campagne pugliesi. Un'azienda agricola e zootecnica che rappresenta un esempio virtuoso di filiera completa e autosufficiente, unendo con dedizione l'allevamento, la trasformazione e la vendita diretta dei propri prodotti.</t>
   </si>
   <si>
@@ -1043,6 +1084,9 @@
     <t>L'Abbondanza</t>
   </si>
   <si>
+    <t>ADRIANO AZZARRI RAPPRESENTANTE S.A.S.</t>
+  </si>
+  <si>
     <t>Un'azienda profondamente radicata nel territorio romagnolo, espressione della Famiglia Brancaleoni, che custodisce e valorizza l'autentica tradizione locale legata alla conservazione e all'affinamento dei formaggi d'eccellenza.</t>
   </si>
   <si>
@@ -1063,6 +1107,12 @@
     <t>19010890</t>
   </si>
   <si>
+    <t>LATTE NOBILE</t>
+  </si>
+  <si>
+    <t>LATTE NOBILE S.R.L.</t>
+  </si>
+  <si>
     <t>Un marchio innovativo e virtuoso nato dalla lungimiranza di allevatori e trasformatori campani. Rappresenta una realtà importante dedicata alla produzione del "Latte Nobile", un metodo rigoroso che pone al centro l'assoluta qualità della materia prima e il rispetto per la natura.</t>
   </si>
   <si>
@@ -1086,6 +1136,9 @@
     <t>Montanari &amp; Gruzza</t>
   </si>
   <si>
+    <t>MONTANARI &amp; GRUZZA S.P.A.</t>
+  </si>
+  <si>
     <t>Realtà emiliana profondamente radicata nel proprio territorio, dedita alla produzione e selezione di eccellenze lattiero-casearie. Un'azienda che rappresenta l'ideale punto di incontro tra una tradizione gastronomica millenaria e il continuo sviluppo tecnologico.</t>
   </si>
   <si>
@@ -1106,6 +1159,12 @@
     <t>19010491</t>
   </si>
   <si>
+    <t>PESSOLANI</t>
+  </si>
+  <si>
+    <t>AZ.AGR.ZOOT.PESSOLANI NICOLA</t>
+  </si>
+  <si>
     <t>Azienda agricola e casearia situata nel cuore dell'Appennino Lucano, dedicata alla valorizzazione del latte e delle carni di bovino Podolico. Una realtà che si pone come autentica custode di antichi mestieri agricoli e di produzioni tipiche quasi scomparse.</t>
   </si>
   <si>
@@ -1126,6 +1185,12 @@
     <t>19010676</t>
   </si>
   <si>
+    <t>VALSAMOGGIA</t>
+  </si>
+  <si>
+    <t>CASEIFICIO VALSAMOGGIA S.N.C.</t>
+  </si>
+  <si>
     <t>Un'importante realtà casearia emiliana che da oltre cinquant'anni si dedica con passione e professionalità alla produzione e selezione di eccellenze gastronomiche, rappresentando un vero e proprio punto di riferimento per i palati più esigenti del territorio.</t>
   </si>
   <si>
@@ -1143,61 +1208,541 @@
     <t>Un assortimento ricco che celebra il gusto della tradizione. Il cuore dell'offerta è rappresentato dalla produzione artigianale di formaggi freschi</t>
   </si>
   <si>
-    <t>CAPRIZ SRL SOCIO UNICO</t>
-  </si>
-  <si>
-    <t>CAPRIZ</t>
-  </si>
-  <si>
-    <t>CARPINELLO</t>
-  </si>
-  <si>
-    <t>T.F.A. SRL</t>
-  </si>
-  <si>
-    <t>CRUCOLO S.R.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRUCOLO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FORMAGGERIA TOSCANA </t>
-  </si>
-  <si>
-    <t>FORMAGGERIA TOSCANA S.R.L.</t>
-  </si>
-  <si>
-    <t>LA CASERA</t>
-  </si>
-  <si>
-    <t>LA CASERA S.R.L</t>
-  </si>
-  <si>
-    <t>MASSERIA LA GHIANDA DI DIGREGORIO ANTONIO</t>
-  </si>
-  <si>
-    <t>ADRIANO AZZARRI RAPPRESENTANTE S.A.S.</t>
-  </si>
-  <si>
-    <t>LATTE NOBILE S.R.L.</t>
-  </si>
-  <si>
-    <t>LATTE NOBILE</t>
-  </si>
-  <si>
-    <t>MONTANARI &amp; GRUZZA S.P.A.</t>
-  </si>
-  <si>
-    <t>PESSOLANI</t>
-  </si>
-  <si>
-    <t>AZ.AGR.ZOOT.PESSOLANI NICOLA</t>
-  </si>
-  <si>
-    <t>VALSAMOGGIA</t>
-  </si>
-  <si>
-    <t>CASEIFICIO VALSAMOGGIA S.N.C.</t>
+    <t>19010658</t>
+  </si>
+  <si>
+    <t>PISANI DOSSI</t>
+  </si>
+  <si>
+    <t>AZIENDA AGRICOLA PISANI DOSSI S.S.</t>
+  </si>
+  <si>
+    <t>Un'azienda agricola situata nel Parco Agricolo Sud di Milano, specializzata da decenni nell'allevamento dello storione e nella produzione di caviale italiano freschissimo. Una realtà che si distingue per la profonda cura artigianale e per una filosofia fieramente lontana dalle logiche della produzione massiva, orientata esclusivamente all'eccellenza e ai dettagli.</t>
+  </si>
+  <si>
+    <t>MARE</t>
+  </si>
+  <si>
+    <t>L'impianto è in piena attività dal 1982. Dopo aver dedicato oltre vent'anni alla commercializzazione di uova embrionate, larve, avannotti e storioni adulti, l'azienda ha compiuto il naturale passo successivo avviando la produzione diretta di storione fresco, affumicato e caviale. Un percorso di specializzazione trentennale che ha permesso di padroneggiare in totale autonomia l'intero ciclo di vita dell'animale, dalla riproduzione fino al confezionamento finale.</t>
+  </si>
+  <si>
+    <t>Vocazione Artigianale: Un approccio meticoloso e attento che privilegia lavorazioni rigorose per raggiungere e mantenere i più alti standard qualitativi.
+Sinergia con il Territorio: Una perfetta integrazione nell'ambiente circostante, operando nel pieno rispetto dei vincoli di tutela imposti dalla vocazione agricola del Parco Sud.
+Purezza e Salute: L'impiego esclusivo di fonti d'acqua incontaminate (pozzi profondi oltre 30 metri e una risorgiva naturale) separate dal reticolo idrografico superficiale, assicurando uno stato sanitario impeccabile per gli animali allevati.</t>
+  </si>
+  <si>
+    <t>L'allevamento si estende su 5 ettari e ricrea le condizioni ottimali di crescita grazie a bacini con fondo naturale e avanzati sistemi tecnologici per il ricircolo, il filtraggio meccanico e la depurazione biologica dell'acqua. La lavorazione del caviale avviene in purezza, senza alcun conservante aggiunto o trattamento, adottando il metodo "malossol" (a bassissimo contenuto di sale). Per le carni di storione si utilizzano tecniche di affumicatura a caldo puramente manuali, impiegando esclusivamente legni nobili.</t>
+  </si>
+  <si>
+    <t>Il catalogo offre prelibatezze di assoluto prestigio e purezza. Caviale Siberian: ottenuto dallo storione siberiano, di colore grigio canna di fucile, si distingue per i granuli uniformi e un sapore delicato con retrogusto di nocciola e frutti di bosco. Caviale Osetra: il prodotto "Riserva" più pregiato, nato da un incrocio russo-siberiano, con sfumature dal grigio perla al bronzo ambrato e una consistenza vellutata con sentori di noce.</t>
+  </si>
+  <si>
+    <t>19010823</t>
+  </si>
+  <si>
+    <t>SCUDELLARO</t>
+  </si>
+  <si>
+    <t>AZIENDA AGRICOLA SCUDELLARO S.AGR.S.</t>
+  </si>
+  <si>
+    <t>Azienda agricola situata nel cuore della Bassa Padovana. Una realtà autentica, fatta di persone, scelte e dedizione al lavoro, profondamente votata all'allevamento avicolo e guidata dal principio fondamentale secondo cui la salute e il benessere degli animali vengono prima di tutto.</t>
+  </si>
+  <si>
+    <t>CARNE/SALUMI</t>
+  </si>
+  <si>
+    <t>Forte di un'esperienza lunga decenni e di quarant'anni di storia, l'azienda ha vissuto molti cambiamenti nel tempo senza mai alterare la propria filosofia originale e il modo di allevare. Un percorso che custodisce e proietta nel futuro la storica tradizione rurale della Corte Padovana.</t>
+  </si>
+  <si>
+    <t>Benessere allo Stato Libero: La scelta etica e quotidiana di lasciare gli animali liberi di muoversi e razzolare all'aria aperta.
+Lento Accrescimento: Il forte credo nel rispetto dei tempi biologici e naturali, garantendo agli animali uno sviluppo sano e mai forzato.
+Purezza e Genuinità: Il rifiuto totale di stimolatori della crescita e il drastico abbattimento dell'uso di medicinali per favorire uno stile di vita sano.</t>
+  </si>
+  <si>
+    <t>Il cuore del lavoro risiede interamente nelle pratiche di allevamento virtuose. Il ciclo di vita segue ritmi naturali, supportato da un'alimentazione estremamente semplice, genuina e mirata, composta unicamente da prodotti naturali selezionati come granaglie, leguminose ed erba medica.</t>
+  </si>
+  <si>
+    <t>L'azienda offre carni avicole uniche ed inimitabili, espressione massima di qualità e cura. Il vero fiore all'occhiello della produzione è rappresentato dal sistema brevettato "Latte &amp; Miele": un metodo esclusivo nato dall'incontro perfetto tra l'antica tradizione locale, la ricerca scientifica dell'Università di Padova e l'intuizione dell'alta cucina.</t>
+  </si>
+  <si>
+    <t>19010801</t>
+  </si>
+  <si>
+    <t>BRANCHI</t>
+  </si>
+  <si>
+    <t>BRANCHI SRL</t>
+  </si>
+  <si>
+    <t>Salumificio artigianale situato a Felino, nel cuore della provincia di Parma. Un'azienda che ha scelto di elevare il concetto di "soltanto buono" a "assolutamente speciale", distinguendosi nel panorama gastronomico per la spiccata manualità e l'attenzione maniacale al dettaglio nella produzione di prosciutti cotti d'eccellenza.</t>
+  </si>
+  <si>
+    <t>SALUMI</t>
+  </si>
+  <si>
+    <t>La storia della famiglia Branchi nel settore delle carni suine prende il via nell'immediato dopoguerra con Erminio Branchi, per poi espandersi notevolmente durante il boom economico con il figlio Franco, vero e proprio pioniere nella lavorazione del prosciutto cotto nel parmense. L'attuale assetto aziendale nasce nel 1987 con Tito Branchi e viene oggi portato avanti dalla terza generazione (Franco, Giovanni e Carlotta), mantenendo salda la propria sede storica tra le dolci colline di Parma.</t>
+  </si>
+  <si>
+    <t>Vocazione Artigianale: Il rifiuto delle logiche industriali per abbracciare la "manualità", investendo il tempo necessario per legare a mano i prodotti e curare ogni singola fase con dedizione assoluta.
+Etichetta Corta e Salubrità: L'impiego di pochissimi ingredienti scelti per la salamoia e l'assenza totale di aromi artificiali, additivi e allergeni, garantendo così la massima digeribilità e sicurezza alimentare.
+Legame col Territorio: Un radicamento profondo nel microclima, nella cultura e nelle tradizioni culinarie parmensi, che rappresentano la lingua materna e l'ispirazione costante della comunità aziendale.</t>
+  </si>
+  <si>
+    <t>La ricerca della perfezione inizia dalla selezione diretta delle cosce fresche presso i macelli. Il vero fiore all'occhiello della produzione è la "salatura in arteria": un'antica tecnica pre-industriale effettuata sul prosciutto intero (non disossato) che sfrutta il circuito arterioso per distribuire la salamoia in modo capillare, mantenendo intatta la struttura della carne. Le affumicature avvengono esclusivamente con vero fumo di legna che arde.</t>
+  </si>
+  <si>
+    <t>Il cuore della produzione è rappresentato dai prosciutti cotti e affumicati (nostrani ed esteri), caratterizzati da sfumature rosate, consistenza morbida, friabile e una succulenza naturale. Ad arricchire la proposta vi sono i salmistrati da cuocere e una selezione di "piccola salumeria" che racchiude le migliori espressioni del territorio, come il salame di Felino, la coppa di Parma, la pancetta, la culatta e la mortadella.</t>
+  </si>
+  <si>
+    <t>19010866</t>
+  </si>
+  <si>
+    <t>CECINAS NIETO</t>
+  </si>
+  <si>
+    <t>CECINAS NIETO S.L.</t>
+  </si>
+  <si>
+    <t>Azienda leader e punto di riferimento mondiale nella produzione di Cecina de León IGP. Una realtà a conduzione familiare che lavora con l'obiettivo di elevare la carne curata a vera e propria esperienza gourmet, offrendo un alimento unico, delizioso e altamente nutritivo.</t>
+  </si>
+  <si>
+    <t>L'impresa viene fondata nel 1965 da José Nieto Blas, discendente di una storica famiglia di arrieros della Maragatería, comarca situata nell'ovest della provincia di León. Proprio attingendo a queste profonde radici e ai segreti dell'antica tradizione locale, l'attività ha saputo evolversi nel tempo, espandendosi con successo anche sui mercati internazionali più prestigiosi ed esigenti.</t>
+  </si>
+  <si>
+    <t>Artigianalità Certificata: Il massimo rispetto per i rigorosi standard stabiliti dal disciplinare dell'Indicazione Geografica Protetta Cecina de León.
+Purezza e Sostenibilità: La scelta di proporre alimenti completamente naturali, senza rinunciare a un forte impegno quotidiano verso la tutela dell'ambiente.
+Inclusività e Carattere Globale: La capacità di aprirsi a nuove culture gastronomiche, diventando un punto di riferimento anche grazie alla creazione di linee dedicate con certificazione Halal.</t>
+  </si>
+  <si>
+    <t>La produzione si basa sulla sapiente e lenta combinazione di pochissimi elementi: carne selezionata, sale, fumo e tempo. Il processo di curazione avviene in modo lento e meticoloso e per le riserve speciali la stagionatura minima garantita supera i 18 mesi. Tutta la lavorazione avviene rigorosamente nel territorio delimitato di León per beneficiare del suo caratteristico microclima.</t>
+  </si>
+  <si>
+    <t>Un catalogo esclusivo incentrato sul meglio della salumeria bovina. Spiccano le diverse selezioni di Cecina de León IGP, disponibili sia in pezzi interi che in comodi formati porzionati e affettati, inclusa la pregiatissima variante di bue.</t>
+  </si>
+  <si>
+    <t>19010720</t>
+  </si>
+  <si>
+    <t>CENTRO CARNE</t>
+  </si>
+  <si>
+    <t>CENTRO CARNE S.R.L.</t>
+  </si>
+  <si>
+    <t>Una solida realtà alimentare abruzzese che da oltre sessant'anni promuove l'autenticità e l'eccellenza del Made in Italy. L'azienda si fa portavoce di una filiera corta e di un consumo consapevole, con la missione di offrire un "cibo buono" capace di nutrire corpo e anima, portando a tavola benessere e qualità.</t>
+  </si>
+  <si>
+    <t>CARNE</t>
+  </si>
+  <si>
+    <t>Il percorso dell'azienda prende il via negli anni '60 a Sant'Egidio alla Vibrata. Tutto nasce dalla visione dei fondatori, Pasquale Nardinocchi e Vincenzo Antelli, di cui ancora oggi viene orgogliosamente portata avanti l'eredità. Una storia decennale fatta di dedizione e di una profonda e indissolubile connessione con la propria terra.</t>
+  </si>
+  <si>
+    <t>Benessere Animale: L'incoraggiamento di scelte alimentari rispettose, ponendo la massima cura nel monitorare le condizioni di vita degli animali durante l'intero ciclo.
+Innovazione e Tradizione: L'equilibrio perfetto tra il rispetto dei sapori di un tempo e la ricerca costante per migliorare l'impatto ambientale dell'attività.</t>
+  </si>
+  <si>
+    <t>Il ciclo produttivo è fortemente orientato all'innovazione ecologica. L'azienda impiega il favino per favorire un'agricoltura più responsabile e locale, e adotta l'innovativo sistema RumiTech negli allevamenti bovini per abbattere le emissioni di CO2. L'intero iter è supportato da rigorosi controlli qualitativi e sistemi di tracciabilità elettronica all'avanguardia.</t>
+  </si>
+  <si>
+    <t>L'azienda propone carni e prodotti di altissima qualità, studiati e lavorati in modo eccellente per rispondere con affidabilità e sicurezza alle complesse esigenze della grande distribuzione, garantendo al consumatore finale un'esperienza di gusto autentica e tracciabile in ogni suo passaggio.</t>
+  </si>
+  <si>
+    <t>19010750</t>
+  </si>
+  <si>
+    <t>COLIMENA</t>
+  </si>
+  <si>
+    <t>COLIMENA LA FABBRICA DEL TONNO SRL</t>
+  </si>
+  <si>
+    <t>Realtà artigianale salentina che fa rivivere l'anima e il fascino dell'antica tonnara attraverso una nuova consapevolezza. Un'azienda che unisce la profonda conoscenza del territorio e del mar Ionio con le moderne esigenze dell'alta ristorazione e le più esigenti tendenze del gusto.</t>
+  </si>
+  <si>
+    <t>Le radici del progetto affondano nell'evocativo paesaggio di Torre Colimena, incastonato tra la storica torre costiera voluta da Carlo V e l'antica Salina, oggi oasi protetta. Un luogo magico, intriso di vissuto e ricordi d'infanzia trascorsi tra le rocce della "Cilona", la sabbia finissima e le barche dei pescatori che rientrano al molo alle prime luci dell'alba.</t>
+  </si>
+  <si>
+    <t>L'Essenza del Territorio: Il legame viscerale con un paesaggio fatto di dune e profumi di macchia mediterranea (timo, mirto e origano), la cui bellezza ispira e "rende più buono" il prodotto finale.
+Artigianalità Paziente: Il valore fondamentale conferito al tempo e alla pazienza umana, elementi considerati indispensabili per creare cose buone e fatte con cura.
+Crescita Qualitativa Costante: L'attenzione rigorosa e quotidiana alle materie prime per garantire standard d'eccellenza, lavorando gomito a gomito con i professionisti del settore gastronomico.</t>
+  </si>
+  <si>
+    <t>Il ciclo produttivo rifiuta la fretta per abbracciare l'assoluta manualità: il tonno viene sfilettato e confezionato rigorosamente a mano. Per la preparazione si utilizza un "metodo gentile", cuocendo le carni in un delicato bagno di erbe profumate, aceto bianco e limone, una tecnica studiata appositamente per non aggredire la materia prima e lasciarle un sapore pieno, genuino e inalterato.</t>
+  </si>
+  <si>
+    <t>Un prodotto unico che rappresenta la perfetta sintesi tra la ricchezza ittica del mar Ionio e la secolare tradizione gastronomica del Salento. Un'offerta incentrata sul tonno lavorato ad arte, concepita per portare in tavola una vera e propria esperienza sensoriale legata ai profumi e alla storia della costa pugliese.</t>
+  </si>
+  <si>
+    <t>19010703</t>
+  </si>
+  <si>
+    <t>MEDIMER</t>
+  </si>
+  <si>
+    <t>CONSERVAS MEDIMER S.L.</t>
+  </si>
+  <si>
+    <t>Azienda specializzata nella produzione di conserve ittiche ad alto valore aggiunto, con un focus specifico sui filetti di acciuga. Nata dalla profonda passione per il mare, si posiziona nel mercato della distribuzione come una realtà di rilievo per chi ricerca un connubio perfetto tra altissima qualità e competitività, rivolgendosi ai consumatori più esigenti.</t>
+  </si>
+  <si>
+    <t>La realtà prende forma dalla determinazione di elevare lo standard qualitativo delle conserve. La sua storia e il suo operato si fondano sulla vasta e solida esperienza dei responsabili della qualità e della produzione, supportati dall'impegno quotidiano e corale di tutti gli operatori che compongono la "grande famiglia" aziendale.</t>
+  </si>
+  <si>
+    <t>Impegno per l'Eccellenza: La ferma convinzione che la qualità non sia mai frutto del caso, garantendo standard elevatissimi di igiene e sicurezza alimentare in ogni fase.
+Evoluzione Continua: Un processo di miglioramento incessante che spinge l'azienda a superarsi ogni giorno, fondendo i valori della tradizione con l'innovazione e le migliori tecniche moderne.
+Salute e Benessere: La promozione e la valorizzazione della dieta mediterranea attraverso le virtù naturali del pesce azzurro, alimento essenziale e naturalmente ricco di preziosi acidi grassi Omega-3.</t>
+  </si>
+  <si>
+    <t>Il processo produttivo si distingue per la meticolosa cura dedicata a ogni singolo dettaglio. Particolare importanza viene riservata alla selezione rigorosa delle materie prime, alla ricerca di un contenuto di salinità perfettamente equilibrato e, soprattutto, a un'estrema attenzione e precisione nella fase di pulizia dei filetti.</t>
+  </si>
+  <si>
+    <t>L'assortimento è interamente dedicato ai filetti di acciuga, lavorati per essere sani, nutrienti e gustosi. Un prodotto dalla straordinaria versatilità, celebrato come ingrediente irrinunciabile della cucina italiana e spagnola (dalla Bagna Cauda piemontese agli spaghetti siciliani), in grado di conferire ai piatti la naturale sapidità e l'inconfondibile "Umami", il ricercato quinto elemento del gusto.</t>
+  </si>
+  <si>
+    <t>19010439</t>
+  </si>
+  <si>
+    <t>DELFINO</t>
+  </si>
+  <si>
+    <t>DELFINO BATTISTA SRL</t>
+  </si>
+  <si>
+    <t>Azienda conserviera artigianale situata a Cetara, nel cuore della Costiera Amalfitana. Una realtà familiare che prosegue con orgoglio la vocazione storica del borgo marinaro legata alla trasformazione del pescato, portando in tavola i sapori autentici e immutati del mare.</t>
+  </si>
+  <si>
+    <t>L'attività nasce nel 1950, nell'immediato dopoguerra, quando Pasquale Battista apre un piccolo laboratorio di conserve alimentari dedicato principalmente alle alici, guidandolo con dedizione fino agli anni '90. Oggi i figli portano avanti questa eredità, mantenendo vivo un legame che affonda le radici nel nome stesso di Cetara, derivante dal latino Cetaria, luogo fin dall'antichità vocato alla lavorazione del pesce.</t>
+  </si>
+  <si>
+    <t>Fedeltà alla Tradizione: La volontà di mantenere i processi produttivi rigorosamente inalterati nel tempo, con la ferma convinzione che l'assenza di cambiamenti si rifletta nella bontà assoluta dei sapori.
+Legame col Territorio: Un rapporto profondo e indissolubile con lo splendido mare della Costiera Amalfitana e con l'identità del proprio borgo di pescatori.
+Passione Familiare: La dedizione tramandata di generazione in generazione nel custodire e continuare la storica arte conserviera locale.</t>
+  </si>
+  <si>
+    <t>La trasformazione del pescato avviene seguendo in modo fedele e rispettoso i rigidi precetti dell'antica tradizione cetarese. Un approccio artigianale che si ispira a un'epoca in cui le salse e le conserve ittiche erano ricercatissime, tramandando saperi antichi per racchiuderli e preservarli al meglio all'interno di nuove confezioni.</t>
+  </si>
+  <si>
+    <t>La produzione si concentra sulla realizzazione di pregiate specialità ittiche, con un focus d'eccellenza sulla lavorazione e conservazione delle alici. Per rafforzare il rapporto diretto con i consumatori e offrire un'esperienza immersiva, l'azienda ha inoltre inaugurato Sapori Cetaresi, un accogliente punto vendita al dettaglio situato a pochissimi passi dalla spiaggia centrale nella marina di Cetara.</t>
+  </si>
+  <si>
+    <t>19010770</t>
+  </si>
+  <si>
+    <t>DI TRIA</t>
+  </si>
+  <si>
+    <t>DI TRIA SOCIETA' AGRICOLA ARL</t>
+  </si>
+  <si>
+    <t>Un vero e proprio atelier del gusto immerso nel suggestivo scenario di Minervino Murge. Una firma d'eccellenza che intreccia memoria, natura e innovazione con l'obiettivo di promuovere e valorizzare il ricco patrimonio agroalimentare pugliese a livello nazionale.</t>
+  </si>
+  <si>
+    <t>GELO</t>
+  </si>
+  <si>
+    <t>L'attività viene fondata nel 1991 da Antonio Di Tria, mosso dal profondo desiderio di capire e mettere a frutto la propria terra. L'eredità è stata poi raccolta dalla figlia Isabella che, spinta da una naturale passione e affiancata dalla lungimirante visione del marito Dino, forte di una ventennale esperienza nella ristorazione, ha saputo ampliare ulteriormente gli orizzonti aziendali.</t>
+  </si>
+  <si>
+    <t>Filiera Zero: Una pratica di trasformazione responsabile che garantisce freschezza assoluta, lavorando le materie prime nell'atelier aziendale situato nelle immediate vicinanze dei campi di raccolta.
+Sostenibilità e Biodiversità: Un approccio produttivo che abbraccia l'agricoltura sinergica e l'ecosostenibilità, nel pieno rispetto dei ritmi e dei tempi naturali dei prodotti autoctoni.
+Sartorialità: Un'attenzione minuziosa alla qualità, unendo la caparbietà e la tradizione agricola a una cura del dettaglio degna di un laboratorio artigianale di alta gamma.</t>
+  </si>
+  <si>
+    <t>Il processo si fonda sull'importanza della materia prima, coltivata in modo diretto su 20 ettari di cereali, 8 ettari di ortaggi e 3 ettari di uliveti. Subito dopo la raccolta, i frutti della terra vengono sottoposti a processi di lavorazione specializzati, accuratamente studiati per esaltarne le caratteristiche organolettiche e preservare l'autenticità e il rispetto del luogo di origine.</t>
+  </si>
+  <si>
+    <t>Il core business si concentra sulla produzione di ortaggi e alimenti freschi surgelati di altissima qualità. Creazioni dal gusto contemporaneamente autentico e sofisticato, ispirate ai sapori della tradizione e capaci di racchiudere i profumi e i colori della terra di Puglia per esportarne l'eccellenza anche ben oltre i propri confini.</t>
+  </si>
+  <si>
+    <t>19010826</t>
+  </si>
+  <si>
+    <t>FATTORIA CA' DANTE</t>
+  </si>
+  <si>
+    <t>FATTORIA CA' DANTE SRL</t>
+  </si>
+  <si>
+    <t>Un prosciuttificio artigianale situato a Fanano, nel cuore dell'Appennino Modenese ai piedi del Monte Cimone. Una realtà che unisce sapientemente l'antica maestria norcina con le più moderne innovazioni, ponendo un forte accento sul forte legame territoriale e sull'ecosostenibilità.</t>
+  </si>
+  <si>
+    <t>Le origini risalgono al 1968, quando la famiglia Pelloni trasformò una vecchia filanda nel primo mattatoio del comprensorio del Cimone. Spinto dal coraggioso desiderio di dimostrare che le montagne di Fanano potevano dare vita a prosciutti di assoluta eccellenza mondiale, Antonio Pelloni ha guidato l'evoluzione dell'attività fino alla creazione del nuovo e moderno stabilimento di Cà Dante, un'eredità oggi raccolta e portata avanti dal figlio Stefano.</t>
+  </si>
+  <si>
+    <t>Dedizione Artigiana: L'importanza imprescindibile del fattore umano; precisione, rigore, esperienza e un grande cuore guidano le abili mani di montagna nella lavorazione di ogni singola coscia.
+Rispetto per l'Ambiente: Un impegno concreto verso la tutela della natura e dei suoi ritmi, sostenuto dall'utilizzo di moderni impianti fotovoltaici e sistemi per il recupero del calore che abbattono drasticamente le emissioni.
+Innovazione Consapevole: La ferma convinzione che solo conoscendo intimamente le proprie radici storiche sia possibile innovare con successo e creare un'unicità sul mercato.</t>
+  </si>
+  <si>
+    <t>L'azienda opera in una struttura all'avanguardia dotata di impianti tecnologici che garantiscono un ricambio d'aria costante e la massima salubrità del prodotto. A questa tecnologia fa da contrappeso una manualità rigorosa: la salatura misurata a occhio, la sugnatura artigianale e il disosso avvengono grazie a braccia forti e sicure. Il microclima appenninico, con la sua aria pura e pungente d'inverno, affina naturalmente le carni conferendo colore e intensità unici.</t>
+  </si>
+  <si>
+    <t>Un'esclusiva produzione di prosciutto crudo di alta salumeria. Il fiore all'occhiello e vero segno distintivo dell'azienda è il Castagnolo, una specialità altamente innovativa dal sapore inconfondibile, capace di racchiudere in sé tutta l'intensità e i profumi dell'autunno e delle montagne modenesi.</t>
+  </si>
+  <si>
+    <t>19010045</t>
+  </si>
+  <si>
+    <t>FRANCHI SALUMI</t>
+  </si>
+  <si>
+    <t>FRANCHI SALUMI SRL</t>
+  </si>
+  <si>
+    <t>Storica realtà piemontese fondata in Valsesia. Un salumificio che da oltre un secolo incarna l'arte salumiera italiana, offrendo prodotti che uniscono la genuinità dei sapori autentici di una volta a standard produttivi all'avanguardia.</t>
+  </si>
+  <si>
+    <t>L'avventura ha inizio nel 1924 a Grignasco grazie al giovane ventisettenne Francesco Franchi, che avvia la produzione di insaccati freschi artigianali. Affermatasi alla fine della grande guerra, l'impresa familiare è cresciuta costantemente nei decenni, trasferendosi poi nel grande stabilimento di Borgosesia. Una storia centenaria capace di tramandare ai giovani, di generazione in generazione, i preziosi segreti del mestiere.</t>
+  </si>
+  <si>
+    <t>Tradizione e Pazienza: Il profondo rispetto per le ricette originali e per i tempi lenti dettati dalla natura, lavorando i salumi "senza fretta" con gli stessi gesti sapienti di un tempo.
+Genuinità e Benessere: Un'attenzione pionieristica alla salute del consumatore, dimostrata dalla scelta di utilizzare pochissimi ingredienti e dall'aver creato, già alla fine degli anni '90, linee pensate per il massimo benessere.
+Innovazione Costante: La perfetta sinergia tra antichi saperi e tecnologie all'avanguardia, avvalendosi di strutture moderne (come le "camere bianche" automatizzate) per garantire massima sicurezza e igiene.</t>
+  </si>
+  <si>
+    <t>Il processo produttivo parte da carni accuratamente selezionate e controllate in ogni singola fase. Gli insaccati sono realizzati con pochi e semplici ingredienti, inseriti in budello naturale e pazientemente legati a mano.</t>
+  </si>
+  <si>
+    <t>Un'ampia gamma di insaccati e salumi che uniscono la genuinità dei sapori autentici di una volta a standard produttivi all'avanguardia, frutto di oltre un secolo di esperienza nell'arte salumiera piemontese.</t>
+  </si>
+  <si>
+    <t>19010372</t>
+  </si>
+  <si>
+    <t>LA BOTTEGA DI ADO'</t>
+  </si>
+  <si>
+    <t>LA BOTTEGA DI ADO' S.R.L.</t>
+  </si>
+  <si>
+    <t>Salumificio artigianale situato ai piedi delle Alpi Apuane, in Toscana. Una realtà che rappresenta un vero e proprio tempio della norcineria locale, dedita a custodire e valorizzare i sapori più autentici e genuini del territorio apuano e versiliese.</t>
+  </si>
+  <si>
+    <t>L'attività storica nasce a Montignoso, legata indissolubilmente al nome del suo fondatore, Adolfo, da tutti affettuosamente chiamato "Adò". Un progetto nato dalla passione per le cose buone che si è trasformato nel tempo in una solida tradizione familiare, tramandando di generazione in generazione l'antica e preziosa arte del norcino.</t>
+  </si>
+  <si>
+    <t>Artigianalità Pura: Il rifiuto delle lavorazioni industriali a favore di una produzione attenta, rigorosa e manuale, nel profondo rispetto delle antiche ricette di famiglia.
+Legame col Territorio: Una forte e radicata identità toscana, espressa attraverso specialità che raccontano la storia e la cultura gastronomica contadina locale.
+Passione Autentica: L'impegno quotidiano e la dedizione assoluta nel portare in tavola alimenti sinceri, garantendo sapori dal fascino rustico e senza tempo.</t>
+  </si>
+  <si>
+    <t>Il processo produttivo si fonda sulla scrupolosa selezione delle carni suine. Le fasi cruciali, come la concia e la salatura, avvengono rigorosamente a mano utilizzando miscele segrete di spezie naturali e aromi. Le lente stagionature beneficiano in modo determinante del microclima unico della zona, nato dall'incontro tra le fresche correnti montane delle Apuane e la brezza del vicino mar Tirreno.</t>
+  </si>
+  <si>
+    <t>Un assortimento prelibato che celebra i grandi classici della salumeria locale. Spiccano eccellenze iconiche come il pregiato lardo sapientemente affinato, la tradizionale mortadella nostrale apuana, le caratteristiche salsicce artigianali e una ricca selezione di insaccati dal gusto intenso e avvolgente, perfetti per riscoprire il carattere vero della Toscana.</t>
+  </si>
+  <si>
+    <t>19010003</t>
+  </si>
+  <si>
+    <t>MENODICIOTTO</t>
+  </si>
+  <si>
+    <t>MENODICIOTTO S.R.L.</t>
+  </si>
+  <si>
+    <t>Una realtà artigianale d'eccellenza dedicata alla produzione di gelati e sorbetti. Il nome stesso dell'azienda racchiude la sua filosofia più profonda: l'impiego esclusivo di ingredienti semplici e genuini, dove il freddo, a -18°C, rappresenta l'unico conservante utilizzato.</t>
+  </si>
+  <si>
+    <t>Tutto ha origine negli anni '80 all'interno del rinomato ristorante di famiglia "Al gatto nero", all'epoca insignito di due stelle Michelin. È in queste cucine che Luca Grassi avvia i primi pionieristici esperimenti con latte, uova e frutta per creare il gelato perfetto. Il successo di queste prove lo porta, nel 1986, ad aprire un piccolo laboratorio artigianale interamente dedicato a questa arte.</t>
+  </si>
+  <si>
+    <t>Controllo della Filiera: Il forte credo nella cultura tradizionale contadina, concretizzato nella creazione di un proprio allevamento con oltre 100 mucche di razza Montbéliarde per produrre direttamente il latte necessario.
+Genuinità Assoluta: La volontà di proporre un prodotto sano, affidandosi solo a uova provenienti da allevamenti all'aperto e frutta rigorosamente di stagione.
+Sostenibilità Ambientale: Un impegno concreto verso il pianeta, supportato dall'uso di energia da fonti rinnovabili (grazie all'installazione di pannelli fotovoltaici) e dalla promozione di una cultura del recupero, impiegando vaschette e barattoli facilmente riutilizzabili per azzerare gli sprechi.</t>
+  </si>
+  <si>
+    <t>Il processo parte da un'accuratissima selezione delle materie prime all'origine, concepita con l'idea che solo da ingredienti eccellenti possa nascere un gelato di altissimo livello. Le materie prime, dal latte fresco autoprodotto alle uova e alla frutta, vengono lavorate sapientemente seguendo metodi artigianali per garantire sempre un sapore intenso e una consistenza impeccabile, affidando unicamente alle basse temperature il compito di preservare il prodotto.</t>
+  </si>
+  <si>
+    <t>Un ricco assortimento di gelati e sorbetti di alta gamma, capace di regalare un'esperienza gustativa indimenticabile attraverso una selezione di oltre 40 gusti differenti, tutti accomunati da un sapore autentico e da una texture eccellente.</t>
+  </si>
+  <si>
+    <t>19010781</t>
+  </si>
+  <si>
+    <t>CORADAZZI</t>
+  </si>
+  <si>
+    <t>PROSCIUTTI CORADAZZI SRL</t>
+  </si>
+  <si>
+    <t>Realtà artigianale dedita dal 1976 alla creazione di un vero e proprio prosciutto d'autore. Un'azienda a conduzione familiare che si interfaccia direttamente sia con i clienti privati che con i rivenditori, lavorando con un unico, grande obiettivo: offrire un prodotto di eccellenza assoluta.</t>
+  </si>
+  <si>
+    <t>L'avventura prende vita grazie a Rino Coradazzi, arrivato a San Daniele da ragazzo negli anni '50. Dopo una lunga gavetta iniziata in una bottega di alimentari e proseguita come direttore di produzione in altri stabilimenti, nel 1976 realizza il suo sogno aprendo l'attività in proprio insieme alla moglie Giovanna. Oggi, la seconda generazione, rappresentata dai figli Angelo e Teresa, porta avanti con lo stesso orgoglio ed entusiasmo il progetto dei genitori.</t>
+  </si>
+  <si>
+    <t>Vocazione Artigianale: L'impegno quotidiano e caparbio nel voler fare sempre meglio, lavorando ogni prodotto singolarmente e con estrema dedizione.
+Fedeltà alla Tradizione: La volontà di innovarsi nel tempo conservando e rispettando l'antica ricetta e gli inestimabili saperi tramandati dalla famiglia.
+Centralità del Cliente: L'apprezzamento dei consumatori visto come la più grande fonte di orgoglio; un approccio che trasforma la soddisfazione del cliente in un vero e proprio dovere e piacere.</t>
+  </si>
+  <si>
+    <t>L'approccio produttivo rifiuta le logiche industriali per concentrarsi su una cura meticolosa: i prosciutti vengono lavorati letteralmente uno a uno. L'intera filiera di trasformazione avviene rigorosamente ed esclusivamente all'interno del comune di San Daniele, difendendo e salvaguardando il legame vitale con il territorio, condizione indispensabile per la riuscita del prodotto.</t>
+  </si>
+  <si>
+    <t>L'azienda concentra tutte le sue energie e le sue competenze nella produzione del Prosciutto di San Daniele. Un prodotto di altissima salumeria, dal sapore inalterato nel tempo, pensato e realizzato per diventare il preferito sulle tavole di chi lo degusta.</t>
+  </si>
+  <si>
+    <t>19010699</t>
+  </si>
+  <si>
+    <t>LOVISON</t>
+  </si>
+  <si>
+    <t>SALUMIFICIO A. LOVISON SRL</t>
+  </si>
+  <si>
+    <t>Un salumificio artigianale situato in Friuli-Venezia Giulia, dedito alla produzione di salumi tipici friulani di eccellenza. La famiglia mantiene viva l'autentica cultura del maiale attraverso una produzione volutamente limitata che non rinuncia mai alla qualità. Il cuore di questa realtà è la figura del maestro norcino, che trasforma le carni tramandando le antiche tradizioni locali.</t>
+  </si>
+  <si>
+    <t>La storia aziendale ha inizio nel 1903 nel borgo medievale di Spilimbergo, quando Agostino Lovison aprì il primo laboratorio di salumeria in piazza Borgolucido. Nel 1974, la produzione è stata trasferita in una nuova sede a un chilometro dal centro cittadino, ma continua a seguire fedelmente le regole e gli insegnamenti del nonno fondatore, tramandati di padre in figlio.</t>
+  </si>
+  <si>
+    <t>Costanza e Tradizione: La volontà di portare avanti le conoscenze acquisite, adeguandole alle normative odierne senza mai perdere il forte richiamo alla tradizione.
+Garanzia della Materia Prima: L'impegno nel seguire direttamente gli allevamenti affinché la carne scelta sia sempre garantita e sicura.
+Saper Fare Artigiano: Il valore conferito ai gesti semplici e antichi, come la ripetizione attenta dei processi e lo sguardo esperto e insostituibile dei collaboratori.</t>
+  </si>
+  <si>
+    <t>Il processo si distingue per la lavorazione a caldo delle carni, effettuata entro appena due ore dalla macellazione per garantire un impasto omogeneo. Gli impasti vengono insaporiti in modo misurato con sale, pepe o spezie selezionate, con il solo scopo di esaltare il naturale sapore della carne. I salumi vengono sapientemente legati a mano utilizzando uno spago di lino grezzo, mentre le fasi di asciugatura e stagionatura avvengono rispettando scrupolosamente i tempi naturali dettati dal prodotto stesso.</t>
+  </si>
+  <si>
+    <t>L'assortimento celebra la cultura alimentare regionale con proposte come la Sopressa, la Salsiccia e il celebre Musetto Lovison, preparato con un mix speziato che include coriandolo, noce moscata e chiodi di garofano. Spicca il tradizionale Salame Friulano, affiancato dall'esclusivo Salame Punta di Coltello. Completano l'offerta altre specialità tipiche come lardo, ossocollo, pancetta, prosciutto crudo e prosciutto cotto.</t>
+  </si>
+  <si>
+    <t>19010014</t>
+  </si>
+  <si>
+    <t>BBS</t>
+  </si>
+  <si>
+    <t>SALUMIFICIO BBS &amp; C. SNC</t>
+  </si>
+  <si>
+    <t>Un'autentica espressione della Bassa Reggiana. Il Salumificio BBS è una realtà artigianale che ha saputo trasformare la radicata tradizione contadina dell'allevamento e della lavorazione del maiale in un'impresa di pura eccellenza.</t>
+  </si>
+  <si>
+    <t>L'azienda nasce nel 1973 a Novellara grazie alla passione della famiglia Bartoli. Il territorio d'origine, un tempo noto come "Nubilaria" per le nebbie persistenti (ideali per la lenta stagionatura dei salumi), vanta una secolare cultura rurale e un ambiente naturale, arricchito dalle acque del fiume Po, che si rivela perfetto per l'arte norcina.</t>
+  </si>
+  <si>
+    <t>Rispetto per la Tradizione: La volontà di mantenere in vita le antiche usanze delle famiglie contadine, lavorando le carni esattamente "come si faceva una volta in campagna".
+Filiera Etica e Controllata: La scelta consapevole di affidarsi esclusivamente a piccoli allevamenti locali, ancora legati a metodi di alimentazione tradizionali e genuini.
+Vocazione Territoriale: Un legame indissolubile con la storia, la cultura e il microclima unico delle Valli reggiane, veri artefici della bontà dei prodotti.</t>
+  </si>
+  <si>
+    <t>La filiera produttiva è curata minuziosamente in ogni sua fase aziendale. Dalla selezione attenta dei suini idonei fino alla macellazione interna, ogni passaggio è eseguito seguendo l'antica arte norcina tramandata da generazioni. Il clima caratteristico della zona contribuisce in modo naturale a un affinamento ottimale.</t>
+  </si>
+  <si>
+    <t>Un'ampia proposta che racchiude tutti i pregiati salumi tipici della tradizione locale. A queste specialità a produzione interna si affiancano il Prosciutto di Parma e il Culatello, due eccellenze la cui lavorazione è affidata esclusivamente ad aziende situate nelle rispettive zone tipiche geografiche, accuratamente selezionate per la loro totale e rigorosa sintonia con la filosofia artigianale del salumificio.</t>
+  </si>
+  <si>
+    <t>19010620</t>
+  </si>
+  <si>
+    <t>SAPORI MEDITERRANEI</t>
+  </si>
+  <si>
+    <t>SAPORI MEDITERRANEI DI GIOVANNI CILIBERTI</t>
+  </si>
+  <si>
+    <t>Salumificio artigianale situato a Cirigliano, in provincia di Matera. La realtà aziendale è profondamente legata alla cultura contadina della Montagna Materana, distinguendosi per la produzione di salumi dal sapore antico, frutto di competenza e tradizioni locali tramandate nel tempo.</t>
+  </si>
+  <si>
+    <t>L'azienda opera a 656 metri sul livello del mare, all'interno di un borgo medievale circondato da immense foreste di querce. La sua lavorazione si ispira direttamente alle necessità storiche della vita contadina locale, la quale richiedeva di conservare la carne suina il più a lungo possibile utilizzando al meglio ogni singola parte edibile dell'animale, senza generare alcuno spreco.</t>
+  </si>
+  <si>
+    <t>Benessere Animale: Le carni provengono esclusivamente da suini pesanti italiani allevati allo stato semibrado all'aria aperta, liberi di pascolare all'interno del Parco Nazionale del Pollino. L'alimentazione è rigorosamente naturale, priva di ormoni e antibiotici, e non si pratica alcuna mutilazione sugli animali.
+Purezza e Genuinità: La produzione si caratterizza per la totale assenza di conservanti, nitriti, nitrati o altri additivi chimici, privilegiando unicamente l'impiego di aromi del tutto naturali.
+Tutela del Patrimonio: L'impegno nel preservare le antiche produzioni locali lucane, un valore sancito dall'adesione al progetto dei Presìdi Slow Food per garantire un modello agricolo fondato su prodotti buoni, puliti e giusti.</t>
+  </si>
+  <si>
+    <t>Il ciclo produttivo, attivo nei mesi che vanno da ottobre ad aprile, si svolge con metodi artigianali e rigorosamente manuali. Le carni vengono mondate, tagliate a grana medio/grossa e mescolate energicamente a mano (fase di "arricciatura") con sale marino di Cervia, peperone secco di Senise, finocchietto selvatico e aglio fresco. Dopo l'insaccatura in budello naturale e la legatura con spago di canapa, i prodotti affrontano una lenta e sapiente stagionatura che beneficia dell'aria pura e del caratteristico microclima montano.</t>
+  </si>
+  <si>
+    <t>Il catalogo racchiude le eccellenze tipiche della Montagna Materana, proponendo specialità come salsiccia, soppressata, capocollo, lombino, guanciale e pancette. Il vero fiore all'occhiello della produzione è il Pezzente della Montagna Materana (Presidio Slow Food), un salume storico nato dal recupero dei tagli meno nobili, che si presta sia al consumo a fette sia come prelibato ingrediente per sughi e zuppe contadine.</t>
+  </si>
+  <si>
+    <t>19010883</t>
+  </si>
+  <si>
+    <t>OBERTO</t>
+  </si>
+  <si>
+    <t>SELEZIONE OBERTO SRL</t>
+  </si>
+  <si>
+    <t>Punto di riferimento a livello internazionale per la selezione, la lavorazione e la distribuzione della carne di Fassona di Razza Piemontese. Un'azienda pionieristica che unisce la cultura del terroir alla manualità artigiana, vantando la primogenitura nella selezione di questa specifica eccellenza.</t>
+  </si>
+  <si>
+    <t>La storia inizia nel 1965 ad Alba, capitale delle Langhe, con l'apertura della "Macelleria Da Piero" da parte di Pietro Oberto, divenuta per oltre 40 anni un punto di riferimento per i più importanti ristoranti dell'Albese. Nel 1990 il figlio Daniele affianca il padre, iniziando un profondo lavoro di valorizzazione della razza. Il 2010 segna il trasferimento nei più ampi locali di Roddi e il battesimo del marchio Oberto, in cui confluiscono oltre 50 anni di dedizione.</t>
+  </si>
+  <si>
+    <t>La Carne è Terroir e Storia: La convinzione che la carne sveli il proprio territorio d'origine (esattamente come il vino), selezionando capi autoctoni provenienti esclusivamente dalle province di Cuneo e Torino.
+Fiducia e Rispetto: Un rapporto diretto e di fiducia con 150 piccoli e medi allevatori, i quali garantiscono animali cresciuti e nutriti nel pieno rispetto dei tempi e dei ritmi della natura.
+Servizio e Consulenza: Un lavoro quotidiano al fianco di chef e ristoratori per insegnare metodi, tecniche e segreti per valorizzare al meglio il prodotto in cucina.</t>
+  </si>
+  <si>
+    <t>La purezza della filiera è garantita dall'assoluta dedizione artigianale. Macellai professionisti e specializzati eseguono rigorosamente a mano ogni fase: dallo stoccaggio al sezionamento, fino al disosso e al taglio. Un elemento fondamentale è il tempo: l'azienda impiega lente e delicate frollature (sperimentate per la prima volta già negli anni '80) concepite come un vero e proprio affinamento su misura per intenerire e nobilitare le fibre.</t>
+  </si>
+  <si>
+    <t>L'azienda ha creato un nuovo e rigoroso standard qualitativo incentrato in via esclusiva sulla Selezione di Fassona. L'offerta si basa al 100% su carne di Razza Piemontese, ottenuta unicamente da capi femmina con età superiore ai 36 mesi e sottoposta a una frollatura di almeno due settimane. Una scelta mirata per offrire una carne geneticamente superiore per tenerezza, magrezza e gusto, esaltando l'autentico "gusto di carne" che la rende unica al mondo.</t>
+  </si>
+  <si>
+    <t>19010444</t>
+  </si>
+  <si>
+    <t>SMERALDA</t>
+  </si>
+  <si>
+    <t>SMERALDA S.R.L.</t>
+  </si>
+  <si>
+    <t>Azienda sarda specializzata nella lavorazione dei prodotti del mare, nata con l'obiettivo di portare in tavola i sapori autentici ispirandosi alla più profonda tradizione dell'isola. Una realtà consolidata che distribuisce le proprie eccellenze a livello nazionale attraverso i canali Ho.Re.Ca., ingrosso e grande distribuzione organizzata (GDO).</t>
+  </si>
+  <si>
+    <t>La storia aziendale prende il via a Cagliari nel 1988, muovendo i primi passi con la lavorazione della bottarga di muggine, una prelibatezza regionale dalle origini antichissime che ancora oggi rappresenta il vero e proprio fiore all'occhiello dell'intera produzione.</t>
+  </si>
+  <si>
+    <t>Rispetto per la Tradizione: L'impegno costante e primario nel preservare l'integrità della cultura gastronomica locale e il valore dell'alta qualità.
+Selezione Rigorosa: Una filosofia fortemente improntata sulla metodica ricerca della materia prima, resa possibile grazie a una vasta e solida conoscenza dei mercati di pesca.
+Trasparenza e Genuinità: La volontà di mettere sempre al primo posto il piacere di mangiare bene, offrendo al consumatore prodotti sani, genuini e realizzati senza segreti.</t>
+  </si>
+  <si>
+    <t>Il ciclo produttivo si distingue per un approccio fortemente artigianale, minuzioso e attento in ogni sua fase. L'azienda segue metodologie in cui lo slancio verso l'innovazione si fonde armoniosamente con il massimo rispetto per le antiche tecniche di preparazione del pescato, apprese nel passato e gelosamente tramandate fino ai giorni nostri.</t>
+  </si>
+  <si>
+    <t>Un catalogo incentrato sulla valorizzazione delle migliori risorse ittiche. Il prodotto principe è la tradizionale bottarga di muggine, a cui si affianca una ricca selezione di specialità regionali, e non solo, pensate per portare l'autentico gusto del mare sulle tavole dei consumatori e dei professionisti della ristorazione.</t>
+  </si>
+  <si>
+    <t>19010205</t>
+  </si>
+  <si>
+    <t>FRACASSA</t>
+  </si>
+  <si>
+    <t>SOCIETA' AGRICOLA FRACASSA S.S.</t>
+  </si>
+  <si>
+    <t>Un'azienda agricola radicata nelle pittoresche colline teramane, al confine tra Abruzzo e Marche. Guidata dal titolare Enrico Fracassa, la realtà si distingue per la produzione artigianale di specialità norcine, valorizzando una filiera corta incentrata esclusivamente sulla trasformazione delle proprie carni.</t>
+  </si>
+  <si>
+    <t>L'attività nasce e si sviluppa nel comune di Sant'Egidio alla Vibrata, in provincia di Teramo. Le sue radici affondano in un contesto geografico privilegiato e unico nel suo genere: un territorio di transizione dove, nell'arco di pochissimi chilometri, si passa dalla brezza del mare all'aria pura di montagne che raggiungono i 1500 metri di altitudine.</t>
+  </si>
+  <si>
+    <t>Filiera Autoprodotta: L'impegno nel gestire in prima persona il ciclo produttivo, impiegando per le lavorazioni esclusivamente carne suina di produzione propria a garanzia di qualità e controllo.
+Identità Territoriale: Una profonda vocazione per la tutela e la riproposizione dei sapori autentici della tradizione abruzzese.
+Accoglienza e Condivisione: La volontà di instaurare un legame diretto e trasparente con il consumatore finale, aprendo le porte dell'azienda per favorire l'incontro e la scoperta.</t>
+  </si>
+  <si>
+    <t>La trasformazione della carne suina avviene nel pieno rispetto delle antiche ricette locali. Il processo di lavorazione e stagionatura beneficia in modo naturale del particolarissimo microclima della zona, in cui l'incontro tra le correnti marine e quelle montane crea le condizioni ideali per l'affinamento dei salumi.</t>
+  </si>
+  <si>
+    <t>Un assortimento incentrato sui sapori decisi e genuini della norcineria locale. Il prodotto di punta è la saporitissima ventricina teramana, affiancata da una selezione di altri salumi tipici della zona. Per un'esperienza completa, l'azienda mette a disposizione dei visitatori un accogliente spazio degustazione e un angolo dedicato alla vendita diretta al pubblico.</t>
+  </si>
+  <si>
+    <t>MARE/GELO</t>
   </si>
 </sst>
 </file>
@@ -1218,14 +1763,16 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1250,14 +1797,8 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FFF4F6F7"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1280,49 +1821,21 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBDC3C7"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBDC3C7"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBDC3C7"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBDC3C7"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFBDC3C7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBDC3C7"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBDC3C7"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBDC3C7"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1337,41 +1850,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1446,11 +1924,6 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
-    <mruColors>
-      <color rgb="FFEAEAEA"/>
-      <color rgb="FFDDDDDD"/>
-      <color rgb="FFBDC3C7"/>
-    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1645,7 +2118,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F231"/>
+  <dimension ref="A1:F331"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1657,3297 +2130,4621 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14">
+      <c r="A2" s="3">
         <v>19010004</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="2" t="s">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="15"/>
+      <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="2" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="15"/>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="2" t="s">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="15"/>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="2" t="s">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="16"/>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="4" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="15"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="4" t="s">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="15"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="4" t="s">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="15"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="4" t="s">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="16"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="98.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="2" t="s">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="15"/>
+      <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="2" t="s">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="15"/>
+      <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="2" t="s">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="15"/>
+      <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="2" t="s">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="16"/>
+      <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="F17" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="4" t="s">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="15"/>
+      <c r="F18" s="2"/>
     </row>
     <row r="19" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="4" t="s">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F19" s="15"/>
+      <c r="F19" s="2"/>
     </row>
     <row r="20" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="4" t="s">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="15"/>
+      <c r="F20" s="2"/>
     </row>
     <row r="21" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="4" t="s">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="16"/>
+      <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="2" t="s">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="15"/>
+      <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="2" t="s">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="15"/>
+      <c r="F24" s="3"/>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="2" t="s">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F25" s="15"/>
+      <c r="F25" s="3"/>
     </row>
     <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="2" t="s">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F26" s="16"/>
+      <c r="F26" s="3"/>
     </row>
     <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="2" t="s">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F28" s="15"/>
+      <c r="F28" s="3"/>
     </row>
     <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="15"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="2" t="s">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="15"/>
+      <c r="F29" s="3"/>
     </row>
     <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="2" t="s">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F30" s="15"/>
+      <c r="F30" s="3"/>
     </row>
     <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="16"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="2" t="s">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F31" s="16"/>
+      <c r="F31" s="3"/>
     </row>
     <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="F32" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="15"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="4" t="s">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="15"/>
+      <c r="F33" s="2"/>
     </row>
     <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="15"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="4" t="s">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="15"/>
+      <c r="F34" s="2"/>
     </row>
     <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="15"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="4" t="s">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F35" s="15"/>
+      <c r="F35" s="2"/>
     </row>
     <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="16"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="4" t="s">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F36" s="16"/>
+      <c r="F36" s="2"/>
     </row>
     <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="15"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="2" t="s">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F38" s="15"/>
+      <c r="F38" s="3"/>
     </row>
     <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="15"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="2" t="s">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F39" s="15"/>
+      <c r="F39" s="3"/>
     </row>
     <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="15"/>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="2" t="s">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F40" s="15"/>
+      <c r="F40" s="3"/>
     </row>
     <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="16"/>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="2" t="s">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F41" s="16"/>
+      <c r="F41" s="3"/>
     </row>
     <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F42" s="17" t="s">
+      <c r="F42" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="15"/>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="4" t="s">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="15"/>
+      <c r="F43" s="2"/>
     </row>
     <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="15"/>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="4" t="s">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F44" s="15"/>
+      <c r="F44" s="2"/>
     </row>
     <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="15"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="4" t="s">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F45" s="15"/>
+      <c r="F45" s="2"/>
     </row>
     <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="16"/>
-      <c r="B46" s="16"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="4" t="s">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="F46" s="16"/>
+      <c r="F46" s="2"/>
     </row>
     <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F47" s="14" t="s">
+      <c r="F47" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="15"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="2" t="s">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="E48" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F48" s="15"/>
+      <c r="F48" s="3"/>
     </row>
     <row r="49" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="15"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="2" t="s">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E49" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="F49" s="15"/>
+      <c r="F49" s="3"/>
     </row>
     <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="15"/>
-      <c r="B50" s="15"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="2" t="s">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="E50" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="F50" s="15"/>
+      <c r="F50" s="3"/>
     </row>
     <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="16"/>
-      <c r="B51" s="16"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="2" t="s">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F51" s="16"/>
+      <c r="F51" s="3"/>
     </row>
     <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="B52" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C52" s="17" t="s">
+      <c r="C52" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="E52" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="F52" s="17" t="s">
+      <c r="F52" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="15"/>
-      <c r="B53" s="15"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="4" t="s">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="E53" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F53" s="15"/>
+      <c r="F53" s="2"/>
     </row>
     <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="15"/>
-      <c r="B54" s="15"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="4" t="s">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E54" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="F54" s="15"/>
+      <c r="F54" s="2"/>
     </row>
     <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="15"/>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="4" t="s">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="E55" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="F55" s="15"/>
+      <c r="F55" s="2"/>
     </row>
     <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="16"/>
-      <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="4" t="s">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="E56" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F56" s="16"/>
+      <c r="F56" s="2"/>
     </row>
     <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="14" t="s">
+      <c r="A57" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E57" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F57" s="14" t="s">
+      <c r="F57" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="15"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15"/>
-      <c r="D58" s="2" t="s">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="E58" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F58" s="15"/>
+      <c r="F58" s="3"/>
     </row>
     <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="15"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="2" t="s">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="E59" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="F59" s="15"/>
+      <c r="F59" s="3"/>
     </row>
     <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="15"/>
-      <c r="B60" s="15"/>
-      <c r="C60" s="15"/>
-      <c r="D60" s="2" t="s">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="E60" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F60" s="15"/>
+      <c r="F60" s="3"/>
     </row>
     <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="16"/>
-      <c r="B61" s="16"/>
-      <c r="C61" s="16"/>
-      <c r="D61" s="2" t="s">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="E61" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="F61" s="16"/>
+      <c r="F61" s="3"/>
     </row>
     <row r="62" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="17" t="s">
+      <c r="A62" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B62" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C62" s="17" t="s">
+      <c r="C62" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="E62" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="F62" s="17" t="s">
+      <c r="F62" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="15"/>
-      <c r="B63" s="15"/>
-      <c r="C63" s="15"/>
-      <c r="D63" s="4" t="s">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="E63" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="F63" s="15"/>
+      <c r="F63" s="2"/>
     </row>
     <row r="64" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="15"/>
-      <c r="B64" s="15"/>
-      <c r="C64" s="15"/>
-      <c r="D64" s="4" t="s">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="E64" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="F64" s="15"/>
+      <c r="F64" s="2"/>
     </row>
     <row r="65" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="15"/>
-      <c r="B65" s="15"/>
-      <c r="C65" s="15"/>
-      <c r="D65" s="4" t="s">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="E65" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="F65" s="15"/>
+      <c r="F65" s="2"/>
     </row>
     <row r="66" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="16"/>
-      <c r="B66" s="16"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="4" t="s">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="E66" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="F66" s="16"/>
+      <c r="F66" s="2"/>
     </row>
     <row r="67" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="14" t="s">
+      <c r="A67" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B67" s="14" t="s">
+      <c r="B67" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C67" s="14" t="s">
+      <c r="C67" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D67" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E67" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="F67" s="14" t="s">
+      <c r="F67" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="15"/>
-      <c r="B68" s="15"/>
-      <c r="C68" s="15"/>
-      <c r="D68" s="2" t="s">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E68" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="F68" s="15"/>
+      <c r="F68" s="3"/>
     </row>
     <row r="69" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="15"/>
-      <c r="B69" s="15"/>
-      <c r="C69" s="15"/>
-      <c r="D69" s="2" t="s">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="E69" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="F69" s="15"/>
+      <c r="F69" s="3"/>
     </row>
     <row r="70" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="15"/>
-      <c r="B70" s="15"/>
-      <c r="C70" s="15"/>
-      <c r="D70" s="2" t="s">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E70" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="F70" s="15"/>
+      <c r="F70" s="3"/>
     </row>
     <row r="71" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="16"/>
-      <c r="B71" s="16"/>
-      <c r="C71" s="16"/>
-      <c r="D71" s="2" t="s">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E71" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="F71" s="16"/>
+      <c r="F71" s="3"/>
     </row>
     <row r="72" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="17" t="s">
+      <c r="A72" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B72" s="17" t="s">
+      <c r="B72" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C72" s="17" t="s">
+      <c r="C72" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="E72" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="F72" s="17" t="s">
+      <c r="F72" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="15"/>
-      <c r="B73" s="15"/>
-      <c r="C73" s="15"/>
-      <c r="D73" s="4" t="s">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="E73" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="F73" s="15"/>
+      <c r="F73" s="2"/>
     </row>
     <row r="74" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="15"/>
-      <c r="B74" s="15"/>
-      <c r="C74" s="15"/>
-      <c r="D74" s="4" t="s">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="E74" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="F74" s="15"/>
+      <c r="F74" s="2"/>
     </row>
     <row r="75" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="15"/>
-      <c r="B75" s="15"/>
-      <c r="C75" s="15"/>
-      <c r="D75" s="4" t="s">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E75" s="5" t="s">
+      <c r="E75" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="F75" s="15"/>
+      <c r="F75" s="2"/>
     </row>
     <row r="76" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="16"/>
-      <c r="B76" s="16"/>
-      <c r="C76" s="16"/>
-      <c r="D76" s="4" t="s">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E76" s="5" t="s">
+      <c r="E76" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="F76" s="16"/>
+      <c r="F76" s="2"/>
     </row>
     <row r="77" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="14" t="s">
+      <c r="A77" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B77" s="14" t="s">
+      <c r="B77" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C77" s="14" t="s">
+      <c r="C77" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="D77" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="E77" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="F77" s="14" t="s">
+      <c r="F77" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="15"/>
-      <c r="B78" s="15"/>
-      <c r="C78" s="15"/>
-      <c r="D78" s="2" t="s">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E78" s="3" t="s">
+      <c r="E78" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="F78" s="15"/>
+      <c r="F78" s="3"/>
     </row>
     <row r="79" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="15"/>
-      <c r="B79" s="15"/>
-      <c r="C79" s="15"/>
-      <c r="D79" s="2" t="s">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E79" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="F79" s="15"/>
+      <c r="F79" s="3"/>
     </row>
     <row r="80" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="15"/>
-      <c r="B80" s="15"/>
-      <c r="C80" s="15"/>
-      <c r="D80" s="2" t="s">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="E80" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="F80" s="15"/>
+      <c r="F80" s="3"/>
     </row>
     <row r="81" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="16"/>
-      <c r="B81" s="16"/>
-      <c r="C81" s="16"/>
-      <c r="D81" s="2" t="s">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E81" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="F81" s="16"/>
+      <c r="F81" s="3"/>
     </row>
     <row r="82" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="17" t="s">
+      <c r="A82" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B82" s="17" t="s">
+      <c r="B82" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C82" s="17" t="s">
+      <c r="C82" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="D82" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E82" s="5" t="s">
+      <c r="E82" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="F82" s="17" t="s">
+      <c r="F82" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="15"/>
-      <c r="B83" s="15"/>
-      <c r="C83" s="15"/>
-      <c r="D83" s="4" t="s">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E83" s="5"/>
-      <c r="F83" s="15"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="2"/>
     </row>
     <row r="84" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="15"/>
-      <c r="B84" s="15"/>
-      <c r="C84" s="15"/>
-      <c r="D84" s="4" t="s">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E84" s="5" t="s">
+      <c r="E84" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="F84" s="15"/>
+      <c r="F84" s="2"/>
     </row>
     <row r="85" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="15"/>
-      <c r="B85" s="15"/>
-      <c r="C85" s="15"/>
-      <c r="D85" s="4" t="s">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E85" s="5" t="s">
+      <c r="E85" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="F85" s="15"/>
+      <c r="F85" s="2"/>
     </row>
     <row r="86" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="16"/>
-      <c r="B86" s="16"/>
-      <c r="C86" s="16"/>
-      <c r="D86" s="4" t="s">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E86" s="5" t="s">
+      <c r="E86" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F86" s="16"/>
+      <c r="F86" s="2"/>
     </row>
     <row r="87" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="14" t="s">
+      <c r="A87" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B87" s="14" t="s">
+      <c r="B87" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C87" s="14" t="s">
+      <c r="C87" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D87" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E87" s="3" t="s">
+      <c r="E87" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="F87" s="14" t="s">
+      <c r="F87" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="15"/>
-      <c r="B88" s="15"/>
-      <c r="C88" s="15"/>
-      <c r="D88" s="2" t="s">
+      <c r="A88" s="3"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E88" s="3" t="s">
+      <c r="E88" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="F88" s="15"/>
+      <c r="F88" s="3"/>
     </row>
     <row r="89" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="15"/>
-      <c r="B89" s="15"/>
-      <c r="C89" s="15"/>
-      <c r="D89" s="2" t="s">
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E89" s="3" t="s">
+      <c r="E89" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F89" s="15"/>
+      <c r="F89" s="3"/>
     </row>
     <row r="90" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="15"/>
-      <c r="B90" s="15"/>
-      <c r="C90" s="15"/>
-      <c r="D90" s="2" t="s">
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E90" s="3" t="s">
+      <c r="E90" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="F90" s="15"/>
+      <c r="F90" s="3"/>
     </row>
     <row r="91" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="16"/>
-      <c r="B91" s="16"/>
-      <c r="C91" s="16"/>
-      <c r="D91" s="2" t="s">
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="E91" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="F91" s="16"/>
+      <c r="F91" s="3"/>
     </row>
     <row r="92" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="17" t="s">
+      <c r="A92" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B92" s="17" t="s">
+      <c r="B92" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C92" s="17" t="s">
+      <c r="C92" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D92" s="4" t="s">
+      <c r="D92" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E92" s="5" t="s">
+      <c r="E92" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="F92" s="17" t="s">
+      <c r="F92" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="15"/>
-      <c r="B93" s="15"/>
-      <c r="C93" s="15"/>
-      <c r="D93" s="4" t="s">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E93" s="5" t="s">
+      <c r="E93" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="F93" s="15"/>
+      <c r="F93" s="2"/>
     </row>
     <row r="94" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="15"/>
-      <c r="B94" s="15"/>
-      <c r="C94" s="15"/>
-      <c r="D94" s="4" t="s">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E94" s="5" t="s">
+      <c r="E94" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="F94" s="15"/>
+      <c r="F94" s="2"/>
     </row>
     <row r="95" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="15"/>
-      <c r="B95" s="15"/>
-      <c r="C95" s="15"/>
-      <c r="D95" s="4" t="s">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E95" s="5" t="s">
+      <c r="E95" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="F95" s="15"/>
+      <c r="F95" s="2"/>
     </row>
     <row r="96" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="16"/>
-      <c r="B96" s="16"/>
-      <c r="C96" s="16"/>
-      <c r="D96" s="4" t="s">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E96" s="5" t="s">
+      <c r="E96" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="F96" s="16"/>
+      <c r="F96" s="2"/>
     </row>
     <row r="97" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="14" t="s">
+      <c r="A97" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B97" s="14" t="s">
+      <c r="B97" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C97" s="14" t="s">
+      <c r="C97" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="D97" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E97" s="3" t="s">
+      <c r="E97" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="F97" s="14" t="s">
+      <c r="F97" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="15"/>
-      <c r="B98" s="15"/>
-      <c r="C98" s="15"/>
-      <c r="D98" s="2" t="s">
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E98" s="3" t="s">
+      <c r="E98" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="F98" s="15"/>
+      <c r="F98" s="3"/>
     </row>
     <row r="99" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="15"/>
-      <c r="B99" s="15"/>
-      <c r="C99" s="15"/>
-      <c r="D99" s="2" t="s">
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E99" s="3" t="s">
+      <c r="E99" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="F99" s="15"/>
+      <c r="F99" s="3"/>
     </row>
     <row r="100" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="15"/>
-      <c r="B100" s="15"/>
-      <c r="C100" s="15"/>
-      <c r="D100" s="2" t="s">
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="E100" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="F100" s="15"/>
+      <c r="F100" s="3"/>
     </row>
     <row r="101" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="16"/>
-      <c r="B101" s="16"/>
-      <c r="C101" s="16"/>
-      <c r="D101" s="2" t="s">
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="E101" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="F101" s="16"/>
+      <c r="F101" s="3"/>
     </row>
     <row r="102" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="17" t="s">
+      <c r="A102" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B102" s="17" t="s">
+      <c r="B102" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C102" s="17" t="s">
+      <c r="C102" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D102" s="4" t="s">
+      <c r="D102" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E102" s="5" t="s">
+      <c r="E102" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="F102" s="17" t="s">
+      <c r="F102" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="15"/>
-      <c r="B103" s="15"/>
-      <c r="C103" s="15"/>
-      <c r="D103" s="4" t="s">
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E103" s="5" t="s">
+      <c r="E103" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="F103" s="15"/>
+      <c r="F103" s="2"/>
     </row>
     <row r="104" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="15"/>
-      <c r="B104" s="15"/>
-      <c r="C104" s="15"/>
-      <c r="D104" s="4" t="s">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E104" s="5" t="s">
+      <c r="E104" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="F104" s="15"/>
+      <c r="F104" s="2"/>
     </row>
     <row r="105" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="15"/>
-      <c r="B105" s="15"/>
-      <c r="C105" s="15"/>
-      <c r="D105" s="4" t="s">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E105" s="5" t="s">
+      <c r="E105" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="F105" s="15"/>
+      <c r="F105" s="2"/>
     </row>
     <row r="106" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="16"/>
-      <c r="B106" s="16"/>
-      <c r="C106" s="16"/>
-      <c r="D106" s="4" t="s">
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E106" s="5" t="s">
+      <c r="E106" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="F106" s="16"/>
+      <c r="F106" s="2"/>
     </row>
     <row r="107" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="14" t="s">
+      <c r="A107" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B107" s="14" t="s">
+      <c r="B107" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C107" s="14" t="s">
+      <c r="C107" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="D107" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E107" s="3" t="s">
+      <c r="E107" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="F107" s="14" t="s">
+      <c r="F107" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="15"/>
-      <c r="B108" s="15"/>
-      <c r="C108" s="15"/>
-      <c r="D108" s="2" t="s">
+      <c r="A108" s="3"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E108" s="3" t="s">
+      <c r="E108" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="F108" s="15"/>
+      <c r="F108" s="3"/>
     </row>
     <row r="109" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="15"/>
-      <c r="B109" s="15"/>
-      <c r="C109" s="15"/>
-      <c r="D109" s="2" t="s">
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E109" s="3" t="s">
+      <c r="E109" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="F109" s="15"/>
+      <c r="F109" s="3"/>
     </row>
     <row r="110" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="15"/>
-      <c r="B110" s="15"/>
-      <c r="C110" s="15"/>
-      <c r="D110" s="2" t="s">
+      <c r="A110" s="3"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E110" s="3" t="s">
+      <c r="E110" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="F110" s="15"/>
+      <c r="F110" s="3"/>
     </row>
     <row r="111" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="16"/>
-      <c r="B111" s="16"/>
-      <c r="C111" s="16"/>
-      <c r="D111" s="2" t="s">
+      <c r="A111" s="3"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E111" s="3" t="s">
+      <c r="E111" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="F111" s="16"/>
+      <c r="F111" s="3"/>
     </row>
     <row r="112" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="17" t="s">
+      <c r="A112" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B112" s="17" t="s">
+      <c r="B112" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C112" s="17" t="s">
+      <c r="C112" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D112" s="4" t="s">
+      <c r="D112" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E112" s="5" t="s">
+      <c r="E112" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="F112" s="17" t="s">
+      <c r="F112" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="15"/>
-      <c r="B113" s="15"/>
-      <c r="C113" s="15"/>
-      <c r="D113" s="4" t="s">
+      <c r="A113" s="2"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+      <c r="D113" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E113" s="5" t="s">
+      <c r="E113" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="F113" s="15"/>
+      <c r="F113" s="2"/>
     </row>
     <row r="114" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="15"/>
-      <c r="B114" s="15"/>
-      <c r="C114" s="15"/>
-      <c r="D114" s="4" t="s">
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E114" s="5" t="s">
+      <c r="E114" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="F114" s="15"/>
+      <c r="F114" s="2"/>
     </row>
     <row r="115" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="15"/>
-      <c r="B115" s="15"/>
-      <c r="C115" s="15"/>
-      <c r="D115" s="4" t="s">
+      <c r="A115" s="2"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E115" s="5" t="s">
+      <c r="E115" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="F115" s="15"/>
+      <c r="F115" s="2"/>
     </row>
     <row r="116" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="16"/>
-      <c r="B116" s="16"/>
-      <c r="C116" s="16"/>
-      <c r="D116" s="4" t="s">
+      <c r="A116" s="2"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E116" s="5" t="s">
+      <c r="E116" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="F116" s="16"/>
+      <c r="F116" s="2"/>
     </row>
     <row r="117" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="14" t="s">
+      <c r="A117" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B117" s="14" t="s">
+      <c r="B117" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C117" s="14" t="s">
+      <c r="C117" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="D117" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E117" s="3" t="s">
+      <c r="E117" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F117" s="14" t="s">
+      <c r="F117" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="15"/>
-      <c r="B118" s="15"/>
-      <c r="C118" s="15"/>
-      <c r="D118" s="2" t="s">
+      <c r="A118" s="3"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E118" s="3" t="s">
+      <c r="E118" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="F118" s="15"/>
+      <c r="F118" s="3"/>
     </row>
     <row r="119" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="15"/>
-      <c r="B119" s="15"/>
-      <c r="C119" s="15"/>
-      <c r="D119" s="2" t="s">
+      <c r="A119" s="3"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E119" s="3" t="s">
+      <c r="E119" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="F119" s="15"/>
+      <c r="F119" s="3"/>
     </row>
     <row r="120" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="15"/>
-      <c r="B120" s="15"/>
-      <c r="C120" s="15"/>
-      <c r="D120" s="2" t="s">
+      <c r="A120" s="3"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E120" s="3" t="s">
+      <c r="E120" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="F120" s="15"/>
+      <c r="F120" s="3"/>
     </row>
     <row r="121" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="16"/>
-      <c r="B121" s="16"/>
-      <c r="C121" s="16"/>
-      <c r="D121" s="2" t="s">
+      <c r="A121" s="3"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E121" s="3" t="s">
+      <c r="E121" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="F121" s="16"/>
+      <c r="F121" s="3"/>
     </row>
     <row r="122" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="17" t="s">
+      <c r="A122" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B122" s="17" t="s">
+      <c r="B122" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C122" s="17" t="s">
+      <c r="C122" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D122" s="4" t="s">
+      <c r="D122" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E122" s="5" t="s">
+      <c r="E122" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="F122" s="17" t="s">
+      <c r="F122" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="15"/>
-      <c r="B123" s="15"/>
-      <c r="C123" s="15"/>
-      <c r="D123" s="4" t="s">
+      <c r="A123" s="2"/>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E123" s="5" t="s">
+      <c r="E123" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="F123" s="15"/>
+      <c r="F123" s="2"/>
     </row>
     <row r="124" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="15"/>
-      <c r="B124" s="15"/>
-      <c r="C124" s="15"/>
-      <c r="D124" s="4" t="s">
+      <c r="A124" s="2"/>
+      <c r="B124" s="2"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E124" s="5" t="s">
+      <c r="E124" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="F124" s="15"/>
+      <c r="F124" s="2"/>
     </row>
     <row r="125" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="15"/>
-      <c r="B125" s="15"/>
-      <c r="C125" s="15"/>
-      <c r="D125" s="4" t="s">
+      <c r="A125" s="2"/>
+      <c r="B125" s="2"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E125" s="5" t="s">
+      <c r="E125" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="F125" s="15"/>
+      <c r="F125" s="2"/>
     </row>
     <row r="126" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="16"/>
-      <c r="B126" s="16"/>
-      <c r="C126" s="16"/>
-      <c r="D126" s="4" t="s">
+      <c r="A126" s="2"/>
+      <c r="B126" s="2"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E126" s="5" t="s">
+      <c r="E126" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="F126" s="16"/>
+      <c r="F126" s="2"/>
     </row>
     <row r="127" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="14" t="s">
+      <c r="A127" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B127" s="14" t="s">
+      <c r="B127" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C127" s="14" t="s">
+      <c r="C127" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="D127" s="2" t="s">
+      <c r="D127" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E127" s="3" t="s">
+      <c r="E127" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="F127" s="14" t="s">
+      <c r="F127" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="15"/>
-      <c r="B128" s="15"/>
-      <c r="C128" s="15"/>
-      <c r="D128" s="2" t="s">
+      <c r="A128" s="3"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E128" s="3" t="s">
+      <c r="E128" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="F128" s="15"/>
+      <c r="F128" s="3"/>
     </row>
     <row r="129" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="15"/>
-      <c r="B129" s="15"/>
-      <c r="C129" s="15"/>
-      <c r="D129" s="2" t="s">
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E129" s="3" t="s">
+      <c r="E129" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="F129" s="15"/>
+      <c r="F129" s="3"/>
     </row>
     <row r="130" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="15"/>
-      <c r="B130" s="15"/>
-      <c r="C130" s="15"/>
-      <c r="D130" s="2" t="s">
+      <c r="A130" s="3"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E130" s="3" t="s">
+      <c r="E130" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="F130" s="15"/>
+      <c r="F130" s="3"/>
     </row>
     <row r="131" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="16"/>
-      <c r="B131" s="16"/>
-      <c r="C131" s="16"/>
-      <c r="D131" s="2" t="s">
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E131" s="3" t="s">
+      <c r="E131" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="F131" s="16"/>
+      <c r="F131" s="3"/>
     </row>
     <row r="132" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="17" t="s">
+      <c r="A132" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B132" s="17" t="s">
+      <c r="B132" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C132" s="17" t="s">
+      <c r="C132" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D132" s="4" t="s">
+      <c r="D132" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E132" s="5" t="s">
+      <c r="E132" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="F132" s="17" t="s">
+      <c r="F132" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="15"/>
-      <c r="B133" s="15"/>
-      <c r="C133" s="15"/>
-      <c r="D133" s="4" t="s">
+      <c r="A133" s="2"/>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E133" s="5" t="s">
+      <c r="E133" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="F133" s="15"/>
+      <c r="F133" s="2"/>
     </row>
     <row r="134" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="15"/>
-      <c r="B134" s="15"/>
-      <c r="C134" s="15"/>
-      <c r="D134" s="4" t="s">
+      <c r="A134" s="2"/>
+      <c r="B134" s="2"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E134" s="5" t="s">
+      <c r="E134" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="F134" s="15"/>
+      <c r="F134" s="2"/>
     </row>
     <row r="135" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="15"/>
-      <c r="B135" s="15"/>
-      <c r="C135" s="15"/>
-      <c r="D135" s="4" t="s">
+      <c r="A135" s="2"/>
+      <c r="B135" s="2"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E135" s="5" t="s">
+      <c r="E135" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="F135" s="15"/>
+      <c r="F135" s="2"/>
     </row>
     <row r="136" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="16"/>
-      <c r="B136" s="16"/>
-      <c r="C136" s="16"/>
-      <c r="D136" s="4" t="s">
+      <c r="A136" s="2"/>
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E136" s="5" t="s">
+      <c r="E136" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="F136" s="16"/>
+      <c r="F136" s="2"/>
     </row>
     <row r="137" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="14" t="s">
+      <c r="A137" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B137" s="14" t="s">
+      <c r="B137" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C137" s="14" t="s">
+      <c r="C137" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D137" s="2" t="s">
+      <c r="D137" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E137" s="3" t="s">
+      <c r="E137" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F137" s="14" t="s">
+      <c r="F137" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="15"/>
-      <c r="B138" s="15"/>
-      <c r="C138" s="15"/>
-      <c r="D138" s="2" t="s">
+      <c r="A138" s="3"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E138" s="3" t="s">
+      <c r="E138" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F138" s="15"/>
+      <c r="F138" s="3"/>
     </row>
     <row r="139" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="15"/>
-      <c r="B139" s="15"/>
-      <c r="C139" s="15"/>
-      <c r="D139" s="2" t="s">
+      <c r="A139" s="3"/>
+      <c r="B139" s="3"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E139" s="3" t="s">
+      <c r="E139" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F139" s="15"/>
+      <c r="F139" s="3"/>
     </row>
     <row r="140" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="15"/>
-      <c r="B140" s="15"/>
-      <c r="C140" s="15"/>
-      <c r="D140" s="2" t="s">
+      <c r="A140" s="3"/>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E140" s="3" t="s">
+      <c r="E140" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F140" s="15"/>
+      <c r="F140" s="3"/>
     </row>
     <row r="141" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="16"/>
-      <c r="B141" s="16"/>
-      <c r="C141" s="16"/>
-      <c r="D141" s="2" t="s">
+      <c r="A141" s="3"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E141" s="3" t="s">
+      <c r="E141" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F141" s="16"/>
+      <c r="F141" s="3"/>
     </row>
     <row r="142" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="14" t="s">
+      <c r="A142" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B142" s="14" t="s">
+      <c r="B142" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C142" s="14" t="s">
+      <c r="C142" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D142" s="2" t="s">
+      <c r="D142" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E142" s="3" t="s">
+      <c r="E142" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="F142" s="14" t="s">
+      <c r="F142" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="15"/>
-      <c r="B143" s="15"/>
-      <c r="C143" s="15"/>
-      <c r="D143" s="2" t="s">
+      <c r="A143" s="3"/>
+      <c r="B143" s="3"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E143" s="3" t="s">
+      <c r="E143" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="F143" s="15"/>
+      <c r="F143" s="3"/>
     </row>
     <row r="144" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="15"/>
-      <c r="B144" s="15"/>
-      <c r="C144" s="15"/>
-      <c r="D144" s="2" t="s">
+      <c r="A144" s="3"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E144" s="3" t="s">
+      <c r="E144" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="F144" s="15"/>
+      <c r="F144" s="3"/>
     </row>
     <row r="145" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="15"/>
-      <c r="B145" s="15"/>
-      <c r="C145" s="15"/>
-      <c r="D145" s="2" t="s">
+      <c r="A145" s="3"/>
+      <c r="B145" s="3"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E145" s="3" t="s">
+      <c r="E145" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="F145" s="15"/>
+      <c r="F145" s="3"/>
     </row>
     <row r="146" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="16"/>
-      <c r="B146" s="16"/>
-      <c r="C146" s="16"/>
-      <c r="D146" s="2" t="s">
+      <c r="A146" s="3"/>
+      <c r="B146" s="3"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E146" s="3" t="s">
+      <c r="E146" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="F146" s="16"/>
+      <c r="F146" s="3"/>
     </row>
     <row r="147" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="17" t="s">
+      <c r="A147" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B147" s="17" t="s">
+      <c r="B147" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C147" s="17" t="s">
+      <c r="C147" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D147" s="4" t="s">
+      <c r="D147" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E147" s="5" t="s">
+      <c r="E147" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="F147" s="17" t="s">
+      <c r="F147" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="15"/>
-      <c r="B148" s="15"/>
-      <c r="C148" s="15"/>
-      <c r="D148" s="4" t="s">
+      <c r="A148" s="2"/>
+      <c r="B148" s="2"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E148" s="5" t="s">
+      <c r="E148" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="F148" s="15"/>
+      <c r="F148" s="2"/>
     </row>
     <row r="149" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="15"/>
-      <c r="B149" s="15"/>
-      <c r="C149" s="15"/>
-      <c r="D149" s="4" t="s">
+      <c r="A149" s="2"/>
+      <c r="B149" s="2"/>
+      <c r="C149" s="2"/>
+      <c r="D149" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E149" s="5" t="s">
+      <c r="E149" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="F149" s="15"/>
+      <c r="F149" s="2"/>
     </row>
     <row r="150" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="15"/>
-      <c r="B150" s="15"/>
-      <c r="C150" s="15"/>
-      <c r="D150" s="4" t="s">
+      <c r="A150" s="2"/>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E150" s="5" t="s">
+      <c r="E150" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="F150" s="15"/>
+      <c r="F150" s="2"/>
     </row>
     <row r="151" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="16"/>
-      <c r="B151" s="16"/>
-      <c r="C151" s="16"/>
-      <c r="D151" s="4" t="s">
+      <c r="A151" s="2"/>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E151" s="5" t="s">
+      <c r="E151" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="F151" s="16"/>
+      <c r="F151" s="2"/>
     </row>
     <row r="152" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="14" t="s">
+      <c r="A152" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B152" s="14" t="s">
+      <c r="B152" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C152" s="14" t="s">
+      <c r="C152" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="D152" s="2" t="s">
+      <c r="D152" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E152" s="3" t="s">
+      <c r="E152" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="F152" s="14" t="s">
+      <c r="F152" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="15"/>
-      <c r="B153" s="15"/>
-      <c r="C153" s="15"/>
-      <c r="D153" s="2" t="s">
+      <c r="A153" s="3"/>
+      <c r="B153" s="3"/>
+      <c r="C153" s="3"/>
+      <c r="D153" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E153" s="3" t="s">
+      <c r="E153" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="F153" s="15"/>
+      <c r="F153" s="3"/>
     </row>
     <row r="154" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="15"/>
-      <c r="B154" s="15"/>
-      <c r="C154" s="15"/>
-      <c r="D154" s="2" t="s">
+      <c r="A154" s="3"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="3"/>
+      <c r="D154" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E154" s="3" t="s">
+      <c r="E154" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="F154" s="15"/>
+      <c r="F154" s="3"/>
     </row>
     <row r="155" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="15"/>
-      <c r="B155" s="15"/>
-      <c r="C155" s="15"/>
-      <c r="D155" s="2" t="s">
+      <c r="A155" s="3"/>
+      <c r="B155" s="3"/>
+      <c r="C155" s="3"/>
+      <c r="D155" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E155" s="3" t="s">
+      <c r="E155" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="F155" s="15"/>
+      <c r="F155" s="3"/>
     </row>
     <row r="156" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="16"/>
-      <c r="B156" s="16"/>
-      <c r="C156" s="16"/>
-      <c r="D156" s="2" t="s">
+      <c r="A156" s="3"/>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E156" s="3" t="s">
+      <c r="E156" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="F156" s="16"/>
+      <c r="F156" s="3"/>
     </row>
     <row r="157" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="17" t="s">
+      <c r="A157" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B157" s="17" t="s">
+      <c r="B157" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C157" s="17" t="s">
+      <c r="C157" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D157" s="4" t="s">
+      <c r="D157" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E157" s="5" t="s">
+      <c r="E157" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="F157" s="17" t="s">
+      <c r="F157" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="15"/>
-      <c r="B158" s="15"/>
-      <c r="C158" s="15"/>
-      <c r="D158" s="4" t="s">
+      <c r="A158" s="2"/>
+      <c r="B158" s="2"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E158" s="5" t="s">
+      <c r="E158" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="F158" s="15"/>
+      <c r="F158" s="2"/>
     </row>
     <row r="159" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="15"/>
-      <c r="B159" s="15"/>
-      <c r="C159" s="15"/>
-      <c r="D159" s="4" t="s">
+      <c r="A159" s="2"/>
+      <c r="B159" s="2"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E159" s="5" t="s">
+      <c r="E159" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="F159" s="15"/>
+      <c r="F159" s="2"/>
     </row>
     <row r="160" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="15"/>
-      <c r="B160" s="15"/>
-      <c r="C160" s="15"/>
-      <c r="D160" s="4" t="s">
+      <c r="A160" s="2"/>
+      <c r="B160" s="2"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E160" s="5" t="s">
+      <c r="E160" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="F160" s="15"/>
+      <c r="F160" s="2"/>
     </row>
     <row r="161" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="16"/>
-      <c r="B161" s="16"/>
-      <c r="C161" s="16"/>
-      <c r="D161" s="4" t="s">
+      <c r="A161" s="2"/>
+      <c r="B161" s="2"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E161" s="5" t="s">
+      <c r="E161" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="F161" s="16"/>
+      <c r="F161" s="2"/>
     </row>
     <row r="162" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="14" t="s">
+      <c r="A162" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B162" s="14" t="s">
+      <c r="B162" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C162" s="14" t="s">
+      <c r="C162" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="D162" s="2" t="s">
+      <c r="D162" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E162" s="3" t="s">
+      <c r="E162" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="F162" s="14" t="s">
+      <c r="F162" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="15"/>
-      <c r="B163" s="15"/>
-      <c r="C163" s="15"/>
-      <c r="D163" s="2" t="s">
+      <c r="A163" s="3"/>
+      <c r="B163" s="3"/>
+      <c r="C163" s="3"/>
+      <c r="D163" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E163" s="3" t="s">
+      <c r="E163" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="F163" s="15"/>
+      <c r="F163" s="3"/>
     </row>
     <row r="164" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="15"/>
-      <c r="B164" s="15"/>
-      <c r="C164" s="15"/>
-      <c r="D164" s="2" t="s">
+      <c r="A164" s="3"/>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E164" s="3" t="s">
+      <c r="E164" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="F164" s="15"/>
+      <c r="F164" s="3"/>
     </row>
     <row r="165" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="15"/>
-      <c r="B165" s="15"/>
-      <c r="C165" s="15"/>
-      <c r="D165" s="2" t="s">
+      <c r="A165" s="3"/>
+      <c r="B165" s="3"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E165" s="3" t="s">
+      <c r="E165" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="F165" s="15"/>
+      <c r="F165" s="3"/>
     </row>
     <row r="166" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="16"/>
-      <c r="B166" s="16"/>
-      <c r="C166" s="16"/>
-      <c r="D166" s="2" t="s">
+      <c r="A166" s="3"/>
+      <c r="B166" s="3"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E166" s="3" t="s">
+      <c r="E166" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="F166" s="16"/>
+      <c r="F166" s="3"/>
     </row>
     <row r="167" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="17">
+      <c r="A167" s="2">
         <v>19010864</v>
       </c>
-      <c r="B167" s="17" t="s">
+      <c r="B167" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C167" s="17" t="s">
+      <c r="C167" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D167" s="4" t="s">
+      <c r="D167" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E167" s="5" t="s">
+      <c r="E167" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="F167" s="17" t="s">
+      <c r="F167" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="15"/>
-      <c r="B168" s="15"/>
-      <c r="C168" s="15"/>
-      <c r="D168" s="4" t="s">
+      <c r="A168" s="2"/>
+      <c r="B168" s="2"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E168" s="5" t="s">
+      <c r="E168" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="F168" s="15"/>
+      <c r="F168" s="2"/>
     </row>
     <row r="169" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="15"/>
-      <c r="B169" s="15"/>
-      <c r="C169" s="15"/>
-      <c r="D169" s="4" t="s">
+      <c r="A169" s="2"/>
+      <c r="B169" s="2"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E169" s="5" t="s">
+      <c r="E169" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="F169" s="15"/>
+      <c r="F169" s="2"/>
     </row>
     <row r="170" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="15"/>
-      <c r="B170" s="15"/>
-      <c r="C170" s="15"/>
-      <c r="D170" s="4" t="s">
+      <c r="A170" s="2"/>
+      <c r="B170" s="2"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E170" s="5" t="s">
+      <c r="E170" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="F170" s="15"/>
+      <c r="F170" s="2"/>
     </row>
     <row r="171" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="16"/>
-      <c r="B171" s="16"/>
-      <c r="C171" s="16"/>
-      <c r="D171" s="4" t="s">
+      <c r="A171" s="2"/>
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E171" s="5" t="s">
+      <c r="E171" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="F171" s="16"/>
+      <c r="F171" s="2"/>
     </row>
     <row r="172" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="18" t="s">
+      <c r="A172" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B172" s="14" t="s">
+      <c r="B172" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C172" s="14" t="s">
+      <c r="C172" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="D172" s="2" t="s">
+      <c r="D172" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E172" s="3" t="s">
+      <c r="E172" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="F172" s="14" t="s">
+      <c r="F172" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="15"/>
-      <c r="B173" s="15"/>
-      <c r="C173" s="15"/>
-      <c r="D173" s="2" t="s">
+      <c r="A173" s="1"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="1"/>
+      <c r="D173" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E173" s="3" t="s">
+      <c r="E173" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="F173" s="15"/>
+      <c r="F173" s="3"/>
     </row>
     <row r="174" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="15"/>
-      <c r="B174" s="15"/>
-      <c r="C174" s="15"/>
-      <c r="D174" s="2" t="s">
+      <c r="A174" s="1"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="1"/>
+      <c r="D174" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E174" s="3" t="s">
+      <c r="E174" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="F174" s="15"/>
+      <c r="F174" s="3"/>
     </row>
     <row r="175" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="15"/>
-      <c r="B175" s="15"/>
-      <c r="C175" s="15"/>
-      <c r="D175" s="2" t="s">
+      <c r="A175" s="1"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
+      <c r="D175" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E175" s="3" t="s">
+      <c r="E175" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="F175" s="15"/>
+      <c r="F175" s="3"/>
     </row>
     <row r="176" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="16"/>
-      <c r="B176" s="16"/>
-      <c r="C176" s="16"/>
-      <c r="D176" s="2" t="s">
+      <c r="A176" s="1"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="1"/>
+      <c r="D176" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E176" s="3" t="s">
+      <c r="E176" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="F176" s="16"/>
+      <c r="F176" s="3"/>
     </row>
     <row r="177" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="11" t="s">
+      <c r="A177" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B177" s="11" t="s">
+      <c r="B177" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="3"/>
+      <c r="B178" s="3"/>
+      <c r="C178" s="3"/>
+      <c r="D178" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="F178" s="3"/>
+    </row>
+    <row r="179" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="3"/>
+      <c r="B179" s="3"/>
+      <c r="C179" s="3"/>
+      <c r="D179" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E179" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="F179" s="3"/>
+    </row>
+    <row r="180" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="3"/>
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E180" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F180" s="3"/>
+    </row>
+    <row r="181" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="3"/>
+      <c r="B181" s="3"/>
+      <c r="C181" s="3"/>
+      <c r="D181" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E181" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="F181" s="3"/>
+    </row>
+    <row r="182" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D182" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E182" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="3"/>
+      <c r="B183" s="3"/>
+      <c r="C183" s="3"/>
+      <c r="D183" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E183" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="F183" s="3"/>
+    </row>
+    <row r="184" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="3"/>
+      <c r="B184" s="3"/>
+      <c r="C184" s="3"/>
+      <c r="D184" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E184" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="F184" s="3"/>
+    </row>
+    <row r="185" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="3"/>
+      <c r="B185" s="3"/>
+      <c r="C185" s="3"/>
+      <c r="D185" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E185" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="F185" s="3"/>
+    </row>
+    <row r="186" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="3"/>
+      <c r="B186" s="3"/>
+      <c r="C186" s="3"/>
+      <c r="D186" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E186" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="F186" s="3"/>
+    </row>
+    <row r="187" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E187" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="3"/>
+      <c r="B188" s="3"/>
+      <c r="C188" s="3"/>
+      <c r="D188" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E188" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="F188" s="3"/>
+    </row>
+    <row r="189" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="3"/>
+      <c r="B189" s="3"/>
+      <c r="C189" s="3"/>
+      <c r="D189" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E189" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="F189" s="3"/>
+    </row>
+    <row r="190" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="3"/>
+      <c r="B190" s="3"/>
+      <c r="C190" s="3"/>
+      <c r="D190" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E190" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="F190" s="3"/>
+    </row>
+    <row r="191" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="3"/>
+      <c r="B191" s="3"/>
+      <c r="C191" s="3"/>
+      <c r="D191" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E191" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="F191" s="3"/>
+    </row>
+    <row r="192" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="D192" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E192" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="3"/>
+      <c r="B193" s="3"/>
+      <c r="C193" s="3"/>
+      <c r="D193" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E193" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="F193" s="3"/>
+    </row>
+    <row r="194" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="3"/>
+      <c r="B194" s="3"/>
+      <c r="C194" s="3"/>
+      <c r="D194" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E194" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="F194" s="3"/>
+    </row>
+    <row r="195" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="3"/>
+      <c r="B195" s="3"/>
+      <c r="C195" s="3"/>
+      <c r="D195" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E195" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="F195" s="3"/>
+    </row>
+    <row r="196" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="3"/>
+      <c r="B196" s="3"/>
+      <c r="C196" s="3"/>
+      <c r="D196" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E196" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="F196" s="3"/>
+    </row>
+    <row r="197" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D197" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E197" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="3"/>
+      <c r="B198" s="3"/>
+      <c r="C198" s="3"/>
+      <c r="D198" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E198" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F198" s="3"/>
+    </row>
+    <row r="199" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="3"/>
+      <c r="B199" s="3"/>
+      <c r="C199" s="3"/>
+      <c r="D199" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E199" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="F199" s="3"/>
+    </row>
+    <row r="200" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="3"/>
+      <c r="B200" s="3"/>
+      <c r="C200" s="3"/>
+      <c r="D200" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E200" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="F200" s="3"/>
+    </row>
+    <row r="201" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="3"/>
+      <c r="B201" s="3"/>
+      <c r="C201" s="3"/>
+      <c r="D201" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E201" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="F201" s="3"/>
+    </row>
+    <row r="202" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D202" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E202" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="3"/>
+      <c r="B203" s="3"/>
+      <c r="C203" s="3"/>
+      <c r="D203" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E203" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="F203" s="3"/>
+    </row>
+    <row r="204" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="3"/>
+      <c r="B204" s="3"/>
+      <c r="C204" s="3"/>
+      <c r="D204" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E204" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="F204" s="3"/>
+    </row>
+    <row r="205" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="3"/>
+      <c r="B205" s="3"/>
+      <c r="C205" s="3"/>
+      <c r="D205" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E205" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F205" s="3"/>
+    </row>
+    <row r="206" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="3"/>
+      <c r="B206" s="3"/>
+      <c r="C206" s="3"/>
+      <c r="D206" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E206" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="F206" s="3"/>
+    </row>
+    <row r="207" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D207" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E207" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="3"/>
+      <c r="B208" s="3"/>
+      <c r="C208" s="3"/>
+      <c r="D208" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E208" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="F208" s="3"/>
+    </row>
+    <row r="209" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="3"/>
+      <c r="B209" s="3"/>
+      <c r="C209" s="3"/>
+      <c r="D209" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E209" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="F209" s="3"/>
+    </row>
+    <row r="210" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="3"/>
+      <c r="B210" s="3"/>
+      <c r="C210" s="3"/>
+      <c r="D210" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E210" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F210" s="3"/>
+    </row>
+    <row r="211" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="3"/>
+      <c r="B211" s="3"/>
+      <c r="C211" s="3"/>
+      <c r="D211" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E211" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="F211" s="3"/>
+    </row>
+    <row r="212" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D212" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E212" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A213" s="3"/>
+      <c r="B213" s="3"/>
+      <c r="C213" s="3"/>
+      <c r="D213" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E213" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="F213" s="3"/>
+    </row>
+    <row r="214" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="3"/>
+      <c r="B214" s="3"/>
+      <c r="C214" s="3"/>
+      <c r="D214" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E214" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="F214" s="3"/>
+    </row>
+    <row r="215" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="3"/>
+      <c r="B215" s="3"/>
+      <c r="C215" s="3"/>
+      <c r="D215" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E215" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="F215" s="3"/>
+    </row>
+    <row r="216" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A216" s="3"/>
+      <c r="B216" s="3"/>
+      <c r="C216" s="3"/>
+      <c r="D216" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E216" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="F216" s="3"/>
+    </row>
+    <row r="217" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D217" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E217" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="3"/>
+      <c r="B218" s="3"/>
+      <c r="C218" s="3"/>
+      <c r="D218" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E218" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="F218" s="3"/>
+    </row>
+    <row r="219" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="3"/>
+      <c r="B219" s="3"/>
+      <c r="C219" s="3"/>
+      <c r="D219" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E219" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="C177" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="D177" s="6" t="s">
+      <c r="F219" s="3"/>
+    </row>
+    <row r="220" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A220" s="3"/>
+      <c r="B220" s="3"/>
+      <c r="C220" s="3"/>
+      <c r="D220" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E220" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="F220" s="3"/>
+    </row>
+    <row r="221" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A221" s="3"/>
+      <c r="B221" s="3"/>
+      <c r="C221" s="3"/>
+      <c r="D221" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E221" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F221" s="3"/>
+    </row>
+    <row r="222" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A222" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="D222" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E177" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="F177" s="11" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="12"/>
-      <c r="B178" s="12"/>
-      <c r="C178" s="12"/>
-      <c r="D178" s="6" t="s">
+      <c r="E222" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A223" s="3"/>
+      <c r="B223" s="3"/>
+      <c r="C223" s="3"/>
+      <c r="D223" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E178" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="F178" s="12"/>
-    </row>
-    <row r="179" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="12"/>
-      <c r="B179" s="12"/>
-      <c r="C179" s="12"/>
-      <c r="D179" s="6" t="s">
+      <c r="E223" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="F223" s="3"/>
+    </row>
+    <row r="224" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A224" s="3"/>
+      <c r="B224" s="3"/>
+      <c r="C224" s="3"/>
+      <c r="D224" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E179" s="7" t="s">
+      <c r="E224" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="F224" s="3"/>
+    </row>
+    <row r="225" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A225" s="3"/>
+      <c r="B225" s="3"/>
+      <c r="C225" s="3"/>
+      <c r="D225" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E225" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="F225" s="3"/>
+    </row>
+    <row r="226" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="3"/>
+      <c r="B226" s="3"/>
+      <c r="C226" s="3"/>
+      <c r="D226" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E226" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="F226" s="3"/>
+    </row>
+    <row r="227" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A227" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D227" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E227" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="F227" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="F179" s="12"/>
-    </row>
-    <row r="180" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="12"/>
-      <c r="B180" s="12"/>
-      <c r="C180" s="12"/>
-      <c r="D180" s="6" t="s">
+    </row>
+    <row r="228" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="3"/>
+      <c r="B228" s="3"/>
+      <c r="C228" s="3"/>
+      <c r="D228" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E228" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="F228" s="3"/>
+    </row>
+    <row r="229" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="3"/>
+      <c r="B229" s="3"/>
+      <c r="C229" s="3"/>
+      <c r="D229" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E229" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="F229" s="3"/>
+    </row>
+    <row r="230" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="3"/>
+      <c r="B230" s="3"/>
+      <c r="C230" s="3"/>
+      <c r="D230" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E180" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="F180" s="12"/>
-    </row>
-    <row r="181" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="13"/>
-      <c r="B181" s="13"/>
-      <c r="C181" s="13"/>
-      <c r="D181" s="6" t="s">
+      <c r="E230" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="F230" s="3"/>
+    </row>
+    <row r="231" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="3"/>
+      <c r="B231" s="3"/>
+      <c r="C231" s="3"/>
+      <c r="D231" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E181" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="F181" s="13"/>
-    </row>
-    <row r="182" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="B182" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="C182" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="D182" s="2" t="s">
+      <c r="E231" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="F231" s="3"/>
+    </row>
+    <row r="232" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D232" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E182" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="F182" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="9"/>
-      <c r="B183" s="9"/>
-      <c r="C183" s="9"/>
-      <c r="D183" s="2" t="s">
+      <c r="E232" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A233" s="3"/>
+      <c r="B233" s="3"/>
+      <c r="C233" s="3"/>
+      <c r="D233" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E183" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="F183" s="9"/>
-    </row>
-    <row r="184" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="9"/>
-      <c r="B184" s="9"/>
-      <c r="C184" s="9"/>
-      <c r="D184" s="2" t="s">
+      <c r="E233" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="F233" s="3"/>
+    </row>
+    <row r="234" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="3"/>
+      <c r="B234" s="3"/>
+      <c r="C234" s="3"/>
+      <c r="D234" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E184" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="F184" s="9"/>
-    </row>
-    <row r="185" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="9"/>
-      <c r="B185" s="9"/>
-      <c r="C185" s="9"/>
-      <c r="D185" s="2" t="s">
+      <c r="E234" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="F234" s="3"/>
+    </row>
+    <row r="235" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A235" s="3"/>
+      <c r="B235" s="3"/>
+      <c r="C235" s="3"/>
+      <c r="D235" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E185" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="F185" s="9"/>
-    </row>
-    <row r="186" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="10"/>
-      <c r="B186" s="10"/>
-      <c r="C186" s="10"/>
-      <c r="D186" s="2" t="s">
+      <c r="E235" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="F235" s="3"/>
+    </row>
+    <row r="236" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="3"/>
+      <c r="B236" s="3"/>
+      <c r="C236" s="3"/>
+      <c r="D236" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E186" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="F186" s="10"/>
-    </row>
-    <row r="187" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="B187" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="C187" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="D187" s="2" t="s">
+      <c r="E236" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F236" s="3"/>
+    </row>
+    <row r="237" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A237" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="D237" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E187" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="F187" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="9"/>
-      <c r="B188" s="9"/>
-      <c r="C188" s="9"/>
-      <c r="D188" s="2" t="s">
+      <c r="E237" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A238" s="3"/>
+      <c r="B238" s="3"/>
+      <c r="C238" s="3"/>
+      <c r="D238" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E188" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="F188" s="9"/>
-    </row>
-    <row r="189" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="9"/>
-      <c r="B189" s="9"/>
-      <c r="C189" s="9"/>
-      <c r="D189" s="2" t="s">
+      <c r="E238" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="F238" s="3"/>
+    </row>
+    <row r="239" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A239" s="3"/>
+      <c r="B239" s="3"/>
+      <c r="C239" s="3"/>
+      <c r="D239" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E189" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="F189" s="9"/>
-    </row>
-    <row r="190" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="9"/>
-      <c r="B190" s="9"/>
-      <c r="C190" s="9"/>
-      <c r="D190" s="2" t="s">
+      <c r="E239" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="F239" s="3"/>
+    </row>
+    <row r="240" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="3"/>
+      <c r="B240" s="3"/>
+      <c r="C240" s="3"/>
+      <c r="D240" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E190" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="F190" s="9"/>
-    </row>
-    <row r="191" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="10"/>
-      <c r="B191" s="10"/>
-      <c r="C191" s="10"/>
-      <c r="D191" s="2" t="s">
+      <c r="E240" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="F240" s="3"/>
+    </row>
+    <row r="241" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="3"/>
+      <c r="B241" s="3"/>
+      <c r="C241" s="3"/>
+      <c r="D241" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E191" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="F191" s="10"/>
-    </row>
-    <row r="192" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="B192" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="C192" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="D192" s="2" t="s">
+      <c r="E241" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="F241" s="3"/>
+    </row>
+    <row r="242" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A242" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D242" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E192" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="F192" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="9"/>
-      <c r="B193" s="9"/>
-      <c r="C193" s="9"/>
-      <c r="D193" s="2" t="s">
+      <c r="E242" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A243" s="3"/>
+      <c r="B243" s="3"/>
+      <c r="C243" s="3"/>
+      <c r="D243" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E193" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="F193" s="9"/>
-    </row>
-    <row r="194" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="9"/>
-      <c r="B194" s="9"/>
-      <c r="C194" s="9"/>
-      <c r="D194" s="2" t="s">
+      <c r="E243" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="F243" s="3"/>
+    </row>
+    <row r="244" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="3"/>
+      <c r="B244" s="3"/>
+      <c r="C244" s="3"/>
+      <c r="D244" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E194" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="F194" s="9"/>
-    </row>
-    <row r="195" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="9"/>
-      <c r="B195" s="9"/>
-      <c r="C195" s="9"/>
-      <c r="D195" s="2" t="s">
+      <c r="E244" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="F244" s="3"/>
+    </row>
+    <row r="245" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A245" s="3"/>
+      <c r="B245" s="3"/>
+      <c r="C245" s="3"/>
+      <c r="D245" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E195" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="F195" s="9"/>
-    </row>
-    <row r="196" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="10"/>
-      <c r="B196" s="10"/>
-      <c r="C196" s="10"/>
-      <c r="D196" s="2" t="s">
+      <c r="E245" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="F245" s="3"/>
+    </row>
+    <row r="246" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A246" s="3"/>
+      <c r="B246" s="3"/>
+      <c r="C246" s="3"/>
+      <c r="D246" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E196" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="F196" s="10"/>
-    </row>
-    <row r="197" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="B197" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="C197" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="D197" s="2" t="s">
+      <c r="E246" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="F246" s="3"/>
+    </row>
+    <row r="247" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A247" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="D247" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E197" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="F197" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="9"/>
-      <c r="B198" s="9"/>
-      <c r="C198" s="9"/>
-      <c r="D198" s="2" t="s">
+      <c r="E247" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A248" s="3"/>
+      <c r="B248" s="3"/>
+      <c r="C248" s="3"/>
+      <c r="D248" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E198" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="F198" s="9"/>
-    </row>
-    <row r="199" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="9"/>
-      <c r="B199" s="9"/>
-      <c r="C199" s="9"/>
-      <c r="D199" s="2" t="s">
+      <c r="E248" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="F248" s="3"/>
+    </row>
+    <row r="249" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A249" s="3"/>
+      <c r="B249" s="3"/>
+      <c r="C249" s="3"/>
+      <c r="D249" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E199" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="F199" s="9"/>
-    </row>
-    <row r="200" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="9"/>
-      <c r="B200" s="9"/>
-      <c r="C200" s="9"/>
-      <c r="D200" s="2" t="s">
+      <c r="E249" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="F249" s="3"/>
+    </row>
+    <row r="250" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A250" s="3"/>
+      <c r="B250" s="3"/>
+      <c r="C250" s="3"/>
+      <c r="D250" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E200" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="F200" s="9"/>
-    </row>
-    <row r="201" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="10"/>
-      <c r="B201" s="10"/>
-      <c r="C201" s="10"/>
-      <c r="D201" s="2" t="s">
+      <c r="E250" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="F250" s="3"/>
+    </row>
+    <row r="251" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A251" s="3"/>
+      <c r="B251" s="3"/>
+      <c r="C251" s="3"/>
+      <c r="D251" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E201" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="F201" s="10"/>
-    </row>
-    <row r="202" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="B202" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C202" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="D202" s="2" t="s">
+      <c r="E251" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="F251" s="3"/>
+    </row>
+    <row r="252" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A252" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="D252" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E202" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="F202" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="9"/>
-      <c r="B203" s="9"/>
-      <c r="C203" s="9"/>
-      <c r="D203" s="2" t="s">
+      <c r="E252" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="3"/>
+      <c r="B253" s="3"/>
+      <c r="C253" s="3"/>
+      <c r="D253" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E203" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="F203" s="9"/>
-    </row>
-    <row r="204" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="9"/>
-      <c r="B204" s="9"/>
-      <c r="C204" s="9"/>
-      <c r="D204" s="2" t="s">
+      <c r="E253" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="F253" s="3"/>
+    </row>
+    <row r="254" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A254" s="3"/>
+      <c r="B254" s="3"/>
+      <c r="C254" s="3"/>
+      <c r="D254" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E204" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="F204" s="9"/>
-    </row>
-    <row r="205" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="9"/>
-      <c r="B205" s="9"/>
-      <c r="C205" s="9"/>
-      <c r="D205" s="2" t="s">
+      <c r="E254" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="F254" s="3"/>
+    </row>
+    <row r="255" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A255" s="3"/>
+      <c r="B255" s="3"/>
+      <c r="C255" s="3"/>
+      <c r="D255" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E205" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="F205" s="9"/>
-    </row>
-    <row r="206" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="10"/>
-      <c r="B206" s="10"/>
-      <c r="C206" s="10"/>
-      <c r="D206" s="2" t="s">
+      <c r="E255" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="F255" s="3"/>
+    </row>
+    <row r="256" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A256" s="3"/>
+      <c r="B256" s="3"/>
+      <c r="C256" s="3"/>
+      <c r="D256" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E206" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F206" s="10"/>
-    </row>
-    <row r="207" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="B207" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="C207" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="D207" s="2" t="s">
+      <c r="E256" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="F256" s="3"/>
+    </row>
+    <row r="257" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D257" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E207" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="F207" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="9"/>
-      <c r="B208" s="9"/>
-      <c r="C208" s="9"/>
-      <c r="D208" s="2" t="s">
+      <c r="E257" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A258" s="3"/>
+      <c r="B258" s="3"/>
+      <c r="C258" s="3"/>
+      <c r="D258" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E208" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="F208" s="9"/>
-    </row>
-    <row r="209" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="9"/>
-      <c r="B209" s="9"/>
-      <c r="C209" s="9"/>
-      <c r="D209" s="2" t="s">
+      <c r="E258" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="F258" s="3"/>
+    </row>
+    <row r="259" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A259" s="3"/>
+      <c r="B259" s="3"/>
+      <c r="C259" s="3"/>
+      <c r="D259" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E209" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="F209" s="9"/>
-    </row>
-    <row r="210" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="9"/>
-      <c r="B210" s="9"/>
-      <c r="C210" s="9"/>
-      <c r="D210" s="2" t="s">
+      <c r="E259" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="F259" s="3"/>
+    </row>
+    <row r="260" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A260" s="3"/>
+      <c r="B260" s="3"/>
+      <c r="C260" s="3"/>
+      <c r="D260" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E210" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="F210" s="9"/>
-    </row>
-    <row r="211" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="10"/>
-      <c r="B211" s="10"/>
-      <c r="C211" s="10"/>
-      <c r="D211" s="2" t="s">
+      <c r="E260" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="F260" s="3"/>
+    </row>
+    <row r="261" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A261" s="3"/>
+      <c r="B261" s="3"/>
+      <c r="C261" s="3"/>
+      <c r="D261" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E211" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="F211" s="10"/>
-    </row>
-    <row r="212" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="B212" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="C212" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="D212" s="2" t="s">
+      <c r="E261" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="F261" s="3"/>
+    </row>
+    <row r="262" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A262" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="D262" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E212" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F212" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="9"/>
-      <c r="B213" s="9"/>
-      <c r="C213" s="9"/>
-      <c r="D213" s="2" t="s">
+      <c r="E262" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="F262" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A263" s="3"/>
+      <c r="B263" s="3"/>
+      <c r="C263" s="3"/>
+      <c r="D263" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E213" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="F213" s="9"/>
-    </row>
-    <row r="214" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="9"/>
-      <c r="B214" s="9"/>
-      <c r="C214" s="9"/>
-      <c r="D214" s="2" t="s">
+      <c r="E263" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="F263" s="3"/>
+    </row>
+    <row r="264" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A264" s="3"/>
+      <c r="B264" s="3"/>
+      <c r="C264" s="3"/>
+      <c r="D264" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E214" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="F214" s="9"/>
-    </row>
-    <row r="215" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="9"/>
-      <c r="B215" s="9"/>
-      <c r="C215" s="9"/>
-      <c r="D215" s="2" t="s">
+      <c r="E264" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="F264" s="3"/>
+    </row>
+    <row r="265" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A265" s="3"/>
+      <c r="B265" s="3"/>
+      <c r="C265" s="3"/>
+      <c r="D265" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E215" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="F215" s="9"/>
-    </row>
-    <row r="216" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="10"/>
-      <c r="B216" s="10"/>
-      <c r="C216" s="10"/>
-      <c r="D216" s="2" t="s">
+      <c r="E265" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="F265" s="3"/>
+    </row>
+    <row r="266" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A266" s="3"/>
+      <c r="B266" s="3"/>
+      <c r="C266" s="3"/>
+      <c r="D266" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E216" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="F216" s="10"/>
-    </row>
-    <row r="217" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="B217" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="C217" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="D217" s="2" t="s">
+      <c r="E266" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="F266" s="3"/>
+    </row>
+    <row r="267" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A267" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D267" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E217" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="F217" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="9"/>
-      <c r="B218" s="9"/>
-      <c r="C218" s="9"/>
-      <c r="D218" s="2" t="s">
+      <c r="E267" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="F267" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A268" s="3"/>
+      <c r="B268" s="3"/>
+      <c r="C268" s="3"/>
+      <c r="D268" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E218" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F218" s="9"/>
-    </row>
-    <row r="219" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="9"/>
-      <c r="B219" s="9"/>
-      <c r="C219" s="9"/>
-      <c r="D219" s="2" t="s">
+      <c r="E268" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="F268" s="3"/>
+    </row>
+    <row r="269" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A269" s="3"/>
+      <c r="B269" s="3"/>
+      <c r="C269" s="3"/>
+      <c r="D269" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E219" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F219" s="9"/>
-    </row>
-    <row r="220" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="9"/>
-      <c r="B220" s="9"/>
-      <c r="C220" s="9"/>
-      <c r="D220" s="2" t="s">
+      <c r="E269" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="F269" s="3"/>
+    </row>
+    <row r="270" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A270" s="3"/>
+      <c r="B270" s="3"/>
+      <c r="C270" s="3"/>
+      <c r="D270" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E220" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="F220" s="9"/>
-    </row>
-    <row r="221" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A221" s="10"/>
-      <c r="B221" s="10"/>
-      <c r="C221" s="10"/>
-      <c r="D221" s="2" t="s">
+      <c r="E270" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="F270" s="3"/>
+    </row>
+    <row r="271" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A271" s="3"/>
+      <c r="B271" s="3"/>
+      <c r="C271" s="3"/>
+      <c r="D271" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E221" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="F221" s="10"/>
-    </row>
-    <row r="222" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="B222" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="C222" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="D222" s="2" t="s">
+      <c r="E271" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="F271" s="3"/>
+    </row>
+    <row r="272" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A272" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="D272" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E222" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="F222" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="9"/>
-      <c r="B223" s="9"/>
-      <c r="C223" s="9"/>
-      <c r="D223" s="2" t="s">
+      <c r="E272" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="F272" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A273" s="3"/>
+      <c r="B273" s="3"/>
+      <c r="C273" s="3"/>
+      <c r="D273" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E223" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="F223" s="9"/>
-    </row>
-    <row r="224" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="9"/>
-      <c r="B224" s="9"/>
-      <c r="C224" s="9"/>
-      <c r="D224" s="2" t="s">
+      <c r="E273" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="F273" s="3"/>
+    </row>
+    <row r="274" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A274" s="3"/>
+      <c r="B274" s="3"/>
+      <c r="C274" s="3"/>
+      <c r="D274" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E224" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F224" s="9"/>
-    </row>
-    <row r="225" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="9"/>
-      <c r="B225" s="9"/>
-      <c r="C225" s="9"/>
-      <c r="D225" s="2" t="s">
+      <c r="E274" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="F274" s="3"/>
+    </row>
+    <row r="275" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A275" s="3"/>
+      <c r="B275" s="3"/>
+      <c r="C275" s="3"/>
+      <c r="D275" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E225" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="F225" s="9"/>
-    </row>
-    <row r="226" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="10"/>
-      <c r="B226" s="10"/>
-      <c r="C226" s="10"/>
-      <c r="D226" s="2" t="s">
+      <c r="E275" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="F275" s="3"/>
+    </row>
+    <row r="276" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A276" s="3"/>
+      <c r="B276" s="3"/>
+      <c r="C276" s="3"/>
+      <c r="D276" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E226" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="F226" s="10"/>
-    </row>
-    <row r="227" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="B227" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="C227" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="D227" s="2" t="s">
+      <c r="E276" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="F276" s="3"/>
+    </row>
+    <row r="277" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A277" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C277" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D277" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E227" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="F227" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="9"/>
-      <c r="B228" s="9"/>
-      <c r="C228" s="9"/>
-      <c r="D228" s="2" t="s">
+      <c r="E277" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="F277" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A278" s="3"/>
+      <c r="B278" s="3"/>
+      <c r="C278" s="3"/>
+      <c r="D278" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E228" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="F228" s="9"/>
-    </row>
-    <row r="229" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="9"/>
-      <c r="B229" s="9"/>
-      <c r="C229" s="9"/>
-      <c r="D229" s="2" t="s">
+      <c r="E278" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="F278" s="3"/>
+    </row>
+    <row r="279" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A279" s="3"/>
+      <c r="B279" s="3"/>
+      <c r="C279" s="3"/>
+      <c r="D279" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E229" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="F229" s="9"/>
-    </row>
-    <row r="230" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="9"/>
-      <c r="B230" s="9"/>
-      <c r="C230" s="9"/>
-      <c r="D230" s="2" t="s">
+      <c r="E279" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="F279" s="3"/>
+    </row>
+    <row r="280" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A280" s="3"/>
+      <c r="B280" s="3"/>
+      <c r="C280" s="3"/>
+      <c r="D280" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E230" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="F230" s="9"/>
-    </row>
-    <row r="231" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="10"/>
-      <c r="B231" s="10"/>
-      <c r="C231" s="10"/>
-      <c r="D231" s="2" t="s">
+      <c r="E280" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="F280" s="3"/>
+    </row>
+    <row r="281" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A281" s="3"/>
+      <c r="B281" s="3"/>
+      <c r="C281" s="3"/>
+      <c r="D281" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E231" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="F231" s="10"/>
+      <c r="E281" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="F281" s="3"/>
+    </row>
+    <row r="282" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A282" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D282" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E282" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="F282" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A283" s="3"/>
+      <c r="B283" s="3"/>
+      <c r="C283" s="3"/>
+      <c r="D283" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E283" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="F283" s="3"/>
+    </row>
+    <row r="284" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A284" s="3"/>
+      <c r="B284" s="3"/>
+      <c r="C284" s="3"/>
+      <c r="D284" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E284" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="F284" s="3"/>
+    </row>
+    <row r="285" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A285" s="3"/>
+      <c r="B285" s="3"/>
+      <c r="C285" s="3"/>
+      <c r="D285" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E285" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="F285" s="3"/>
+    </row>
+    <row r="286" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A286" s="3"/>
+      <c r="B286" s="3"/>
+      <c r="C286" s="3"/>
+      <c r="D286" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E286" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="F286" s="3"/>
+    </row>
+    <row r="287" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A287" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B287" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="C287" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D287" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E287" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="F287" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A288" s="3"/>
+      <c r="B288" s="3"/>
+      <c r="C288" s="3"/>
+      <c r="D288" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E288" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="F288" s="3"/>
+    </row>
+    <row r="289" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A289" s="3"/>
+      <c r="B289" s="3"/>
+      <c r="C289" s="3"/>
+      <c r="D289" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E289" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="F289" s="3"/>
+    </row>
+    <row r="290" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A290" s="3"/>
+      <c r="B290" s="3"/>
+      <c r="C290" s="3"/>
+      <c r="D290" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E290" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="F290" s="3"/>
+    </row>
+    <row r="291" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A291" s="3"/>
+      <c r="B291" s="3"/>
+      <c r="C291" s="3"/>
+      <c r="D291" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E291" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="F291" s="3"/>
+    </row>
+    <row r="292" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A292" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="C292" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D292" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E292" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="F292" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A293" s="3"/>
+      <c r="B293" s="3"/>
+      <c r="C293" s="3"/>
+      <c r="D293" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E293" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F293" s="3"/>
+    </row>
+    <row r="294" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A294" s="3"/>
+      <c r="B294" s="3"/>
+      <c r="C294" s="3"/>
+      <c r="D294" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E294" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="F294" s="3"/>
+    </row>
+    <row r="295" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A295" s="3"/>
+      <c r="B295" s="3"/>
+      <c r="C295" s="3"/>
+      <c r="D295" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E295" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="F295" s="3"/>
+    </row>
+    <row r="296" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A296" s="3"/>
+      <c r="B296" s="3"/>
+      <c r="C296" s="3"/>
+      <c r="D296" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E296" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="F296" s="3"/>
+    </row>
+    <row r="297" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A297" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="B297" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C297" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="D297" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E297" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="F297" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A298" s="3"/>
+      <c r="B298" s="3"/>
+      <c r="C298" s="3"/>
+      <c r="D298" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E298" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="F298" s="3"/>
+    </row>
+    <row r="299" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A299" s="3"/>
+      <c r="B299" s="3"/>
+      <c r="C299" s="3"/>
+      <c r="D299" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E299" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="F299" s="3"/>
+    </row>
+    <row r="300" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A300" s="3"/>
+      <c r="B300" s="3"/>
+      <c r="C300" s="3"/>
+      <c r="D300" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E300" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="F300" s="3"/>
+    </row>
+    <row r="301" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A301" s="3"/>
+      <c r="B301" s="3"/>
+      <c r="C301" s="3"/>
+      <c r="D301" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E301" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="F301" s="3"/>
+    </row>
+    <row r="302" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A302" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="B302" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C302" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D302" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E302" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="F302" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A303" s="3"/>
+      <c r="B303" s="3"/>
+      <c r="C303" s="3"/>
+      <c r="D303" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E303" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="F303" s="3"/>
+    </row>
+    <row r="304" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A304" s="3"/>
+      <c r="B304" s="3"/>
+      <c r="C304" s="3"/>
+      <c r="D304" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E304" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="F304" s="3"/>
+    </row>
+    <row r="305" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A305" s="3"/>
+      <c r="B305" s="3"/>
+      <c r="C305" s="3"/>
+      <c r="D305" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E305" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="F305" s="3"/>
+    </row>
+    <row r="306" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A306" s="3"/>
+      <c r="B306" s="3"/>
+      <c r="C306" s="3"/>
+      <c r="D306" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E306" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="F306" s="3"/>
+    </row>
+    <row r="307" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A307" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="B307" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C307" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="D307" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E307" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="F307" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A308" s="3"/>
+      <c r="B308" s="3"/>
+      <c r="C308" s="3"/>
+      <c r="D308" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E308" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="F308" s="3"/>
+    </row>
+    <row r="309" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A309" s="3"/>
+      <c r="B309" s="3"/>
+      <c r="C309" s="3"/>
+      <c r="D309" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E309" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="F309" s="3"/>
+    </row>
+    <row r="310" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A310" s="3"/>
+      <c r="B310" s="3"/>
+      <c r="C310" s="3"/>
+      <c r="D310" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E310" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="F310" s="3"/>
+    </row>
+    <row r="311" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A311" s="3"/>
+      <c r="B311" s="3"/>
+      <c r="C311" s="3"/>
+      <c r="D311" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E311" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="F311" s="3"/>
+    </row>
+    <row r="312" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A312" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="B312" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C312" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="D312" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E312" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="F312" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A313" s="3"/>
+      <c r="B313" s="3"/>
+      <c r="C313" s="3"/>
+      <c r="D313" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E313" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="F313" s="3"/>
+    </row>
+    <row r="314" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A314" s="3"/>
+      <c r="B314" s="3"/>
+      <c r="C314" s="3"/>
+      <c r="D314" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E314" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="F314" s="3"/>
+    </row>
+    <row r="315" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A315" s="3"/>
+      <c r="B315" s="3"/>
+      <c r="C315" s="3"/>
+      <c r="D315" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E315" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="F315" s="3"/>
+    </row>
+    <row r="316" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A316" s="3"/>
+      <c r="B316" s="3"/>
+      <c r="C316" s="3"/>
+      <c r="D316" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E316" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="F316" s="3"/>
+    </row>
+    <row r="317" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A317" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="B317" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="C317" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="D317" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E317" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="F317" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A318" s="3"/>
+      <c r="B318" s="3"/>
+      <c r="C318" s="3"/>
+      <c r="D318" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E318" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="F318" s="3"/>
+    </row>
+    <row r="319" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A319" s="3"/>
+      <c r="B319" s="3"/>
+      <c r="C319" s="3"/>
+      <c r="D319" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E319" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="F319" s="3"/>
+    </row>
+    <row r="320" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A320" s="3"/>
+      <c r="B320" s="3"/>
+      <c r="C320" s="3"/>
+      <c r="D320" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E320" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="F320" s="3"/>
+    </row>
+    <row r="321" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A321" s="3"/>
+      <c r="B321" s="3"/>
+      <c r="C321" s="3"/>
+      <c r="D321" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E321" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="F321" s="3"/>
+    </row>
+    <row r="322" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A322" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="B322" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="C322" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="D322" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E322" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="F322" s="3" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A323" s="3"/>
+      <c r="B323" s="3"/>
+      <c r="C323" s="3"/>
+      <c r="D323" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E323" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="F323" s="3"/>
+    </row>
+    <row r="324" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A324" s="3"/>
+      <c r="B324" s="3"/>
+      <c r="C324" s="3"/>
+      <c r="D324" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E324" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="F324" s="3"/>
+    </row>
+    <row r="325" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A325" s="3"/>
+      <c r="B325" s="3"/>
+      <c r="C325" s="3"/>
+      <c r="D325" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E325" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="F325" s="3"/>
+    </row>
+    <row r="326" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A326" s="3"/>
+      <c r="B326" s="3"/>
+      <c r="C326" s="3"/>
+      <c r="D326" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E326" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="F326" s="3"/>
+    </row>
+    <row r="327" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A327" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="B327" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="C327" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="D327" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E327" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F327" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A328" s="3"/>
+      <c r="B328" s="3"/>
+      <c r="C328" s="3"/>
+      <c r="D328" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E328" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="F328" s="3"/>
+    </row>
+    <row r="329" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A329" s="3"/>
+      <c r="B329" s="3"/>
+      <c r="C329" s="3"/>
+      <c r="D329" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E329" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="F329" s="3"/>
+    </row>
+    <row r="330" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A330" s="3"/>
+      <c r="B330" s="3"/>
+      <c r="C330" s="3"/>
+      <c r="D330" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E330" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="F330" s="3"/>
+    </row>
+    <row r="331" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A331" s="3"/>
+      <c r="B331" s="3"/>
+      <c r="C331" s="3"/>
+      <c r="D331" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E331" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="F331" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="184">
-    <mergeCell ref="A167:A171"/>
-    <mergeCell ref="B137:B141"/>
-    <mergeCell ref="F77:F81"/>
-    <mergeCell ref="A32:A36"/>
-    <mergeCell ref="F27:F31"/>
-    <mergeCell ref="A97:A101"/>
-    <mergeCell ref="F67:F71"/>
-    <mergeCell ref="A152:A156"/>
-    <mergeCell ref="C32:C36"/>
-    <mergeCell ref="F117:F121"/>
-    <mergeCell ref="A77:A81"/>
-    <mergeCell ref="C77:C81"/>
-    <mergeCell ref="C87:C91"/>
-    <mergeCell ref="A67:A71"/>
-    <mergeCell ref="A132:A136"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A107:A111"/>
-    <mergeCell ref="A82:A86"/>
-    <mergeCell ref="C107:C111"/>
-    <mergeCell ref="F112:F116"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A42:A46"/>
-    <mergeCell ref="A72:A76"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C72:C76"/>
-    <mergeCell ref="A22:A26"/>
-    <mergeCell ref="A62:A66"/>
-    <mergeCell ref="A122:A126"/>
-    <mergeCell ref="F52:F56"/>
-    <mergeCell ref="C122:C126"/>
-    <mergeCell ref="A112:A116"/>
-    <mergeCell ref="F107:F111"/>
-    <mergeCell ref="F82:F86"/>
-    <mergeCell ref="C37:C41"/>
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="C47:C51"/>
-    <mergeCell ref="B42:B46"/>
-    <mergeCell ref="C22:C26"/>
-    <mergeCell ref="A37:A41"/>
-    <mergeCell ref="A12:A16"/>
-    <mergeCell ref="F2:F6"/>
-    <mergeCell ref="F17:F21"/>
-    <mergeCell ref="F47:F51"/>
-    <mergeCell ref="A7:A11"/>
-    <mergeCell ref="B27:B31"/>
-    <mergeCell ref="A172:A176"/>
-    <mergeCell ref="C172:C176"/>
-    <mergeCell ref="A162:A166"/>
-    <mergeCell ref="C147:C151"/>
-    <mergeCell ref="C162:C166"/>
-    <mergeCell ref="B77:B81"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="B117:B121"/>
-    <mergeCell ref="A137:A141"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="B112:B116"/>
-    <mergeCell ref="C27:C31"/>
-    <mergeCell ref="C132:C136"/>
-    <mergeCell ref="C67:C71"/>
-    <mergeCell ref="B22:B26"/>
-    <mergeCell ref="B102:B106"/>
-    <mergeCell ref="B152:B156"/>
-    <mergeCell ref="C127:C131"/>
-    <mergeCell ref="C117:C121"/>
-    <mergeCell ref="C52:C56"/>
-    <mergeCell ref="B87:B91"/>
-    <mergeCell ref="B127:B131"/>
-    <mergeCell ref="A147:A151"/>
-    <mergeCell ref="A157:A161"/>
-    <mergeCell ref="C157:C161"/>
-    <mergeCell ref="F167:F171"/>
-    <mergeCell ref="C82:C86"/>
-    <mergeCell ref="F57:F61"/>
-    <mergeCell ref="A127:A131"/>
-    <mergeCell ref="A102:A106"/>
-    <mergeCell ref="A117:A121"/>
-    <mergeCell ref="C102:C106"/>
-    <mergeCell ref="A142:A146"/>
-    <mergeCell ref="C62:C66"/>
-    <mergeCell ref="F157:F161"/>
-    <mergeCell ref="C92:C96"/>
-    <mergeCell ref="F72:F76"/>
-    <mergeCell ref="F62:F66"/>
-    <mergeCell ref="F122:F126"/>
-    <mergeCell ref="F127:F131"/>
-    <mergeCell ref="F142:F146"/>
-    <mergeCell ref="F97:F101"/>
-    <mergeCell ref="F132:F136"/>
-    <mergeCell ref="C167:C171"/>
-    <mergeCell ref="B82:B86"/>
-    <mergeCell ref="B147:B151"/>
-    <mergeCell ref="A52:A56"/>
-    <mergeCell ref="B142:B146"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="B72:B76"/>
-    <mergeCell ref="B62:B66"/>
-    <mergeCell ref="B122:B126"/>
-    <mergeCell ref="F87:F91"/>
-    <mergeCell ref="B32:B36"/>
-    <mergeCell ref="C42:C46"/>
-    <mergeCell ref="F7:F11"/>
-    <mergeCell ref="B97:B101"/>
-    <mergeCell ref="A92:A96"/>
-    <mergeCell ref="F137:F141"/>
-    <mergeCell ref="C97:C101"/>
-    <mergeCell ref="C137:C141"/>
-    <mergeCell ref="B52:B56"/>
-    <mergeCell ref="B67:B71"/>
-    <mergeCell ref="A87:A91"/>
-    <mergeCell ref="B132:B136"/>
-    <mergeCell ref="B107:B111"/>
-    <mergeCell ref="A57:A61"/>
-    <mergeCell ref="F102:F106"/>
-    <mergeCell ref="C57:C61"/>
-    <mergeCell ref="B92:B96"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="B167:B171"/>
-    <mergeCell ref="F12:F16"/>
-    <mergeCell ref="C142:C146"/>
-    <mergeCell ref="B17:B21"/>
-    <mergeCell ref="B57:B61"/>
-    <mergeCell ref="C112:C116"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="B172:B176"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="F92:F96"/>
-    <mergeCell ref="F152:F156"/>
-    <mergeCell ref="F172:F176"/>
-    <mergeCell ref="F147:F151"/>
-    <mergeCell ref="F162:F166"/>
-    <mergeCell ref="C152:C156"/>
-    <mergeCell ref="B157:B161"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="F42:F46"/>
-    <mergeCell ref="F37:F41"/>
-    <mergeCell ref="F32:F36"/>
-    <mergeCell ref="B37:B41"/>
-    <mergeCell ref="F22:F26"/>
-    <mergeCell ref="B162:B166"/>
-    <mergeCell ref="F177:F181"/>
-    <mergeCell ref="C177:C181"/>
-    <mergeCell ref="B177:B181"/>
-    <mergeCell ref="A177:A181"/>
+  <mergeCells count="264">
+    <mergeCell ref="A317:A321"/>
+    <mergeCell ref="B317:B321"/>
+    <mergeCell ref="C317:C321"/>
+    <mergeCell ref="F317:F321"/>
+    <mergeCell ref="A322:A326"/>
+    <mergeCell ref="B322:B326"/>
+    <mergeCell ref="C322:C326"/>
+    <mergeCell ref="F322:F326"/>
+    <mergeCell ref="A327:A331"/>
+    <mergeCell ref="B327:B331"/>
+    <mergeCell ref="C327:C331"/>
+    <mergeCell ref="F327:F331"/>
+    <mergeCell ref="A302:A306"/>
+    <mergeCell ref="B302:B306"/>
+    <mergeCell ref="C302:C306"/>
+    <mergeCell ref="F302:F306"/>
+    <mergeCell ref="A307:A311"/>
+    <mergeCell ref="B307:B311"/>
+    <mergeCell ref="C307:C311"/>
+    <mergeCell ref="F307:F311"/>
+    <mergeCell ref="A312:A316"/>
+    <mergeCell ref="B312:B316"/>
+    <mergeCell ref="C312:C316"/>
+    <mergeCell ref="F312:F316"/>
+    <mergeCell ref="A287:A291"/>
+    <mergeCell ref="B287:B291"/>
+    <mergeCell ref="C287:C291"/>
+    <mergeCell ref="F287:F291"/>
+    <mergeCell ref="A292:A296"/>
+    <mergeCell ref="B292:B296"/>
+    <mergeCell ref="C292:C296"/>
+    <mergeCell ref="F292:F296"/>
+    <mergeCell ref="A297:A301"/>
+    <mergeCell ref="B297:B301"/>
+    <mergeCell ref="C297:C301"/>
+    <mergeCell ref="F297:F301"/>
+    <mergeCell ref="A272:A276"/>
+    <mergeCell ref="B272:B276"/>
+    <mergeCell ref="C272:C276"/>
+    <mergeCell ref="F272:F276"/>
+    <mergeCell ref="A277:A281"/>
+    <mergeCell ref="B277:B281"/>
+    <mergeCell ref="C277:C281"/>
+    <mergeCell ref="F277:F281"/>
+    <mergeCell ref="A282:A286"/>
+    <mergeCell ref="B282:B286"/>
+    <mergeCell ref="C282:C286"/>
+    <mergeCell ref="F282:F286"/>
+    <mergeCell ref="A257:A261"/>
+    <mergeCell ref="B257:B261"/>
+    <mergeCell ref="C257:C261"/>
+    <mergeCell ref="F257:F261"/>
+    <mergeCell ref="A262:A266"/>
+    <mergeCell ref="B262:B266"/>
+    <mergeCell ref="C262:C266"/>
+    <mergeCell ref="F262:F266"/>
+    <mergeCell ref="A267:A271"/>
+    <mergeCell ref="B267:B271"/>
+    <mergeCell ref="C267:C271"/>
+    <mergeCell ref="F267:F271"/>
+    <mergeCell ref="A242:A246"/>
+    <mergeCell ref="B242:B246"/>
+    <mergeCell ref="C242:C246"/>
+    <mergeCell ref="F242:F246"/>
+    <mergeCell ref="A247:A251"/>
+    <mergeCell ref="B247:B251"/>
+    <mergeCell ref="C247:C251"/>
+    <mergeCell ref="F247:F251"/>
+    <mergeCell ref="A252:A256"/>
+    <mergeCell ref="B252:B256"/>
+    <mergeCell ref="C252:C256"/>
+    <mergeCell ref="F252:F256"/>
+    <mergeCell ref="A227:A231"/>
+    <mergeCell ref="B227:B231"/>
+    <mergeCell ref="C227:C231"/>
+    <mergeCell ref="F227:F231"/>
+    <mergeCell ref="A232:A236"/>
+    <mergeCell ref="B232:B236"/>
+    <mergeCell ref="C232:C236"/>
+    <mergeCell ref="F232:F236"/>
+    <mergeCell ref="A237:A241"/>
+    <mergeCell ref="B237:B241"/>
+    <mergeCell ref="C237:C241"/>
+    <mergeCell ref="F237:F241"/>
+    <mergeCell ref="A212:A216"/>
+    <mergeCell ref="B212:B216"/>
+    <mergeCell ref="C212:C216"/>
+    <mergeCell ref="F212:F216"/>
+    <mergeCell ref="A217:A221"/>
+    <mergeCell ref="B217:B221"/>
+    <mergeCell ref="C217:C221"/>
+    <mergeCell ref="F217:F221"/>
+    <mergeCell ref="A222:A226"/>
+    <mergeCell ref="B222:B226"/>
+    <mergeCell ref="C222:C226"/>
+    <mergeCell ref="F222:F226"/>
+    <mergeCell ref="A197:A201"/>
+    <mergeCell ref="B197:B201"/>
+    <mergeCell ref="C197:C201"/>
+    <mergeCell ref="F197:F201"/>
+    <mergeCell ref="A202:A206"/>
+    <mergeCell ref="B202:B206"/>
+    <mergeCell ref="C202:C206"/>
+    <mergeCell ref="F202:F206"/>
+    <mergeCell ref="A207:A211"/>
+    <mergeCell ref="B207:B211"/>
+    <mergeCell ref="C207:C211"/>
+    <mergeCell ref="F207:F211"/>
     <mergeCell ref="A182:A186"/>
     <mergeCell ref="B182:B186"/>
     <mergeCell ref="C182:C186"/>
@@ -4960,36 +6757,152 @@
     <mergeCell ref="B192:B196"/>
     <mergeCell ref="C192:C196"/>
     <mergeCell ref="F192:F196"/>
-    <mergeCell ref="A197:A201"/>
-    <mergeCell ref="B197:B201"/>
-    <mergeCell ref="C197:C201"/>
-    <mergeCell ref="F197:F201"/>
-    <mergeCell ref="B202:B206"/>
-    <mergeCell ref="A202:A206"/>
-    <mergeCell ref="C202:C206"/>
-    <mergeCell ref="F202:F206"/>
-    <mergeCell ref="A222:A226"/>
-    <mergeCell ref="B222:B226"/>
-    <mergeCell ref="C222:C226"/>
-    <mergeCell ref="F222:F226"/>
-    <mergeCell ref="F227:F231"/>
-    <mergeCell ref="C227:C231"/>
-    <mergeCell ref="B227:B231"/>
-    <mergeCell ref="A227:A231"/>
-    <mergeCell ref="A207:A211"/>
-    <mergeCell ref="B207:B211"/>
-    <mergeCell ref="C207:C211"/>
-    <mergeCell ref="F207:F211"/>
-    <mergeCell ref="A212:A216"/>
-    <mergeCell ref="B212:B216"/>
-    <mergeCell ref="C212:C216"/>
-    <mergeCell ref="F212:F216"/>
-    <mergeCell ref="A217:A221"/>
-    <mergeCell ref="B217:B221"/>
-    <mergeCell ref="C217:C221"/>
-    <mergeCell ref="F217:F221"/>
+    <mergeCell ref="A167:A171"/>
+    <mergeCell ref="B167:B171"/>
+    <mergeCell ref="C167:C171"/>
+    <mergeCell ref="F167:F171"/>
+    <mergeCell ref="A172:A176"/>
+    <mergeCell ref="B172:B176"/>
+    <mergeCell ref="C172:C176"/>
+    <mergeCell ref="F172:F176"/>
+    <mergeCell ref="A177:A181"/>
+    <mergeCell ref="B177:B181"/>
+    <mergeCell ref="C177:C181"/>
+    <mergeCell ref="F177:F181"/>
+    <mergeCell ref="A152:A156"/>
+    <mergeCell ref="B152:B156"/>
+    <mergeCell ref="C152:C156"/>
+    <mergeCell ref="F152:F156"/>
+    <mergeCell ref="A157:A161"/>
+    <mergeCell ref="B157:B161"/>
+    <mergeCell ref="C157:C161"/>
+    <mergeCell ref="F157:F161"/>
+    <mergeCell ref="A162:A166"/>
+    <mergeCell ref="B162:B166"/>
+    <mergeCell ref="C162:C166"/>
+    <mergeCell ref="F162:F166"/>
+    <mergeCell ref="A137:A141"/>
+    <mergeCell ref="B137:B141"/>
+    <mergeCell ref="C137:C141"/>
+    <mergeCell ref="F137:F141"/>
+    <mergeCell ref="A142:A146"/>
+    <mergeCell ref="B142:B146"/>
+    <mergeCell ref="C142:C146"/>
+    <mergeCell ref="F142:F146"/>
+    <mergeCell ref="A147:A151"/>
+    <mergeCell ref="B147:B151"/>
+    <mergeCell ref="C147:C151"/>
+    <mergeCell ref="F147:F151"/>
+    <mergeCell ref="A122:A126"/>
+    <mergeCell ref="B122:B126"/>
+    <mergeCell ref="C122:C126"/>
+    <mergeCell ref="F122:F126"/>
+    <mergeCell ref="A127:A131"/>
+    <mergeCell ref="B127:B131"/>
+    <mergeCell ref="C127:C131"/>
+    <mergeCell ref="F127:F131"/>
+    <mergeCell ref="A132:A136"/>
+    <mergeCell ref="B132:B136"/>
+    <mergeCell ref="C132:C136"/>
+    <mergeCell ref="F132:F136"/>
+    <mergeCell ref="A107:A111"/>
+    <mergeCell ref="B107:B111"/>
+    <mergeCell ref="C107:C111"/>
+    <mergeCell ref="F107:F111"/>
+    <mergeCell ref="A112:A116"/>
+    <mergeCell ref="B112:B116"/>
+    <mergeCell ref="C112:C116"/>
+    <mergeCell ref="F112:F116"/>
+    <mergeCell ref="A117:A121"/>
+    <mergeCell ref="B117:B121"/>
+    <mergeCell ref="C117:C121"/>
+    <mergeCell ref="F117:F121"/>
+    <mergeCell ref="A92:A96"/>
+    <mergeCell ref="B92:B96"/>
+    <mergeCell ref="C92:C96"/>
+    <mergeCell ref="F92:F96"/>
+    <mergeCell ref="A97:A101"/>
+    <mergeCell ref="B97:B101"/>
+    <mergeCell ref="C97:C101"/>
+    <mergeCell ref="F97:F101"/>
+    <mergeCell ref="A102:A106"/>
+    <mergeCell ref="B102:B106"/>
+    <mergeCell ref="C102:C106"/>
+    <mergeCell ref="F102:F106"/>
+    <mergeCell ref="A77:A81"/>
+    <mergeCell ref="B77:B81"/>
+    <mergeCell ref="C77:C81"/>
+    <mergeCell ref="F77:F81"/>
+    <mergeCell ref="A82:A86"/>
+    <mergeCell ref="B82:B86"/>
+    <mergeCell ref="C82:C86"/>
+    <mergeCell ref="F82:F86"/>
+    <mergeCell ref="A87:A91"/>
+    <mergeCell ref="B87:B91"/>
+    <mergeCell ref="C87:C91"/>
+    <mergeCell ref="F87:F91"/>
+    <mergeCell ref="A62:A66"/>
+    <mergeCell ref="B62:B66"/>
+    <mergeCell ref="C62:C66"/>
+    <mergeCell ref="F62:F66"/>
+    <mergeCell ref="A67:A71"/>
+    <mergeCell ref="B67:B71"/>
+    <mergeCell ref="C67:C71"/>
+    <mergeCell ref="F67:F71"/>
+    <mergeCell ref="A72:A76"/>
+    <mergeCell ref="B72:B76"/>
+    <mergeCell ref="C72:C76"/>
+    <mergeCell ref="F72:F76"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="C47:C51"/>
+    <mergeCell ref="F47:F51"/>
+    <mergeCell ref="A52:A56"/>
+    <mergeCell ref="B52:B56"/>
+    <mergeCell ref="C52:C56"/>
+    <mergeCell ref="F52:F56"/>
+    <mergeCell ref="A57:A61"/>
+    <mergeCell ref="B57:B61"/>
+    <mergeCell ref="C57:C61"/>
+    <mergeCell ref="F57:F61"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="C32:C36"/>
+    <mergeCell ref="F32:F36"/>
+    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="B37:B41"/>
+    <mergeCell ref="C37:C41"/>
+    <mergeCell ref="F37:F41"/>
+    <mergeCell ref="A42:A46"/>
+    <mergeCell ref="B42:B46"/>
+    <mergeCell ref="C42:C46"/>
+    <mergeCell ref="F42:F46"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="F17:F21"/>
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="B22:B26"/>
+    <mergeCell ref="C22:C26"/>
+    <mergeCell ref="F22:F26"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="C27:C31"/>
+    <mergeCell ref="F27:F31"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="F2:F6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="F7:F11"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="F12:F16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/sofood/ABSTRACT.xlsx
+++ b/sofood/ABSTRACT.xlsx
@@ -2036,6 +2036,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2043,9 +2046,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2347,13 +2347,13 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8">
+      <c r="A2" s="9">
         <v>19010004</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -2362,66 +2362,66 @@
       <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
       <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="8"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
       <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="8"/>
+      <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="8"/>
+      <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
       <c r="D6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="8"/>
+      <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="4" t="s">
@@ -2430,66 +2430,66 @@
       <c r="E7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
       <c r="D8" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="9"/>
+      <c r="F8" s="10"/>
     </row>
     <row r="9" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
       <c r="D9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="9"/>
+      <c r="F9" s="10"/>
     </row>
     <row r="10" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
       <c r="D10" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="9"/>
+      <c r="F10" s="10"/>
     </row>
     <row r="11" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
       <c r="D11" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="9"/>
+      <c r="F11" s="10"/>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="2" t="s">
@@ -2498,66 +2498,66 @@
       <c r="E12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="98.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
       <c r="D13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="8"/>
+      <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
       <c r="D14" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="8"/>
+      <c r="F14" s="9"/>
     </row>
     <row r="15" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
       <c r="D15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="8"/>
+      <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
       <c r="D16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="8"/>
+      <c r="F16" s="9"/>
     </row>
     <row r="17" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="4" t="s">
@@ -2566,66 +2566,66 @@
       <c r="E17" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
       <c r="D18" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="9"/>
+      <c r="F18" s="10"/>
     </row>
     <row r="19" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
       <c r="D19" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F19" s="9"/>
+      <c r="F19" s="10"/>
     </row>
     <row r="20" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
       <c r="D20" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="9"/>
+      <c r="F20" s="10"/>
     </row>
     <row r="21" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
       <c r="D21" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="9"/>
+      <c r="F21" s="10"/>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="9" t="s">
         <v>40</v>
       </c>
       <c r="D22" s="2" t="s">
@@ -2634,66 +2634,66 @@
       <c r="E22" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
       <c r="D23" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="8"/>
+      <c r="F23" s="9"/>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
       <c r="D24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="8"/>
+      <c r="F24" s="9"/>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
       <c r="D25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F25" s="8"/>
+      <c r="F25" s="9"/>
     </row>
     <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
       <c r="D26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F26" s="8"/>
+      <c r="F26" s="9"/>
     </row>
     <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="9" t="s">
         <v>48</v>
       </c>
       <c r="D27" s="2" t="s">
@@ -2702,66 +2702,66 @@
       <c r="E27" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
       <c r="D28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F28" s="8"/>
+      <c r="F28" s="9"/>
     </row>
     <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
       <c r="D29" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="8"/>
+      <c r="F29" s="9"/>
     </row>
     <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
       <c r="D30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F30" s="8"/>
+      <c r="F30" s="9"/>
     </row>
     <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
       <c r="D31" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F31" s="8"/>
+      <c r="F31" s="9"/>
     </row>
     <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D32" s="4" t="s">
@@ -2770,66 +2770,66 @@
       <c r="E32" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
       <c r="D33" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="9"/>
+      <c r="F33" s="10"/>
     </row>
     <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
       <c r="D34" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="9"/>
+      <c r="F34" s="10"/>
     </row>
     <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
       <c r="D35" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F35" s="9"/>
+      <c r="F35" s="10"/>
     </row>
     <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
       <c r="D36" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F36" s="9"/>
+      <c r="F36" s="10"/>
     </row>
     <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="9" t="s">
         <v>64</v>
       </c>
       <c r="D37" s="2" t="s">
@@ -2838,66 +2838,66 @@
       <c r="E37" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="F37" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
       <c r="D38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F38" s="8"/>
+      <c r="F38" s="9"/>
     </row>
     <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
+      <c r="A39" s="9"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
       <c r="D39" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F39" s="8"/>
+      <c r="F39" s="9"/>
     </row>
     <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
+      <c r="A40" s="9"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
       <c r="D40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F40" s="8"/>
+      <c r="F40" s="9"/>
     </row>
     <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
       <c r="D41" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F41" s="8"/>
+      <c r="F41" s="9"/>
     </row>
     <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="10" t="s">
         <v>72</v>
       </c>
       <c r="D42" s="4" t="s">
@@ -2906,66 +2906,66 @@
       <c r="E42" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F42" s="9" t="s">
+      <c r="F42" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
+      <c r="A43" s="10"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
       <c r="D43" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="9"/>
+      <c r="F43" s="10"/>
     </row>
     <row r="44" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
+      <c r="A44" s="10"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
       <c r="D44" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F44" s="9"/>
+      <c r="F44" s="10"/>
     </row>
     <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
+      <c r="A45" s="10"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
       <c r="D45" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F45" s="9"/>
+      <c r="F45" s="10"/>
     </row>
     <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
+      <c r="A46" s="10"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
       <c r="D46" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F46" s="9"/>
+      <c r="F46" s="10"/>
     </row>
     <row r="47" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="9" t="s">
         <v>80</v>
       </c>
       <c r="D47" s="2" t="s">
@@ -2974,66 +2974,66 @@
       <c r="E47" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F47" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
+      <c r="A48" s="9"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
       <c r="D48" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F48" s="8"/>
+      <c r="F48" s="9"/>
     </row>
     <row r="49" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
+      <c r="A49" s="9"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
       <c r="D49" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F49" s="8"/>
+      <c r="F49" s="9"/>
     </row>
     <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="8"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
+      <c r="A50" s="9"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
       <c r="D50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F50" s="8"/>
+      <c r="F50" s="9"/>
     </row>
     <row r="51" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
+      <c r="A51" s="9"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
       <c r="D51" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F51" s="8"/>
+      <c r="F51" s="9"/>
     </row>
     <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="9" t="s">
+      <c r="A52" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="10" t="s">
         <v>88</v>
       </c>
       <c r="D52" s="4" t="s">
@@ -3042,66 +3042,66 @@
       <c r="E52" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="F52" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="9"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
+      <c r="A53" s="10"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="10"/>
       <c r="D53" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F53" s="9"/>
+      <c r="F53" s="10"/>
     </row>
     <row r="54" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="9"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
+      <c r="A54" s="10"/>
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
       <c r="D54" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="F54" s="9"/>
+      <c r="F54" s="10"/>
     </row>
     <row r="55" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="9"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
+      <c r="A55" s="10"/>
+      <c r="B55" s="10"/>
+      <c r="C55" s="10"/>
       <c r="D55" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="F55" s="9"/>
+      <c r="F55" s="10"/>
     </row>
     <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="9"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
+      <c r="A56" s="10"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="10"/>
       <c r="D56" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E56" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="F56" s="9"/>
+      <c r="F56" s="10"/>
     </row>
     <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="9" t="s">
         <v>96</v>
       </c>
       <c r="D57" s="2" t="s">
@@ -3110,66 +3110,66 @@
       <c r="E57" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F57" s="8" t="s">
+      <c r="F57" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="8"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
+      <c r="A58" s="9"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
       <c r="D58" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="F58" s="8"/>
+      <c r="F58" s="9"/>
     </row>
     <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="8"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
+      <c r="A59" s="9"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
       <c r="D59" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="F59" s="8"/>
+      <c r="F59" s="9"/>
     </row>
     <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="8"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
+      <c r="A60" s="9"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
       <c r="D60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F60" s="8"/>
+      <c r="F60" s="9"/>
     </row>
     <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="8"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
+      <c r="A61" s="9"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
       <c r="D61" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F61" s="8"/>
+      <c r="F61" s="9"/>
     </row>
     <row r="62" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="9" t="s">
+      <c r="A62" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="C62" s="9" t="s">
+      <c r="C62" s="10" t="s">
         <v>104</v>
       </c>
       <c r="D62" s="4" t="s">
@@ -3178,66 +3178,66 @@
       <c r="E62" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="F62" s="9" t="s">
+      <c r="F62" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="9"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
+      <c r="A63" s="10"/>
+      <c r="B63" s="10"/>
+      <c r="C63" s="10"/>
       <c r="D63" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F63" s="9"/>
+      <c r="F63" s="10"/>
     </row>
     <row r="64" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="9"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
+      <c r="A64" s="10"/>
+      <c r="B64" s="10"/>
+      <c r="C64" s="10"/>
       <c r="D64" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E64" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F64" s="9"/>
+      <c r="F64" s="10"/>
     </row>
     <row r="65" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="9"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
+      <c r="A65" s="10"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="10"/>
       <c r="D65" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F65" s="9"/>
+      <c r="F65" s="10"/>
     </row>
     <row r="66" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="9"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
+      <c r="A66" s="10"/>
+      <c r="B66" s="10"/>
+      <c r="C66" s="10"/>
       <c r="D66" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="F66" s="9"/>
+      <c r="F66" s="10"/>
     </row>
     <row r="67" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="9" t="s">
         <v>112</v>
       </c>
       <c r="D67" s="2" t="s">
@@ -3246,66 +3246,66 @@
       <c r="E67" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="F67" s="8" t="s">
+      <c r="F67" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="8"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
+      <c r="A68" s="9"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
       <c r="D68" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F68" s="8"/>
+      <c r="F68" s="9"/>
     </row>
     <row r="69" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="8"/>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
+      <c r="A69" s="9"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
       <c r="D69" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F69" s="8"/>
+      <c r="F69" s="9"/>
     </row>
     <row r="70" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="8"/>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
+      <c r="A70" s="9"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
       <c r="D70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="F70" s="8"/>
+      <c r="F70" s="9"/>
     </row>
     <row r="71" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="8"/>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
+      <c r="A71" s="9"/>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
       <c r="D71" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F71" s="8"/>
+      <c r="F71" s="9"/>
     </row>
     <row r="72" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="9" t="s">
+      <c r="A72" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="C72" s="10" t="s">
         <v>120</v>
       </c>
       <c r="D72" s="4" t="s">
@@ -3314,66 +3314,66 @@
       <c r="E72" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F72" s="9" t="s">
+      <c r="F72" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="9"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
+      <c r="A73" s="10"/>
+      <c r="B73" s="10"/>
+      <c r="C73" s="10"/>
       <c r="D73" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="F73" s="9"/>
+      <c r="F73" s="10"/>
     </row>
     <row r="74" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="9"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
+      <c r="A74" s="10"/>
+      <c r="B74" s="10"/>
+      <c r="C74" s="10"/>
       <c r="D74" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="F74" s="9"/>
+      <c r="F74" s="10"/>
     </row>
     <row r="75" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="9"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
+      <c r="A75" s="10"/>
+      <c r="B75" s="10"/>
+      <c r="C75" s="10"/>
       <c r="D75" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F75" s="9"/>
+      <c r="F75" s="10"/>
     </row>
     <row r="76" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="9"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
+      <c r="A76" s="10"/>
+      <c r="B76" s="10"/>
+      <c r="C76" s="10"/>
       <c r="D76" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="F76" s="9"/>
+      <c r="F76" s="10"/>
     </row>
     <row r="77" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" s="9" t="s">
         <v>128</v>
       </c>
       <c r="D77" s="2" t="s">
@@ -3382,66 +3382,66 @@
       <c r="E77" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F77" s="8" t="s">
+      <c r="F77" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="8"/>
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
+      <c r="A78" s="9"/>
+      <c r="B78" s="9"/>
+      <c r="C78" s="9"/>
       <c r="D78" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="F78" s="8"/>
+      <c r="F78" s="9"/>
     </row>
     <row r="79" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="8"/>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
+      <c r="A79" s="9"/>
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
       <c r="D79" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="F79" s="8"/>
+      <c r="F79" s="9"/>
     </row>
     <row r="80" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="8"/>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
+      <c r="A80" s="9"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
       <c r="D80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F80" s="8"/>
+      <c r="F80" s="9"/>
     </row>
     <row r="81" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="8"/>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
+      <c r="A81" s="9"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
       <c r="D81" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="F81" s="8"/>
+      <c r="F81" s="9"/>
     </row>
     <row r="82" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="9" t="s">
+      <c r="A82" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="B82" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="C82" s="9" t="s">
+      <c r="C82" s="10" t="s">
         <v>136</v>
       </c>
       <c r="D82" s="4" t="s">
@@ -3450,64 +3450,64 @@
       <c r="E82" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F82" s="9" t="s">
+      <c r="F82" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="9"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
+      <c r="A83" s="10"/>
+      <c r="B83" s="10"/>
+      <c r="C83" s="10"/>
       <c r="D83" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E83" s="5"/>
-      <c r="F83" s="9"/>
+      <c r="F83" s="10"/>
     </row>
     <row r="84" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="9"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
+      <c r="A84" s="10"/>
+      <c r="B84" s="10"/>
+      <c r="C84" s="10"/>
       <c r="D84" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="F84" s="9"/>
+      <c r="F84" s="10"/>
     </row>
     <row r="85" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="9"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="9"/>
+      <c r="A85" s="10"/>
+      <c r="B85" s="10"/>
+      <c r="C85" s="10"/>
       <c r="D85" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="F85" s="9"/>
+      <c r="F85" s="10"/>
     </row>
     <row r="86" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="9"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="9"/>
+      <c r="A86" s="10"/>
+      <c r="B86" s="10"/>
+      <c r="C86" s="10"/>
       <c r="D86" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E86" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="F86" s="9"/>
+      <c r="F86" s="10"/>
     </row>
     <row r="87" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="8" t="s">
+      <c r="A87" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="C87" s="9" t="s">
         <v>143</v>
       </c>
       <c r="D87" s="2" t="s">
@@ -3516,66 +3516,66 @@
       <c r="E87" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F87" s="8" t="s">
+      <c r="F87" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="8"/>
-      <c r="B88" s="8"/>
-      <c r="C88" s="8"/>
+      <c r="A88" s="9"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="9"/>
       <c r="D88" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="F88" s="8"/>
+      <c r="F88" s="9"/>
     </row>
     <row r="89" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="8"/>
-      <c r="B89" s="8"/>
-      <c r="C89" s="8"/>
+      <c r="A89" s="9"/>
+      <c r="B89" s="9"/>
+      <c r="C89" s="9"/>
       <c r="D89" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F89" s="8"/>
+      <c r="F89" s="9"/>
     </row>
     <row r="90" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="8"/>
-      <c r="B90" s="8"/>
-      <c r="C90" s="8"/>
+      <c r="A90" s="9"/>
+      <c r="B90" s="9"/>
+      <c r="C90" s="9"/>
       <c r="D90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F90" s="8"/>
+      <c r="F90" s="9"/>
     </row>
     <row r="91" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="8"/>
-      <c r="B91" s="8"/>
-      <c r="C91" s="8"/>
+      <c r="A91" s="9"/>
+      <c r="B91" s="9"/>
+      <c r="C91" s="9"/>
       <c r="D91" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F91" s="8"/>
+      <c r="F91" s="9"/>
     </row>
     <row r="92" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="9" t="s">
+      <c r="A92" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="B92" s="9" t="s">
+      <c r="B92" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C92" s="9" t="s">
+      <c r="C92" s="10" t="s">
         <v>151</v>
       </c>
       <c r="D92" s="4" t="s">
@@ -3584,66 +3584,66 @@
       <c r="E92" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="F92" s="9" t="s">
+      <c r="F92" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="9"/>
-      <c r="B93" s="9"/>
-      <c r="C93" s="9"/>
+      <c r="A93" s="10"/>
+      <c r="B93" s="10"/>
+      <c r="C93" s="10"/>
       <c r="D93" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E93" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F93" s="9"/>
+      <c r="F93" s="10"/>
     </row>
     <row r="94" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="9"/>
-      <c r="B94" s="9"/>
-      <c r="C94" s="9"/>
+      <c r="A94" s="10"/>
+      <c r="B94" s="10"/>
+      <c r="C94" s="10"/>
       <c r="D94" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E94" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="F94" s="9"/>
+      <c r="F94" s="10"/>
     </row>
     <row r="95" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="9"/>
-      <c r="B95" s="9"/>
-      <c r="C95" s="9"/>
+      <c r="A95" s="10"/>
+      <c r="B95" s="10"/>
+      <c r="C95" s="10"/>
       <c r="D95" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="F95" s="9"/>
+      <c r="F95" s="10"/>
     </row>
     <row r="96" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="9"/>
-      <c r="B96" s="9"/>
-      <c r="C96" s="9"/>
+      <c r="A96" s="10"/>
+      <c r="B96" s="10"/>
+      <c r="C96" s="10"/>
       <c r="D96" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E96" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="F96" s="9"/>
+      <c r="F96" s="10"/>
     </row>
     <row r="97" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B97" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="C97" s="8" t="s">
+      <c r="C97" s="9" t="s">
         <v>159</v>
       </c>
       <c r="D97" s="2" t="s">
@@ -3652,66 +3652,66 @@
       <c r="E97" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F97" s="8" t="s">
+      <c r="F97" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="8"/>
-      <c r="B98" s="8"/>
-      <c r="C98" s="8"/>
+      <c r="A98" s="9"/>
+      <c r="B98" s="9"/>
+      <c r="C98" s="9"/>
       <c r="D98" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="F98" s="8"/>
+      <c r="F98" s="9"/>
     </row>
     <row r="99" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="8"/>
-      <c r="B99" s="8"/>
-      <c r="C99" s="8"/>
+      <c r="A99" s="9"/>
+      <c r="B99" s="9"/>
+      <c r="C99" s="9"/>
       <c r="D99" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="F99" s="8"/>
+      <c r="F99" s="9"/>
     </row>
     <row r="100" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="8"/>
-      <c r="B100" s="8"/>
-      <c r="C100" s="8"/>
+      <c r="A100" s="9"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="9"/>
       <c r="D100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="F100" s="8"/>
+      <c r="F100" s="9"/>
     </row>
     <row r="101" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="8"/>
-      <c r="B101" s="8"/>
-      <c r="C101" s="8"/>
+      <c r="A101" s="9"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
       <c r="D101" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F101" s="8"/>
+      <c r="F101" s="9"/>
     </row>
     <row r="102" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="9" t="s">
+      <c r="A102" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="B102" s="9" t="s">
+      <c r="B102" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="C102" s="9" t="s">
+      <c r="C102" s="10" t="s">
         <v>167</v>
       </c>
       <c r="D102" s="4" t="s">
@@ -3720,66 +3720,66 @@
       <c r="E102" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="F102" s="9" t="s">
+      <c r="F102" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="9"/>
-      <c r="B103" s="9"/>
-      <c r="C103" s="9"/>
+      <c r="A103" s="10"/>
+      <c r="B103" s="10"/>
+      <c r="C103" s="10"/>
       <c r="D103" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E103" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="F103" s="9"/>
+      <c r="F103" s="10"/>
     </row>
     <row r="104" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="9"/>
-      <c r="B104" s="9"/>
-      <c r="C104" s="9"/>
+      <c r="A104" s="10"/>
+      <c r="B104" s="10"/>
+      <c r="C104" s="10"/>
       <c r="D104" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="F104" s="9"/>
+      <c r="F104" s="10"/>
     </row>
     <row r="105" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="9"/>
-      <c r="B105" s="9"/>
-      <c r="C105" s="9"/>
+      <c r="A105" s="10"/>
+      <c r="B105" s="10"/>
+      <c r="C105" s="10"/>
       <c r="D105" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E105" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="F105" s="9"/>
+      <c r="F105" s="10"/>
     </row>
     <row r="106" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="9"/>
-      <c r="B106" s="9"/>
-      <c r="C106" s="9"/>
+      <c r="A106" s="10"/>
+      <c r="B106" s="10"/>
+      <c r="C106" s="10"/>
       <c r="D106" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E106" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F106" s="9"/>
+      <c r="F106" s="10"/>
     </row>
     <row r="107" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="8" t="s">
+      <c r="A107" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B107" s="8" t="s">
+      <c r="B107" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="C107" s="8" t="s">
+      <c r="C107" s="9" t="s">
         <v>175</v>
       </c>
       <c r="D107" s="2" t="s">
@@ -3788,66 +3788,66 @@
       <c r="E107" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="F107" s="8" t="s">
+      <c r="F107" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="8"/>
-      <c r="B108" s="8"/>
-      <c r="C108" s="8"/>
+      <c r="A108" s="9"/>
+      <c r="B108" s="9"/>
+      <c r="C108" s="9"/>
       <c r="D108" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="F108" s="8"/>
+      <c r="F108" s="9"/>
     </row>
     <row r="109" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="8"/>
-      <c r="B109" s="8"/>
-      <c r="C109" s="8"/>
+      <c r="A109" s="9"/>
+      <c r="B109" s="9"/>
+      <c r="C109" s="9"/>
       <c r="D109" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="F109" s="8"/>
+      <c r="F109" s="9"/>
     </row>
     <row r="110" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="8"/>
-      <c r="B110" s="8"/>
-      <c r="C110" s="8"/>
+      <c r="A110" s="9"/>
+      <c r="B110" s="9"/>
+      <c r="C110" s="9"/>
       <c r="D110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="F110" s="8"/>
+      <c r="F110" s="9"/>
     </row>
     <row r="111" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="8"/>
-      <c r="B111" s="8"/>
-      <c r="C111" s="8"/>
+      <c r="A111" s="9"/>
+      <c r="B111" s="9"/>
+      <c r="C111" s="9"/>
       <c r="D111" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="F111" s="8"/>
+      <c r="F111" s="9"/>
     </row>
     <row r="112" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="9" t="s">
+      <c r="A112" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="B112" s="9" t="s">
+      <c r="B112" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="C112" s="9" t="s">
+      <c r="C112" s="10" t="s">
         <v>183</v>
       </c>
       <c r="D112" s="4" t="s">
@@ -3856,66 +3856,66 @@
       <c r="E112" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="F112" s="9" t="s">
+      <c r="F112" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="9"/>
-      <c r="B113" s="9"/>
-      <c r="C113" s="9"/>
+      <c r="A113" s="10"/>
+      <c r="B113" s="10"/>
+      <c r="C113" s="10"/>
       <c r="D113" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="F113" s="9"/>
+      <c r="F113" s="10"/>
     </row>
     <row r="114" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="9"/>
-      <c r="B114" s="9"/>
-      <c r="C114" s="9"/>
+      <c r="A114" s="10"/>
+      <c r="B114" s="10"/>
+      <c r="C114" s="10"/>
       <c r="D114" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E114" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="F114" s="9"/>
+      <c r="F114" s="10"/>
     </row>
     <row r="115" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="9"/>
-      <c r="B115" s="9"/>
-      <c r="C115" s="9"/>
+      <c r="A115" s="10"/>
+      <c r="B115" s="10"/>
+      <c r="C115" s="10"/>
       <c r="D115" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E115" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="F115" s="9"/>
+      <c r="F115" s="10"/>
     </row>
     <row r="116" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="9"/>
-      <c r="B116" s="9"/>
-      <c r="C116" s="9"/>
+      <c r="A116" s="10"/>
+      <c r="B116" s="10"/>
+      <c r="C116" s="10"/>
       <c r="D116" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E116" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="F116" s="9"/>
+      <c r="F116" s="10"/>
     </row>
     <row r="117" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="8" t="s">
+      <c r="A117" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="B117" s="8" t="s">
+      <c r="B117" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="C117" s="8" t="s">
+      <c r="C117" s="9" t="s">
         <v>191</v>
       </c>
       <c r="D117" s="2" t="s">
@@ -3924,66 +3924,66 @@
       <c r="E117" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F117" s="8" t="s">
+      <c r="F117" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="8"/>
-      <c r="B118" s="8"/>
-      <c r="C118" s="8"/>
+      <c r="A118" s="9"/>
+      <c r="B118" s="9"/>
+      <c r="C118" s="9"/>
       <c r="D118" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="F118" s="8"/>
+      <c r="F118" s="9"/>
     </row>
     <row r="119" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="8"/>
-      <c r="B119" s="8"/>
-      <c r="C119" s="8"/>
+      <c r="A119" s="9"/>
+      <c r="B119" s="9"/>
+      <c r="C119" s="9"/>
       <c r="D119" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F119" s="8"/>
+      <c r="F119" s="9"/>
     </row>
     <row r="120" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="8"/>
-      <c r="B120" s="8"/>
-      <c r="C120" s="8"/>
+      <c r="A120" s="9"/>
+      <c r="B120" s="9"/>
+      <c r="C120" s="9"/>
       <c r="D120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F120" s="8"/>
+      <c r="F120" s="9"/>
     </row>
     <row r="121" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="8"/>
-      <c r="B121" s="8"/>
-      <c r="C121" s="8"/>
+      <c r="A121" s="9"/>
+      <c r="B121" s="9"/>
+      <c r="C121" s="9"/>
       <c r="D121" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="F121" s="8"/>
+      <c r="F121" s="9"/>
     </row>
     <row r="122" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="9" t="s">
+      <c r="A122" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="B122" s="9" t="s">
+      <c r="B122" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="C122" s="9" t="s">
+      <c r="C122" s="10" t="s">
         <v>199</v>
       </c>
       <c r="D122" s="4" t="s">
@@ -3992,66 +3992,66 @@
       <c r="E122" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="F122" s="9" t="s">
+      <c r="F122" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="9"/>
-      <c r="B123" s="9"/>
-      <c r="C123" s="9"/>
+      <c r="A123" s="10"/>
+      <c r="B123" s="10"/>
+      <c r="C123" s="10"/>
       <c r="D123" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="F123" s="9"/>
+      <c r="F123" s="10"/>
     </row>
     <row r="124" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="9"/>
-      <c r="B124" s="9"/>
-      <c r="C124" s="9"/>
+      <c r="A124" s="10"/>
+      <c r="B124" s="10"/>
+      <c r="C124" s="10"/>
       <c r="D124" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="F124" s="9"/>
+      <c r="F124" s="10"/>
     </row>
     <row r="125" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="9"/>
-      <c r="B125" s="9"/>
-      <c r="C125" s="9"/>
+      <c r="A125" s="10"/>
+      <c r="B125" s="10"/>
+      <c r="C125" s="10"/>
       <c r="D125" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E125" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="F125" s="9"/>
+      <c r="F125" s="10"/>
     </row>
     <row r="126" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="9"/>
-      <c r="B126" s="9"/>
-      <c r="C126" s="9"/>
+      <c r="A126" s="10"/>
+      <c r="B126" s="10"/>
+      <c r="C126" s="10"/>
       <c r="D126" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E126" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="F126" s="9"/>
+      <c r="F126" s="10"/>
     </row>
     <row r="127" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="8" t="s">
+      <c r="A127" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="B127" s="8" t="s">
+      <c r="B127" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="C127" s="8" t="s">
+      <c r="C127" s="9" t="s">
         <v>207</v>
       </c>
       <c r="D127" s="2" t="s">
@@ -4060,66 +4060,66 @@
       <c r="E127" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F127" s="8" t="s">
+      <c r="F127" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="8"/>
-      <c r="B128" s="8"/>
-      <c r="C128" s="8"/>
+      <c r="A128" s="9"/>
+      <c r="B128" s="9"/>
+      <c r="C128" s="9"/>
       <c r="D128" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="F128" s="8"/>
+      <c r="F128" s="9"/>
     </row>
     <row r="129" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="8"/>
-      <c r="B129" s="8"/>
-      <c r="C129" s="8"/>
+      <c r="A129" s="9"/>
+      <c r="B129" s="9"/>
+      <c r="C129" s="9"/>
       <c r="D129" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F129" s="8"/>
+      <c r="F129" s="9"/>
     </row>
     <row r="130" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="8"/>
-      <c r="B130" s="8"/>
-      <c r="C130" s="8"/>
+      <c r="A130" s="9"/>
+      <c r="B130" s="9"/>
+      <c r="C130" s="9"/>
       <c r="D130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="F130" s="8"/>
+      <c r="F130" s="9"/>
     </row>
     <row r="131" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="8"/>
-      <c r="B131" s="8"/>
-      <c r="C131" s="8"/>
+      <c r="A131" s="9"/>
+      <c r="B131" s="9"/>
+      <c r="C131" s="9"/>
       <c r="D131" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="F131" s="8"/>
+      <c r="F131" s="9"/>
     </row>
     <row r="132" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="9" t="s">
+      <c r="A132" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="B132" s="9" t="s">
+      <c r="B132" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="C132" s="9" t="s">
+      <c r="C132" s="10" t="s">
         <v>215</v>
       </c>
       <c r="D132" s="4" t="s">
@@ -4128,66 +4128,66 @@
       <c r="E132" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="F132" s="9" t="s">
+      <c r="F132" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="9"/>
-      <c r="B133" s="9"/>
-      <c r="C133" s="9"/>
+      <c r="A133" s="10"/>
+      <c r="B133" s="10"/>
+      <c r="C133" s="10"/>
       <c r="D133" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E133" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="F133" s="9"/>
+      <c r="F133" s="10"/>
     </row>
     <row r="134" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="9"/>
-      <c r="B134" s="9"/>
-      <c r="C134" s="9"/>
+      <c r="A134" s="10"/>
+      <c r="B134" s="10"/>
+      <c r="C134" s="10"/>
       <c r="D134" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E134" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="F134" s="9"/>
+      <c r="F134" s="10"/>
     </row>
     <row r="135" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="9"/>
-      <c r="B135" s="9"/>
-      <c r="C135" s="9"/>
+      <c r="A135" s="10"/>
+      <c r="B135" s="10"/>
+      <c r="C135" s="10"/>
       <c r="D135" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E135" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="F135" s="9"/>
+      <c r="F135" s="10"/>
     </row>
     <row r="136" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="9"/>
-      <c r="B136" s="9"/>
-      <c r="C136" s="9"/>
+      <c r="A136" s="10"/>
+      <c r="B136" s="10"/>
+      <c r="C136" s="10"/>
       <c r="D136" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="F136" s="9"/>
+      <c r="F136" s="10"/>
     </row>
     <row r="137" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="8" t="s">
+      <c r="A137" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="B137" s="8" t="s">
+      <c r="B137" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C137" s="8" t="s">
+      <c r="C137" s="9" t="s">
         <v>222</v>
       </c>
       <c r="D137" s="2" t="s">
@@ -4196,66 +4196,66 @@
       <c r="E137" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F137" s="8" t="s">
+      <c r="F137" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="8"/>
-      <c r="B138" s="8"/>
-      <c r="C138" s="8"/>
+      <c r="A138" s="9"/>
+      <c r="B138" s="9"/>
+      <c r="C138" s="9"/>
       <c r="D138" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F138" s="8"/>
+      <c r="F138" s="9"/>
     </row>
     <row r="139" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="8"/>
-      <c r="B139" s="8"/>
-      <c r="C139" s="8"/>
+      <c r="A139" s="9"/>
+      <c r="B139" s="9"/>
+      <c r="C139" s="9"/>
       <c r="D139" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F139" s="8"/>
+      <c r="F139" s="9"/>
     </row>
     <row r="140" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="8"/>
-      <c r="B140" s="8"/>
-      <c r="C140" s="8"/>
+      <c r="A140" s="9"/>
+      <c r="B140" s="9"/>
+      <c r="C140" s="9"/>
       <c r="D140" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F140" s="8"/>
+      <c r="F140" s="9"/>
     </row>
     <row r="141" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="8"/>
-      <c r="B141" s="8"/>
-      <c r="C141" s="8"/>
+      <c r="A141" s="9"/>
+      <c r="B141" s="9"/>
+      <c r="C141" s="9"/>
       <c r="D141" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F141" s="8"/>
+      <c r="F141" s="9"/>
     </row>
     <row r="142" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="8" t="s">
+      <c r="A142" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="B142" s="8" t="s">
+      <c r="B142" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="C142" s="8" t="s">
+      <c r="C142" s="9" t="s">
         <v>225</v>
       </c>
       <c r="D142" s="2" t="s">
@@ -4264,66 +4264,66 @@
       <c r="E142" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="F142" s="8" t="s">
+      <c r="F142" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="8"/>
-      <c r="B143" s="8"/>
-      <c r="C143" s="8"/>
+      <c r="A143" s="9"/>
+      <c r="B143" s="9"/>
+      <c r="C143" s="9"/>
       <c r="D143" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="F143" s="8"/>
+      <c r="F143" s="9"/>
     </row>
     <row r="144" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="8"/>
-      <c r="B144" s="8"/>
-      <c r="C144" s="8"/>
+      <c r="A144" s="9"/>
+      <c r="B144" s="9"/>
+      <c r="C144" s="9"/>
       <c r="D144" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="F144" s="8"/>
+      <c r="F144" s="9"/>
     </row>
     <row r="145" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="8"/>
-      <c r="B145" s="8"/>
-      <c r="C145" s="8"/>
+      <c r="A145" s="9"/>
+      <c r="B145" s="9"/>
+      <c r="C145" s="9"/>
       <c r="D145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="F145" s="8"/>
+      <c r="F145" s="9"/>
     </row>
     <row r="146" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="8"/>
-      <c r="B146" s="8"/>
-      <c r="C146" s="8"/>
+      <c r="A146" s="9"/>
+      <c r="B146" s="9"/>
+      <c r="C146" s="9"/>
       <c r="D146" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="F146" s="8"/>
+      <c r="F146" s="9"/>
     </row>
     <row r="147" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="9" t="s">
+      <c r="A147" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B147" s="9" t="s">
+      <c r="B147" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="C147" s="9" t="s">
+      <c r="C147" s="10" t="s">
         <v>233</v>
       </c>
       <c r="D147" s="4" t="s">
@@ -4332,66 +4332,66 @@
       <c r="E147" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="F147" s="9" t="s">
+      <c r="F147" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="9"/>
-      <c r="B148" s="9"/>
-      <c r="C148" s="9"/>
+      <c r="A148" s="10"/>
+      <c r="B148" s="10"/>
+      <c r="C148" s="10"/>
       <c r="D148" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E148" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="F148" s="9"/>
+      <c r="F148" s="10"/>
     </row>
     <row r="149" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="9"/>
-      <c r="B149" s="9"/>
-      <c r="C149" s="9"/>
+      <c r="A149" s="10"/>
+      <c r="B149" s="10"/>
+      <c r="C149" s="10"/>
       <c r="D149" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="F149" s="9"/>
+      <c r="F149" s="10"/>
     </row>
     <row r="150" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="9"/>
-      <c r="B150" s="9"/>
-      <c r="C150" s="9"/>
+      <c r="A150" s="10"/>
+      <c r="B150" s="10"/>
+      <c r="C150" s="10"/>
       <c r="D150" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="F150" s="9"/>
+      <c r="F150" s="10"/>
     </row>
     <row r="151" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="9"/>
-      <c r="B151" s="9"/>
-      <c r="C151" s="9"/>
+      <c r="A151" s="10"/>
+      <c r="B151" s="10"/>
+      <c r="C151" s="10"/>
       <c r="D151" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E151" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="F151" s="9"/>
+      <c r="F151" s="10"/>
     </row>
     <row r="152" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="8" t="s">
+      <c r="A152" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="B152" s="8" t="s">
+      <c r="B152" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="C152" s="8" t="s">
+      <c r="C152" s="9" t="s">
         <v>241</v>
       </c>
       <c r="D152" s="2" t="s">
@@ -4400,66 +4400,66 @@
       <c r="E152" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="F152" s="8" t="s">
+      <c r="F152" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="8"/>
-      <c r="B153" s="8"/>
-      <c r="C153" s="8"/>
+      <c r="A153" s="9"/>
+      <c r="B153" s="9"/>
+      <c r="C153" s="9"/>
       <c r="D153" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="F153" s="8"/>
+      <c r="F153" s="9"/>
     </row>
     <row r="154" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="8"/>
-      <c r="B154" s="8"/>
-      <c r="C154" s="8"/>
+      <c r="A154" s="9"/>
+      <c r="B154" s="9"/>
+      <c r="C154" s="9"/>
       <c r="D154" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="F154" s="8"/>
+      <c r="F154" s="9"/>
     </row>
     <row r="155" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="8"/>
-      <c r="B155" s="8"/>
-      <c r="C155" s="8"/>
+      <c r="A155" s="9"/>
+      <c r="B155" s="9"/>
+      <c r="C155" s="9"/>
       <c r="D155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F155" s="8"/>
+      <c r="F155" s="9"/>
     </row>
     <row r="156" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="8"/>
-      <c r="B156" s="8"/>
-      <c r="C156" s="8"/>
+      <c r="A156" s="9"/>
+      <c r="B156" s="9"/>
+      <c r="C156" s="9"/>
       <c r="D156" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E156" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="F156" s="8"/>
+      <c r="F156" s="9"/>
     </row>
     <row r="157" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="9" t="s">
+      <c r="A157" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="B157" s="9" t="s">
+      <c r="B157" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="C157" s="9" t="s">
+      <c r="C157" s="10" t="s">
         <v>248</v>
       </c>
       <c r="D157" s="4" t="s">
@@ -4468,66 +4468,66 @@
       <c r="E157" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="F157" s="9" t="s">
+      <c r="F157" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="9"/>
-      <c r="B158" s="9"/>
-      <c r="C158" s="9"/>
+      <c r="A158" s="10"/>
+      <c r="B158" s="10"/>
+      <c r="C158" s="10"/>
       <c r="D158" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E158" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="F158" s="9"/>
+      <c r="F158" s="10"/>
     </row>
     <row r="159" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="9"/>
-      <c r="B159" s="9"/>
-      <c r="C159" s="9"/>
+      <c r="A159" s="10"/>
+      <c r="B159" s="10"/>
+      <c r="C159" s="10"/>
       <c r="D159" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E159" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="F159" s="9"/>
+      <c r="F159" s="10"/>
     </row>
     <row r="160" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="9"/>
-      <c r="B160" s="9"/>
-      <c r="C160" s="9"/>
+      <c r="A160" s="10"/>
+      <c r="B160" s="10"/>
+      <c r="C160" s="10"/>
       <c r="D160" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E160" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="F160" s="9"/>
+      <c r="F160" s="10"/>
     </row>
     <row r="161" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="9"/>
-      <c r="B161" s="9"/>
-      <c r="C161" s="9"/>
+      <c r="A161" s="10"/>
+      <c r="B161" s="10"/>
+      <c r="C161" s="10"/>
       <c r="D161" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E161" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="F161" s="9"/>
+      <c r="F161" s="10"/>
     </row>
     <row r="162" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="8" t="s">
+      <c r="A162" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="B162" s="8" t="s">
+      <c r="B162" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C162" s="8" t="s">
+      <c r="C162" s="9" t="s">
         <v>256</v>
       </c>
       <c r="D162" s="2" t="s">
@@ -4536,66 +4536,66 @@
       <c r="E162" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="F162" s="8" t="s">
+      <c r="F162" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="8"/>
-      <c r="B163" s="8"/>
-      <c r="C163" s="8"/>
+      <c r="A163" s="9"/>
+      <c r="B163" s="9"/>
+      <c r="C163" s="9"/>
       <c r="D163" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="F163" s="8"/>
+      <c r="F163" s="9"/>
     </row>
     <row r="164" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="8"/>
-      <c r="B164" s="8"/>
-      <c r="C164" s="8"/>
+      <c r="A164" s="9"/>
+      <c r="B164" s="9"/>
+      <c r="C164" s="9"/>
       <c r="D164" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="F164" s="8"/>
+      <c r="F164" s="9"/>
     </row>
     <row r="165" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="8"/>
-      <c r="B165" s="8"/>
-      <c r="C165" s="8"/>
+      <c r="A165" s="9"/>
+      <c r="B165" s="9"/>
+      <c r="C165" s="9"/>
       <c r="D165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="F165" s="8"/>
+      <c r="F165" s="9"/>
     </row>
     <row r="166" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="8"/>
-      <c r="B166" s="8"/>
-      <c r="C166" s="8"/>
+      <c r="A166" s="9"/>
+      <c r="B166" s="9"/>
+      <c r="C166" s="9"/>
       <c r="D166" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="F166" s="8"/>
+      <c r="F166" s="9"/>
     </row>
     <row r="167" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="9">
+      <c r="A167" s="10">
         <v>19010864</v>
       </c>
-      <c r="B167" s="9" t="s">
+      <c r="B167" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="C167" s="9" t="s">
+      <c r="C167" s="10" t="s">
         <v>263</v>
       </c>
       <c r="D167" s="4" t="s">
@@ -4604,66 +4604,66 @@
       <c r="E167" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="F167" s="9" t="s">
+      <c r="F167" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="9"/>
-      <c r="B168" s="9"/>
-      <c r="C168" s="9"/>
+      <c r="A168" s="10"/>
+      <c r="B168" s="10"/>
+      <c r="C168" s="10"/>
       <c r="D168" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="F168" s="9"/>
+      <c r="F168" s="10"/>
     </row>
     <row r="169" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="9"/>
-      <c r="B169" s="9"/>
-      <c r="C169" s="9"/>
+      <c r="A169" s="10"/>
+      <c r="B169" s="10"/>
+      <c r="C169" s="10"/>
       <c r="D169" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E169" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="F169" s="9"/>
+      <c r="F169" s="10"/>
     </row>
     <row r="170" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="9"/>
-      <c r="B170" s="9"/>
-      <c r="C170" s="9"/>
+      <c r="A170" s="10"/>
+      <c r="B170" s="10"/>
+      <c r="C170" s="10"/>
       <c r="D170" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E170" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="F170" s="9"/>
+      <c r="F170" s="10"/>
     </row>
     <row r="171" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="9"/>
-      <c r="B171" s="9"/>
-      <c r="C171" s="9"/>
+      <c r="A171" s="10"/>
+      <c r="B171" s="10"/>
+      <c r="C171" s="10"/>
       <c r="D171" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E171" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="F171" s="9"/>
+      <c r="F171" s="10"/>
     </row>
     <row r="172" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="10" t="s">
+      <c r="A172" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="B172" s="8" t="s">
+      <c r="B172" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="C172" s="8" t="s">
+      <c r="C172" s="9" t="s">
         <v>271</v>
       </c>
       <c r="D172" s="2" t="s">
@@ -4672,66 +4672,66 @@
       <c r="E172" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F172" s="8" t="s">
+      <c r="F172" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="10"/>
-      <c r="B173" s="10"/>
-      <c r="C173" s="10"/>
+      <c r="A173" s="11"/>
+      <c r="B173" s="11"/>
+      <c r="C173" s="11"/>
       <c r="D173" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E173" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="F173" s="8"/>
+      <c r="F173" s="9"/>
     </row>
     <row r="174" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="10"/>
-      <c r="B174" s="10"/>
-      <c r="C174" s="10"/>
+      <c r="A174" s="11"/>
+      <c r="B174" s="11"/>
+      <c r="C174" s="11"/>
       <c r="D174" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F174" s="8"/>
+      <c r="F174" s="9"/>
     </row>
     <row r="175" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="10"/>
-      <c r="B175" s="10"/>
-      <c r="C175" s="10"/>
+      <c r="A175" s="11"/>
+      <c r="B175" s="11"/>
+      <c r="C175" s="11"/>
       <c r="D175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="F175" s="8"/>
+      <c r="F175" s="9"/>
     </row>
     <row r="176" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="10"/>
-      <c r="B176" s="10"/>
-      <c r="C176" s="10"/>
+      <c r="A176" s="11"/>
+      <c r="B176" s="11"/>
+      <c r="C176" s="11"/>
       <c r="D176" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F176" s="8"/>
+      <c r="F176" s="9"/>
     </row>
     <row r="177" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="8" t="s">
+      <c r="A177" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="B177" s="8" t="s">
+      <c r="B177" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="C177" s="8" t="s">
+      <c r="C177" s="9" t="s">
         <v>279</v>
       </c>
       <c r="D177" s="2" t="s">
@@ -4740,66 +4740,66 @@
       <c r="E177" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F177" s="8" t="s">
+      <c r="F177" s="9" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="8"/>
-      <c r="B178" s="8"/>
-      <c r="C178" s="8"/>
+      <c r="A178" s="9"/>
+      <c r="B178" s="9"/>
+      <c r="C178" s="9"/>
       <c r="D178" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="F178" s="8"/>
+      <c r="F178" s="9"/>
     </row>
     <row r="179" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="8"/>
-      <c r="B179" s="8"/>
-      <c r="C179" s="8"/>
+      <c r="A179" s="9"/>
+      <c r="B179" s="9"/>
+      <c r="C179" s="9"/>
       <c r="D179" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="F179" s="8"/>
+      <c r="F179" s="9"/>
     </row>
     <row r="180" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="8"/>
-      <c r="B180" s="8"/>
-      <c r="C180" s="8"/>
+      <c r="A180" s="9"/>
+      <c r="B180" s="9"/>
+      <c r="C180" s="9"/>
       <c r="D180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E180" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="F180" s="8"/>
+      <c r="F180" s="9"/>
     </row>
     <row r="181" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="8"/>
-      <c r="B181" s="8"/>
-      <c r="C181" s="8"/>
+      <c r="A181" s="9"/>
+      <c r="B181" s="9"/>
+      <c r="C181" s="9"/>
       <c r="D181" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="F181" s="8"/>
+      <c r="F181" s="9"/>
     </row>
     <row r="182" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="8" t="s">
+      <c r="A182" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="B182" s="8" t="s">
+      <c r="B182" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="C182" s="8" t="s">
+      <c r="C182" s="9" t="s">
         <v>288</v>
       </c>
       <c r="D182" s="2" t="s">
@@ -4808,66 +4808,66 @@
       <c r="E182" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="F182" s="8" t="s">
+      <c r="F182" s="9" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="8"/>
-      <c r="B183" s="8"/>
-      <c r="C183" s="8"/>
+      <c r="A183" s="9"/>
+      <c r="B183" s="9"/>
+      <c r="C183" s="9"/>
       <c r="D183" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E183" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="F183" s="8"/>
+      <c r="F183" s="9"/>
     </row>
     <row r="184" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="8"/>
-      <c r="B184" s="8"/>
-      <c r="C184" s="8"/>
+      <c r="A184" s="9"/>
+      <c r="B184" s="9"/>
+      <c r="C184" s="9"/>
       <c r="D184" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E184" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="F184" s="8"/>
+      <c r="F184" s="9"/>
     </row>
     <row r="185" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="8"/>
-      <c r="B185" s="8"/>
-      <c r="C185" s="8"/>
+      <c r="A185" s="9"/>
+      <c r="B185" s="9"/>
+      <c r="C185" s="9"/>
       <c r="D185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="F185" s="8"/>
+      <c r="F185" s="9"/>
     </row>
     <row r="186" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="8"/>
-      <c r="B186" s="8"/>
-      <c r="C186" s="8"/>
+      <c r="A186" s="9"/>
+      <c r="B186" s="9"/>
+      <c r="C186" s="9"/>
       <c r="D186" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E186" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="F186" s="8"/>
+      <c r="F186" s="9"/>
     </row>
     <row r="187" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="8" t="s">
+      <c r="A187" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="B187" s="8" t="s">
+      <c r="B187" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="C187" s="8" t="s">
+      <c r="C187" s="9" t="s">
         <v>296</v>
       </c>
       <c r="D187" s="2" t="s">
@@ -4876,66 +4876,66 @@
       <c r="E187" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="F187" s="8" t="s">
+      <c r="F187" s="9" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="8"/>
-      <c r="B188" s="8"/>
-      <c r="C188" s="8"/>
+      <c r="A188" s="9"/>
+      <c r="B188" s="9"/>
+      <c r="C188" s="9"/>
       <c r="D188" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="F188" s="8"/>
+      <c r="F188" s="9"/>
     </row>
     <row r="189" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="8"/>
-      <c r="B189" s="8"/>
-      <c r="C189" s="8"/>
+      <c r="A189" s="9"/>
+      <c r="B189" s="9"/>
+      <c r="C189" s="9"/>
       <c r="D189" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="F189" s="8"/>
+      <c r="F189" s="9"/>
     </row>
     <row r="190" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="8"/>
-      <c r="B190" s="8"/>
-      <c r="C190" s="8"/>
+      <c r="A190" s="9"/>
+      <c r="B190" s="9"/>
+      <c r="C190" s="9"/>
       <c r="D190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E190" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="F190" s="8"/>
+      <c r="F190" s="9"/>
     </row>
     <row r="191" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="8"/>
-      <c r="B191" s="8"/>
-      <c r="C191" s="8"/>
+      <c r="A191" s="9"/>
+      <c r="B191" s="9"/>
+      <c r="C191" s="9"/>
       <c r="D191" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="F191" s="8"/>
+      <c r="F191" s="9"/>
     </row>
     <row r="192" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="8" t="s">
+      <c r="A192" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="B192" s="8" t="s">
+      <c r="B192" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="C192" s="8" t="s">
+      <c r="C192" s="9" t="s">
         <v>305</v>
       </c>
       <c r="D192" s="2" t="s">
@@ -4944,66 +4944,66 @@
       <c r="E192" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="F192" s="8" t="s">
+      <c r="F192" s="9" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="8"/>
-      <c r="B193" s="8"/>
-      <c r="C193" s="8"/>
+      <c r="A193" s="9"/>
+      <c r="B193" s="9"/>
+      <c r="C193" s="9"/>
       <c r="D193" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="F193" s="8"/>
+      <c r="F193" s="9"/>
     </row>
     <row r="194" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="8"/>
-      <c r="B194" s="8"/>
-      <c r="C194" s="8"/>
+      <c r="A194" s="9"/>
+      <c r="B194" s="9"/>
+      <c r="C194" s="9"/>
       <c r="D194" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E194" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="F194" s="8"/>
+      <c r="F194" s="9"/>
     </row>
     <row r="195" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="8"/>
-      <c r="B195" s="8"/>
-      <c r="C195" s="8"/>
+      <c r="A195" s="9"/>
+      <c r="B195" s="9"/>
+      <c r="C195" s="9"/>
       <c r="D195" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="F195" s="8"/>
+      <c r="F195" s="9"/>
     </row>
     <row r="196" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="8"/>
-      <c r="B196" s="8"/>
-      <c r="C196" s="8"/>
+      <c r="A196" s="9"/>
+      <c r="B196" s="9"/>
+      <c r="C196" s="9"/>
       <c r="D196" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="F196" s="8"/>
+      <c r="F196" s="9"/>
     </row>
     <row r="197" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="8" t="s">
+      <c r="A197" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="B197" s="8" t="s">
+      <c r="B197" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="C197" s="8" t="s">
+      <c r="C197" s="9" t="s">
         <v>313</v>
       </c>
       <c r="D197" s="2" t="s">
@@ -5012,66 +5012,66 @@
       <c r="E197" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="F197" s="8" t="s">
+      <c r="F197" s="9" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="198" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="8"/>
-      <c r="B198" s="8"/>
-      <c r="C198" s="8"/>
+      <c r="A198" s="9"/>
+      <c r="B198" s="9"/>
+      <c r="C198" s="9"/>
       <c r="D198" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="F198" s="8"/>
+      <c r="F198" s="9"/>
     </row>
     <row r="199" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="8"/>
-      <c r="B199" s="8"/>
-      <c r="C199" s="8"/>
+      <c r="A199" s="9"/>
+      <c r="B199" s="9"/>
+      <c r="C199" s="9"/>
       <c r="D199" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="F199" s="8"/>
+      <c r="F199" s="9"/>
     </row>
     <row r="200" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="8"/>
-      <c r="B200" s="8"/>
-      <c r="C200" s="8"/>
+      <c r="A200" s="9"/>
+      <c r="B200" s="9"/>
+      <c r="C200" s="9"/>
       <c r="D200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E200" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="F200" s="8"/>
+      <c r="F200" s="9"/>
     </row>
     <row r="201" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="8"/>
-      <c r="B201" s="8"/>
-      <c r="C201" s="8"/>
+      <c r="A201" s="9"/>
+      <c r="B201" s="9"/>
+      <c r="C201" s="9"/>
       <c r="D201" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="F201" s="8"/>
+      <c r="F201" s="9"/>
     </row>
     <row r="202" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="8" t="s">
+      <c r="A202" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="B202" s="8" t="s">
+      <c r="B202" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="C202" s="8" t="s">
+      <c r="C202" s="9" t="s">
         <v>321</v>
       </c>
       <c r="D202" s="2" t="s">
@@ -5080,66 +5080,66 @@
       <c r="E202" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="F202" s="8" t="s">
+      <c r="F202" s="9" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="203" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="8"/>
-      <c r="B203" s="8"/>
-      <c r="C203" s="8"/>
+      <c r="A203" s="9"/>
+      <c r="B203" s="9"/>
+      <c r="C203" s="9"/>
       <c r="D203" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="F203" s="8"/>
+      <c r="F203" s="9"/>
     </row>
     <row r="204" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="8"/>
-      <c r="B204" s="8"/>
-      <c r="C204" s="8"/>
+      <c r="A204" s="9"/>
+      <c r="B204" s="9"/>
+      <c r="C204" s="9"/>
       <c r="D204" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E204" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="F204" s="8"/>
+      <c r="F204" s="9"/>
     </row>
     <row r="205" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="8"/>
-      <c r="B205" s="8"/>
-      <c r="C205" s="8"/>
+      <c r="A205" s="9"/>
+      <c r="B205" s="9"/>
+      <c r="C205" s="9"/>
       <c r="D205" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E205" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="F205" s="8"/>
+      <c r="F205" s="9"/>
     </row>
     <row r="206" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="8"/>
-      <c r="B206" s="8"/>
-      <c r="C206" s="8"/>
+      <c r="A206" s="9"/>
+      <c r="B206" s="9"/>
+      <c r="C206" s="9"/>
       <c r="D206" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E206" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="F206" s="8"/>
+      <c r="F206" s="9"/>
     </row>
     <row r="207" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="8" t="s">
+      <c r="A207" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="B207" s="8" t="s">
+      <c r="B207" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="C207" s="8" t="s">
+      <c r="C207" s="9" t="s">
         <v>329</v>
       </c>
       <c r="D207" s="2" t="s">
@@ -5148,66 +5148,66 @@
       <c r="E207" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="F207" s="8" t="s">
+      <c r="F207" s="9" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="8"/>
-      <c r="B208" s="8"/>
-      <c r="C208" s="8"/>
+      <c r="A208" s="9"/>
+      <c r="B208" s="9"/>
+      <c r="C208" s="9"/>
       <c r="D208" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E208" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="F208" s="8"/>
+      <c r="F208" s="9"/>
     </row>
     <row r="209" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="8"/>
-      <c r="B209" s="8"/>
-      <c r="C209" s="8"/>
+      <c r="A209" s="9"/>
+      <c r="B209" s="9"/>
+      <c r="C209" s="9"/>
       <c r="D209" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E209" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="F209" s="8"/>
+      <c r="F209" s="9"/>
     </row>
     <row r="210" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="8"/>
-      <c r="B210" s="8"/>
-      <c r="C210" s="8"/>
+      <c r="A210" s="9"/>
+      <c r="B210" s="9"/>
+      <c r="C210" s="9"/>
       <c r="D210" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E210" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="F210" s="8"/>
+      <c r="F210" s="9"/>
     </row>
     <row r="211" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="8"/>
-      <c r="B211" s="8"/>
-      <c r="C211" s="8"/>
+      <c r="A211" s="9"/>
+      <c r="B211" s="9"/>
+      <c r="C211" s="9"/>
       <c r="D211" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E211" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="F211" s="8"/>
+      <c r="F211" s="9"/>
     </row>
     <row r="212" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="8" t="s">
+      <c r="A212" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="B212" s="8" t="s">
+      <c r="B212" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="C212" s="8" t="s">
+      <c r="C212" s="9" t="s">
         <v>337</v>
       </c>
       <c r="D212" s="2" t="s">
@@ -5216,66 +5216,66 @@
       <c r="E212" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="F212" s="8" t="s">
+      <c r="F212" s="9" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="213" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="8"/>
-      <c r="B213" s="8"/>
-      <c r="C213" s="8"/>
+      <c r="A213" s="9"/>
+      <c r="B213" s="9"/>
+      <c r="C213" s="9"/>
       <c r="D213" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E213" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="F213" s="8"/>
+      <c r="F213" s="9"/>
     </row>
     <row r="214" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="8"/>
-      <c r="B214" s="8"/>
-      <c r="C214" s="8"/>
+      <c r="A214" s="9"/>
+      <c r="B214" s="9"/>
+      <c r="C214" s="9"/>
       <c r="D214" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E214" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="F214" s="8"/>
+      <c r="F214" s="9"/>
     </row>
     <row r="215" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="8"/>
-      <c r="B215" s="8"/>
-      <c r="C215" s="8"/>
+      <c r="A215" s="9"/>
+      <c r="B215" s="9"/>
+      <c r="C215" s="9"/>
       <c r="D215" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E215" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="F215" s="8"/>
+      <c r="F215" s="9"/>
     </row>
     <row r="216" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="8"/>
-      <c r="B216" s="8"/>
-      <c r="C216" s="8"/>
+      <c r="A216" s="9"/>
+      <c r="B216" s="9"/>
+      <c r="C216" s="9"/>
       <c r="D216" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E216" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="F216" s="8"/>
+      <c r="F216" s="9"/>
     </row>
     <row r="217" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="8" t="s">
+      <c r="A217" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="B217" s="8" t="s">
+      <c r="B217" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="C217" s="8" t="s">
+      <c r="C217" s="9" t="s">
         <v>345</v>
       </c>
       <c r="D217" s="2" t="s">
@@ -5284,66 +5284,66 @@
       <c r="E217" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="F217" s="8" t="s">
+      <c r="F217" s="9" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="218" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="8"/>
-      <c r="B218" s="8"/>
-      <c r="C218" s="8"/>
+      <c r="A218" s="9"/>
+      <c r="B218" s="9"/>
+      <c r="C218" s="9"/>
       <c r="D218" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E218" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="F218" s="8"/>
+      <c r="F218" s="9"/>
     </row>
     <row r="219" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="8"/>
-      <c r="B219" s="8"/>
-      <c r="C219" s="8"/>
+      <c r="A219" s="9"/>
+      <c r="B219" s="9"/>
+      <c r="C219" s="9"/>
       <c r="D219" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E219" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="F219" s="8"/>
+      <c r="F219" s="9"/>
     </row>
     <row r="220" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="8"/>
-      <c r="B220" s="8"/>
-      <c r="C220" s="8"/>
+      <c r="A220" s="9"/>
+      <c r="B220" s="9"/>
+      <c r="C220" s="9"/>
       <c r="D220" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E220" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="F220" s="8"/>
+      <c r="F220" s="9"/>
     </row>
     <row r="221" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A221" s="8"/>
-      <c r="B221" s="8"/>
-      <c r="C221" s="8"/>
+      <c r="A221" s="9"/>
+      <c r="B221" s="9"/>
+      <c r="C221" s="9"/>
       <c r="D221" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E221" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="F221" s="8"/>
+      <c r="F221" s="9"/>
     </row>
     <row r="222" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="8" t="s">
+      <c r="A222" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="B222" s="8" t="s">
+      <c r="B222" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="C222" s="8" t="s">
+      <c r="C222" s="9" t="s">
         <v>353</v>
       </c>
       <c r="D222" s="2" t="s">
@@ -5352,66 +5352,66 @@
       <c r="E222" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="F222" s="8" t="s">
+      <c r="F222" s="9" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="223" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="8"/>
-      <c r="B223" s="8"/>
-      <c r="C223" s="8"/>
+      <c r="A223" s="9"/>
+      <c r="B223" s="9"/>
+      <c r="C223" s="9"/>
       <c r="D223" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E223" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="F223" s="8"/>
+      <c r="F223" s="9"/>
     </row>
     <row r="224" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="8"/>
-      <c r="B224" s="8"/>
-      <c r="C224" s="8"/>
+      <c r="A224" s="9"/>
+      <c r="B224" s="9"/>
+      <c r="C224" s="9"/>
       <c r="D224" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E224" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="F224" s="8"/>
+      <c r="F224" s="9"/>
     </row>
     <row r="225" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="8"/>
-      <c r="B225" s="8"/>
-      <c r="C225" s="8"/>
+      <c r="A225" s="9"/>
+      <c r="B225" s="9"/>
+      <c r="C225" s="9"/>
       <c r="D225" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E225" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="F225" s="8"/>
+      <c r="F225" s="9"/>
     </row>
     <row r="226" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="8"/>
-      <c r="B226" s="8"/>
-      <c r="C226" s="8"/>
+      <c r="A226" s="9"/>
+      <c r="B226" s="9"/>
+      <c r="C226" s="9"/>
       <c r="D226" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E226" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="F226" s="8"/>
+      <c r="F226" s="9"/>
     </row>
     <row r="227" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="8" t="s">
+      <c r="A227" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B227" s="8" t="s">
+      <c r="B227" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="C227" s="8" t="s">
+      <c r="C227" s="9" t="s">
         <v>361</v>
       </c>
       <c r="D227" s="2" t="s">
@@ -5420,66 +5420,66 @@
       <c r="E227" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="F227" s="8" t="s">
+      <c r="F227" s="9" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="228" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="8"/>
-      <c r="B228" s="8"/>
-      <c r="C228" s="8"/>
+      <c r="A228" s="9"/>
+      <c r="B228" s="9"/>
+      <c r="C228" s="9"/>
       <c r="D228" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E228" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="F228" s="8"/>
+      <c r="F228" s="9"/>
     </row>
     <row r="229" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="8"/>
-      <c r="B229" s="8"/>
-      <c r="C229" s="8"/>
+      <c r="A229" s="9"/>
+      <c r="B229" s="9"/>
+      <c r="C229" s="9"/>
       <c r="D229" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E229" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="F229" s="8"/>
+      <c r="F229" s="9"/>
     </row>
     <row r="230" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="8"/>
-      <c r="B230" s="8"/>
-      <c r="C230" s="8"/>
+      <c r="A230" s="9"/>
+      <c r="B230" s="9"/>
+      <c r="C230" s="9"/>
       <c r="D230" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E230" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="F230" s="8"/>
+      <c r="F230" s="9"/>
     </row>
     <row r="231" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="8"/>
-      <c r="B231" s="8"/>
-      <c r="C231" s="8"/>
+      <c r="A231" s="9"/>
+      <c r="B231" s="9"/>
+      <c r="C231" s="9"/>
       <c r="D231" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E231" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="F231" s="8"/>
+      <c r="F231" s="9"/>
     </row>
     <row r="232" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="8" t="s">
+      <c r="A232" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="B232" s="8" t="s">
+      <c r="B232" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="C232" s="8" t="s">
+      <c r="C232" s="9" t="s">
         <v>369</v>
       </c>
       <c r="D232" s="2" t="s">
@@ -5488,66 +5488,66 @@
       <c r="E232" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="F232" s="8" t="s">
+      <c r="F232" s="9" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="233" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="8"/>
-      <c r="B233" s="8"/>
-      <c r="C233" s="8"/>
+      <c r="A233" s="9"/>
+      <c r="B233" s="9"/>
+      <c r="C233" s="9"/>
       <c r="D233" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E233" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="F233" s="8"/>
+      <c r="F233" s="9"/>
     </row>
     <row r="234" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="8"/>
-      <c r="B234" s="8"/>
-      <c r="C234" s="8"/>
+      <c r="A234" s="9"/>
+      <c r="B234" s="9"/>
+      <c r="C234" s="9"/>
       <c r="D234" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E234" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="F234" s="8"/>
+      <c r="F234" s="9"/>
     </row>
     <row r="235" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="8"/>
-      <c r="B235" s="8"/>
-      <c r="C235" s="8"/>
+      <c r="A235" s="9"/>
+      <c r="B235" s="9"/>
+      <c r="C235" s="9"/>
       <c r="D235" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E235" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="F235" s="8"/>
+      <c r="F235" s="9"/>
     </row>
     <row r="236" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="8"/>
-      <c r="B236" s="8"/>
-      <c r="C236" s="8"/>
+      <c r="A236" s="9"/>
+      <c r="B236" s="9"/>
+      <c r="C236" s="9"/>
       <c r="D236" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E236" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="F236" s="8"/>
+      <c r="F236" s="9"/>
     </row>
     <row r="237" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="8" t="s">
+      <c r="A237" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="B237" s="8" t="s">
+      <c r="B237" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="C237" s="8" t="s">
+      <c r="C237" s="9" t="s">
         <v>378</v>
       </c>
       <c r="D237" s="2" t="s">
@@ -5556,66 +5556,66 @@
       <c r="E237" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="F237" s="8" t="s">
+      <c r="F237" s="9" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="238" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="8"/>
-      <c r="B238" s="8"/>
-      <c r="C238" s="8"/>
+      <c r="A238" s="9"/>
+      <c r="B238" s="9"/>
+      <c r="C238" s="9"/>
       <c r="D238" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E238" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="F238" s="8"/>
+      <c r="F238" s="9"/>
     </row>
     <row r="239" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="8"/>
-      <c r="B239" s="8"/>
-      <c r="C239" s="8"/>
+      <c r="A239" s="9"/>
+      <c r="B239" s="9"/>
+      <c r="C239" s="9"/>
       <c r="D239" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E239" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="F239" s="8"/>
+      <c r="F239" s="9"/>
     </row>
     <row r="240" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="8"/>
-      <c r="B240" s="8"/>
-      <c r="C240" s="8"/>
+      <c r="A240" s="9"/>
+      <c r="B240" s="9"/>
+      <c r="C240" s="9"/>
       <c r="D240" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E240" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="F240" s="8"/>
+      <c r="F240" s="9"/>
     </row>
     <row r="241" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="8"/>
-      <c r="B241" s="8"/>
-      <c r="C241" s="8"/>
+      <c r="A241" s="9"/>
+      <c r="B241" s="9"/>
+      <c r="C241" s="9"/>
       <c r="D241" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="F241" s="8"/>
+      <c r="F241" s="9"/>
     </row>
     <row r="242" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="8" t="s">
+      <c r="A242" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="B242" s="8" t="s">
+      <c r="B242" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="C242" s="8" t="s">
+      <c r="C242" s="9" t="s">
         <v>387</v>
       </c>
       <c r="D242" s="2" t="s">
@@ -5624,66 +5624,66 @@
       <c r="E242" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="F242" s="8" t="s">
+      <c r="F242" s="9" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="243" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="8"/>
-      <c r="B243" s="8"/>
-      <c r="C243" s="8"/>
+      <c r="A243" s="9"/>
+      <c r="B243" s="9"/>
+      <c r="C243" s="9"/>
       <c r="D243" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E243" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="F243" s="8"/>
+      <c r="F243" s="9"/>
     </row>
     <row r="244" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="8"/>
-      <c r="B244" s="8"/>
-      <c r="C244" s="8"/>
+      <c r="A244" s="9"/>
+      <c r="B244" s="9"/>
+      <c r="C244" s="9"/>
       <c r="D244" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E244" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="F244" s="8"/>
+      <c r="F244" s="9"/>
     </row>
     <row r="245" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="8"/>
-      <c r="B245" s="8"/>
-      <c r="C245" s="8"/>
+      <c r="A245" s="9"/>
+      <c r="B245" s="9"/>
+      <c r="C245" s="9"/>
       <c r="D245" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E245" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="F245" s="8"/>
+      <c r="F245" s="9"/>
     </row>
     <row r="246" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="8"/>
-      <c r="B246" s="8"/>
-      <c r="C246" s="8"/>
+      <c r="A246" s="9"/>
+      <c r="B246" s="9"/>
+      <c r="C246" s="9"/>
       <c r="D246" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E246" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="F246" s="8"/>
+      <c r="F246" s="9"/>
     </row>
     <row r="247" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="8" t="s">
+      <c r="A247" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="B247" s="8" t="s">
+      <c r="B247" s="9" t="s">
         <v>395</v>
       </c>
-      <c r="C247" s="8" t="s">
+      <c r="C247" s="9" t="s">
         <v>396</v>
       </c>
       <c r="D247" s="2" t="s">
@@ -5692,66 +5692,66 @@
       <c r="E247" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="F247" s="8" t="s">
+      <c r="F247" s="9" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="248" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="8"/>
-      <c r="B248" s="8"/>
-      <c r="C248" s="8"/>
+      <c r="A248" s="9"/>
+      <c r="B248" s="9"/>
+      <c r="C248" s="9"/>
       <c r="D248" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E248" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="F248" s="8"/>
+      <c r="F248" s="9"/>
     </row>
     <row r="249" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="8"/>
-      <c r="B249" s="8"/>
-      <c r="C249" s="8"/>
+      <c r="A249" s="9"/>
+      <c r="B249" s="9"/>
+      <c r="C249" s="9"/>
       <c r="D249" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E249" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="F249" s="8"/>
+      <c r="F249" s="9"/>
     </row>
     <row r="250" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="8"/>
-      <c r="B250" s="8"/>
-      <c r="C250" s="8"/>
+      <c r="A250" s="9"/>
+      <c r="B250" s="9"/>
+      <c r="C250" s="9"/>
       <c r="D250" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E250" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="F250" s="8"/>
+      <c r="F250" s="9"/>
     </row>
     <row r="251" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="8"/>
-      <c r="B251" s="8"/>
-      <c r="C251" s="8"/>
+      <c r="A251" s="9"/>
+      <c r="B251" s="9"/>
+      <c r="C251" s="9"/>
       <c r="D251" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E251" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="F251" s="8"/>
+      <c r="F251" s="9"/>
     </row>
     <row r="252" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A252" s="8" t="s">
+      <c r="A252" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="B252" s="8" t="s">
+      <c r="B252" s="9" t="s">
         <v>403</v>
       </c>
-      <c r="C252" s="8" t="s">
+      <c r="C252" s="9" t="s">
         <v>404</v>
       </c>
       <c r="D252" s="2" t="s">
@@ -5760,66 +5760,66 @@
       <c r="E252" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="F252" s="8" t="s">
+      <c r="F252" s="9" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="253" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A253" s="8"/>
-      <c r="B253" s="8"/>
-      <c r="C253" s="8"/>
+      <c r="A253" s="9"/>
+      <c r="B253" s="9"/>
+      <c r="C253" s="9"/>
       <c r="D253" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="F253" s="8"/>
+      <c r="F253" s="9"/>
     </row>
     <row r="254" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A254" s="8"/>
-      <c r="B254" s="8"/>
-      <c r="C254" s="8"/>
+      <c r="A254" s="9"/>
+      <c r="B254" s="9"/>
+      <c r="C254" s="9"/>
       <c r="D254" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E254" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="F254" s="8"/>
+      <c r="F254" s="9"/>
     </row>
     <row r="255" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A255" s="8"/>
-      <c r="B255" s="8"/>
-      <c r="C255" s="8"/>
+      <c r="A255" s="9"/>
+      <c r="B255" s="9"/>
+      <c r="C255" s="9"/>
       <c r="D255" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E255" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="F255" s="8"/>
+      <c r="F255" s="9"/>
     </row>
     <row r="256" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="8"/>
-      <c r="B256" s="8"/>
-      <c r="C256" s="8"/>
+      <c r="A256" s="9"/>
+      <c r="B256" s="9"/>
+      <c r="C256" s="9"/>
       <c r="D256" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E256" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="F256" s="8"/>
+      <c r="F256" s="9"/>
     </row>
     <row r="257" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="8" t="s">
+      <c r="A257" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="B257" s="8" t="s">
+      <c r="B257" s="9" t="s">
         <v>412</v>
       </c>
-      <c r="C257" s="8" t="s">
+      <c r="C257" s="9" t="s">
         <v>413</v>
       </c>
       <c r="D257" s="2" t="s">
@@ -5828,66 +5828,66 @@
       <c r="E257" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="F257" s="8" t="s">
+      <c r="F257" s="9" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="258" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="8"/>
-      <c r="B258" s="8"/>
-      <c r="C258" s="8"/>
+      <c r="A258" s="9"/>
+      <c r="B258" s="9"/>
+      <c r="C258" s="9"/>
       <c r="D258" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E258" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="F258" s="8"/>
+      <c r="F258" s="9"/>
     </row>
     <row r="259" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="8"/>
-      <c r="B259" s="8"/>
-      <c r="C259" s="8"/>
+      <c r="A259" s="9"/>
+      <c r="B259" s="9"/>
+      <c r="C259" s="9"/>
       <c r="D259" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E259" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="F259" s="8"/>
+      <c r="F259" s="9"/>
     </row>
     <row r="260" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A260" s="8"/>
-      <c r="B260" s="8"/>
-      <c r="C260" s="8"/>
+      <c r="A260" s="9"/>
+      <c r="B260" s="9"/>
+      <c r="C260" s="9"/>
       <c r="D260" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E260" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="F260" s="8"/>
+      <c r="F260" s="9"/>
     </row>
     <row r="261" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="8"/>
-      <c r="B261" s="8"/>
-      <c r="C261" s="8"/>
+      <c r="A261" s="9"/>
+      <c r="B261" s="9"/>
+      <c r="C261" s="9"/>
       <c r="D261" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E261" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="F261" s="8"/>
+      <c r="F261" s="9"/>
     </row>
     <row r="262" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A262" s="8" t="s">
+      <c r="A262" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="B262" s="8" t="s">
+      <c r="B262" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="C262" s="8" t="s">
+      <c r="C262" s="9" t="s">
         <v>421</v>
       </c>
       <c r="D262" s="2" t="s">
@@ -5896,66 +5896,66 @@
       <c r="E262" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="F262" s="8" t="s">
+      <c r="F262" s="9" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="263" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A263" s="8"/>
-      <c r="B263" s="8"/>
-      <c r="C263" s="8"/>
+      <c r="A263" s="9"/>
+      <c r="B263" s="9"/>
+      <c r="C263" s="9"/>
       <c r="D263" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="F263" s="8"/>
+      <c r="F263" s="9"/>
     </row>
     <row r="264" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A264" s="8"/>
-      <c r="B264" s="8"/>
-      <c r="C264" s="8"/>
+      <c r="A264" s="9"/>
+      <c r="B264" s="9"/>
+      <c r="C264" s="9"/>
       <c r="D264" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="F264" s="8"/>
+      <c r="F264" s="9"/>
     </row>
     <row r="265" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A265" s="8"/>
-      <c r="B265" s="8"/>
-      <c r="C265" s="8"/>
+      <c r="A265" s="9"/>
+      <c r="B265" s="9"/>
+      <c r="C265" s="9"/>
       <c r="D265" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="F265" s="8"/>
+      <c r="F265" s="9"/>
     </row>
     <row r="266" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A266" s="8"/>
-      <c r="B266" s="8"/>
-      <c r="C266" s="8"/>
+      <c r="A266" s="9"/>
+      <c r="B266" s="9"/>
+      <c r="C266" s="9"/>
       <c r="D266" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E266" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="F266" s="8"/>
+      <c r="F266" s="9"/>
     </row>
     <row r="267" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A267" s="8" t="s">
+      <c r="A267" s="9" t="s">
         <v>427</v>
       </c>
-      <c r="B267" s="8" t="s">
+      <c r="B267" s="9" t="s">
         <v>428</v>
       </c>
-      <c r="C267" s="8" t="s">
+      <c r="C267" s="9" t="s">
         <v>429</v>
       </c>
       <c r="D267" s="2" t="s">
@@ -5964,66 +5964,66 @@
       <c r="E267" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="F267" s="8" t="s">
+      <c r="F267" s="9" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="268" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A268" s="8"/>
-      <c r="B268" s="8"/>
-      <c r="C268" s="8"/>
+      <c r="A268" s="9"/>
+      <c r="B268" s="9"/>
+      <c r="C268" s="9"/>
       <c r="D268" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E268" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="F268" s="8"/>
+      <c r="F268" s="9"/>
     </row>
     <row r="269" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A269" s="8"/>
-      <c r="B269" s="8"/>
-      <c r="C269" s="8"/>
+      <c r="A269" s="9"/>
+      <c r="B269" s="9"/>
+      <c r="C269" s="9"/>
       <c r="D269" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E269" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="F269" s="8"/>
+      <c r="F269" s="9"/>
     </row>
     <row r="270" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A270" s="8"/>
-      <c r="B270" s="8"/>
-      <c r="C270" s="8"/>
+      <c r="A270" s="9"/>
+      <c r="B270" s="9"/>
+      <c r="C270" s="9"/>
       <c r="D270" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E270" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="F270" s="8"/>
+      <c r="F270" s="9"/>
     </row>
     <row r="271" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A271" s="8"/>
-      <c r="B271" s="8"/>
-      <c r="C271" s="8"/>
+      <c r="A271" s="9"/>
+      <c r="B271" s="9"/>
+      <c r="C271" s="9"/>
       <c r="D271" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E271" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="F271" s="8"/>
+      <c r="F271" s="9"/>
     </row>
     <row r="272" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A272" s="8" t="s">
+      <c r="A272" s="9" t="s">
         <v>435</v>
       </c>
-      <c r="B272" s="8" t="s">
+      <c r="B272" s="9" t="s">
         <v>436</v>
       </c>
-      <c r="C272" s="8" t="s">
+      <c r="C272" s="9" t="s">
         <v>437</v>
       </c>
       <c r="D272" s="2" t="s">
@@ -6032,66 +6032,66 @@
       <c r="E272" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="F272" s="8" t="s">
+      <c r="F272" s="9" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="273" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A273" s="8"/>
-      <c r="B273" s="8"/>
-      <c r="C273" s="8"/>
+      <c r="A273" s="9"/>
+      <c r="B273" s="9"/>
+      <c r="C273" s="9"/>
       <c r="D273" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E273" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="F273" s="8"/>
+      <c r="F273" s="9"/>
     </row>
     <row r="274" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A274" s="8"/>
-      <c r="B274" s="8"/>
-      <c r="C274" s="8"/>
+      <c r="A274" s="9"/>
+      <c r="B274" s="9"/>
+      <c r="C274" s="9"/>
       <c r="D274" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E274" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="F274" s="8"/>
+      <c r="F274" s="9"/>
     </row>
     <row r="275" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A275" s="8"/>
-      <c r="B275" s="8"/>
-      <c r="C275" s="8"/>
+      <c r="A275" s="9"/>
+      <c r="B275" s="9"/>
+      <c r="C275" s="9"/>
       <c r="D275" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E275" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="F275" s="8"/>
+      <c r="F275" s="9"/>
     </row>
     <row r="276" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A276" s="8"/>
-      <c r="B276" s="8"/>
-      <c r="C276" s="8"/>
+      <c r="A276" s="9"/>
+      <c r="B276" s="9"/>
+      <c r="C276" s="9"/>
       <c r="D276" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E276" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="F276" s="8"/>
+      <c r="F276" s="9"/>
     </row>
     <row r="277" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A277" s="8" t="s">
+      <c r="A277" s="9" t="s">
         <v>444</v>
       </c>
-      <c r="B277" s="8" t="s">
+      <c r="B277" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="C277" s="8" t="s">
+      <c r="C277" s="9" t="s">
         <v>446</v>
       </c>
       <c r="D277" s="2" t="s">
@@ -6100,66 +6100,66 @@
       <c r="E277" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F277" s="8" t="s">
+      <c r="F277" s="9" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="278" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A278" s="8"/>
-      <c r="B278" s="8"/>
-      <c r="C278" s="8"/>
+      <c r="A278" s="9"/>
+      <c r="B278" s="9"/>
+      <c r="C278" s="9"/>
       <c r="D278" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E278" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="F278" s="8"/>
+      <c r="F278" s="9"/>
     </row>
     <row r="279" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A279" s="8"/>
-      <c r="B279" s="8"/>
-      <c r="C279" s="8"/>
+      <c r="A279" s="9"/>
+      <c r="B279" s="9"/>
+      <c r="C279" s="9"/>
       <c r="D279" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E279" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="F279" s="8"/>
+      <c r="F279" s="9"/>
     </row>
     <row r="280" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A280" s="8"/>
-      <c r="B280" s="8"/>
-      <c r="C280" s="8"/>
+      <c r="A280" s="9"/>
+      <c r="B280" s="9"/>
+      <c r="C280" s="9"/>
       <c r="D280" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E280" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="F280" s="8"/>
+      <c r="F280" s="9"/>
     </row>
     <row r="281" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A281" s="8"/>
-      <c r="B281" s="8"/>
-      <c r="C281" s="8"/>
+      <c r="A281" s="9"/>
+      <c r="B281" s="9"/>
+      <c r="C281" s="9"/>
       <c r="D281" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E281" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="F281" s="8"/>
+      <c r="F281" s="9"/>
     </row>
     <row r="282" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A282" s="8" t="s">
+      <c r="A282" s="9" t="s">
         <v>452</v>
       </c>
-      <c r="B282" s="8" t="s">
+      <c r="B282" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="C282" s="8" t="s">
+      <c r="C282" s="9" t="s">
         <v>454</v>
       </c>
       <c r="D282" s="2" t="s">
@@ -6168,66 +6168,66 @@
       <c r="E282" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="F282" s="8" t="s">
+      <c r="F282" s="9" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="283" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A283" s="8"/>
-      <c r="B283" s="8"/>
-      <c r="C283" s="8"/>
+      <c r="A283" s="9"/>
+      <c r="B283" s="9"/>
+      <c r="C283" s="9"/>
       <c r="D283" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E283" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="F283" s="8"/>
+      <c r="F283" s="9"/>
     </row>
     <row r="284" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A284" s="8"/>
-      <c r="B284" s="8"/>
-      <c r="C284" s="8"/>
+      <c r="A284" s="9"/>
+      <c r="B284" s="9"/>
+      <c r="C284" s="9"/>
       <c r="D284" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E284" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="F284" s="8"/>
+      <c r="F284" s="9"/>
     </row>
     <row r="285" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A285" s="8"/>
-      <c r="B285" s="8"/>
-      <c r="C285" s="8"/>
+      <c r="A285" s="9"/>
+      <c r="B285" s="9"/>
+      <c r="C285" s="9"/>
       <c r="D285" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E285" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="F285" s="8"/>
+      <c r="F285" s="9"/>
     </row>
     <row r="286" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A286" s="8"/>
-      <c r="B286" s="8"/>
-      <c r="C286" s="8"/>
+      <c r="A286" s="9"/>
+      <c r="B286" s="9"/>
+      <c r="C286" s="9"/>
       <c r="D286" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E286" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="F286" s="8"/>
+      <c r="F286" s="9"/>
     </row>
     <row r="287" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A287" s="8" t="s">
+      <c r="A287" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="B287" s="8" t="s">
+      <c r="B287" s="9" t="s">
         <v>461</v>
       </c>
-      <c r="C287" s="8" t="s">
+      <c r="C287" s="9" t="s">
         <v>462</v>
       </c>
       <c r="D287" s="2" t="s">
@@ -6236,66 +6236,66 @@
       <c r="E287" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="F287" s="8" t="s">
+      <c r="F287" s="9" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="288" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A288" s="8"/>
-      <c r="B288" s="8"/>
-      <c r="C288" s="8"/>
+      <c r="A288" s="9"/>
+      <c r="B288" s="9"/>
+      <c r="C288" s="9"/>
       <c r="D288" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E288" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="F288" s="8"/>
+      <c r="F288" s="9"/>
     </row>
     <row r="289" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A289" s="8"/>
-      <c r="B289" s="8"/>
-      <c r="C289" s="8"/>
+      <c r="A289" s="9"/>
+      <c r="B289" s="9"/>
+      <c r="C289" s="9"/>
       <c r="D289" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E289" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="F289" s="8"/>
+      <c r="F289" s="9"/>
     </row>
     <row r="290" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A290" s="8"/>
-      <c r="B290" s="8"/>
-      <c r="C290" s="8"/>
+      <c r="A290" s="9"/>
+      <c r="B290" s="9"/>
+      <c r="C290" s="9"/>
       <c r="D290" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E290" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="F290" s="8"/>
+      <c r="F290" s="9"/>
     </row>
     <row r="291" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A291" s="8"/>
-      <c r="B291" s="8"/>
-      <c r="C291" s="8"/>
+      <c r="A291" s="9"/>
+      <c r="B291" s="9"/>
+      <c r="C291" s="9"/>
       <c r="D291" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E291" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="F291" s="8"/>
+      <c r="F291" s="9"/>
     </row>
     <row r="292" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A292" s="8" t="s">
+      <c r="A292" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="B292" s="8" t="s">
+      <c r="B292" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="C292" s="8" t="s">
+      <c r="C292" s="9" t="s">
         <v>470</v>
       </c>
       <c r="D292" s="2" t="s">
@@ -6304,66 +6304,66 @@
       <c r="E292" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="F292" s="8" t="s">
+      <c r="F292" s="9" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="293" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A293" s="8"/>
-      <c r="B293" s="8"/>
-      <c r="C293" s="8"/>
+      <c r="A293" s="9"/>
+      <c r="B293" s="9"/>
+      <c r="C293" s="9"/>
       <c r="D293" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E293" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="F293" s="8"/>
+      <c r="F293" s="9"/>
     </row>
     <row r="294" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A294" s="8"/>
-      <c r="B294" s="8"/>
-      <c r="C294" s="8"/>
+      <c r="A294" s="9"/>
+      <c r="B294" s="9"/>
+      <c r="C294" s="9"/>
       <c r="D294" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E294" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="F294" s="8"/>
+      <c r="F294" s="9"/>
     </row>
     <row r="295" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A295" s="8"/>
-      <c r="B295" s="8"/>
-      <c r="C295" s="8"/>
+      <c r="A295" s="9"/>
+      <c r="B295" s="9"/>
+      <c r="C295" s="9"/>
       <c r="D295" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E295" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="F295" s="8"/>
+      <c r="F295" s="9"/>
     </row>
     <row r="296" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A296" s="8"/>
-      <c r="B296" s="8"/>
-      <c r="C296" s="8"/>
+      <c r="A296" s="9"/>
+      <c r="B296" s="9"/>
+      <c r="C296" s="9"/>
       <c r="D296" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E296" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="F296" s="8"/>
+      <c r="F296" s="9"/>
     </row>
     <row r="297" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A297" s="8" t="s">
+      <c r="A297" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="B297" s="8" t="s">
+      <c r="B297" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="C297" s="8" t="s">
+      <c r="C297" s="9" t="s">
         <v>478</v>
       </c>
       <c r="D297" s="2" t="s">
@@ -6372,66 +6372,66 @@
       <c r="E297" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="F297" s="8" t="s">
+      <c r="F297" s="9" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="298" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A298" s="8"/>
-      <c r="B298" s="8"/>
-      <c r="C298" s="8"/>
+      <c r="A298" s="9"/>
+      <c r="B298" s="9"/>
+      <c r="C298" s="9"/>
       <c r="D298" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E298" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="F298" s="8"/>
+      <c r="F298" s="9"/>
     </row>
     <row r="299" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A299" s="8"/>
-      <c r="B299" s="8"/>
-      <c r="C299" s="8"/>
+      <c r="A299" s="9"/>
+      <c r="B299" s="9"/>
+      <c r="C299" s="9"/>
       <c r="D299" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E299" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="F299" s="8"/>
+      <c r="F299" s="9"/>
     </row>
     <row r="300" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A300" s="8"/>
-      <c r="B300" s="8"/>
-      <c r="C300" s="8"/>
+      <c r="A300" s="9"/>
+      <c r="B300" s="9"/>
+      <c r="C300" s="9"/>
       <c r="D300" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E300" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="F300" s="8"/>
+      <c r="F300" s="9"/>
     </row>
     <row r="301" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A301" s="8"/>
-      <c r="B301" s="8"/>
-      <c r="C301" s="8"/>
+      <c r="A301" s="9"/>
+      <c r="B301" s="9"/>
+      <c r="C301" s="9"/>
       <c r="D301" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E301" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="F301" s="8"/>
+      <c r="F301" s="9"/>
     </row>
     <row r="302" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A302" s="8" t="s">
+      <c r="A302" s="9" t="s">
         <v>484</v>
       </c>
-      <c r="B302" s="8" t="s">
+      <c r="B302" s="9" t="s">
         <v>485</v>
       </c>
-      <c r="C302" s="8" t="s">
+      <c r="C302" s="9" t="s">
         <v>486</v>
       </c>
       <c r="D302" s="2" t="s">
@@ -6440,66 +6440,66 @@
       <c r="E302" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F302" s="8" t="s">
+      <c r="F302" s="9" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="303" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A303" s="8"/>
-      <c r="B303" s="8"/>
-      <c r="C303" s="8"/>
+      <c r="A303" s="9"/>
+      <c r="B303" s="9"/>
+      <c r="C303" s="9"/>
       <c r="D303" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E303" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="F303" s="8"/>
+      <c r="F303" s="9"/>
     </row>
     <row r="304" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A304" s="8"/>
-      <c r="B304" s="8"/>
-      <c r="C304" s="8"/>
+      <c r="A304" s="9"/>
+      <c r="B304" s="9"/>
+      <c r="C304" s="9"/>
       <c r="D304" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E304" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="F304" s="8"/>
+      <c r="F304" s="9"/>
     </row>
     <row r="305" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A305" s="8"/>
-      <c r="B305" s="8"/>
-      <c r="C305" s="8"/>
+      <c r="A305" s="9"/>
+      <c r="B305" s="9"/>
+      <c r="C305" s="9"/>
       <c r="D305" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E305" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="F305" s="8"/>
+      <c r="F305" s="9"/>
     </row>
     <row r="306" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A306" s="8"/>
-      <c r="B306" s="8"/>
-      <c r="C306" s="8"/>
+      <c r="A306" s="9"/>
+      <c r="B306" s="9"/>
+      <c r="C306" s="9"/>
       <c r="D306" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E306" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="F306" s="8"/>
+      <c r="F306" s="9"/>
     </row>
     <row r="307" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A307" s="8" t="s">
+      <c r="A307" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="B307" s="8" t="s">
+      <c r="B307" s="9" t="s">
         <v>493</v>
       </c>
-      <c r="C307" s="8" t="s">
+      <c r="C307" s="9" t="s">
         <v>494</v>
       </c>
       <c r="D307" s="2" t="s">
@@ -6508,66 +6508,66 @@
       <c r="E307" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="F307" s="8" t="s">
+      <c r="F307" s="9" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="308" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A308" s="8"/>
-      <c r="B308" s="8"/>
-      <c r="C308" s="8"/>
+      <c r="A308" s="9"/>
+      <c r="B308" s="9"/>
+      <c r="C308" s="9"/>
       <c r="D308" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E308" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="F308" s="8"/>
+      <c r="F308" s="9"/>
     </row>
     <row r="309" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A309" s="8"/>
-      <c r="B309" s="8"/>
-      <c r="C309" s="8"/>
+      <c r="A309" s="9"/>
+      <c r="B309" s="9"/>
+      <c r="C309" s="9"/>
       <c r="D309" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E309" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="F309" s="8"/>
+      <c r="F309" s="9"/>
     </row>
     <row r="310" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A310" s="8"/>
-      <c r="B310" s="8"/>
-      <c r="C310" s="8"/>
+      <c r="A310" s="9"/>
+      <c r="B310" s="9"/>
+      <c r="C310" s="9"/>
       <c r="D310" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E310" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="F310" s="8"/>
+      <c r="F310" s="9"/>
     </row>
     <row r="311" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A311" s="8"/>
-      <c r="B311" s="8"/>
-      <c r="C311" s="8"/>
+      <c r="A311" s="9"/>
+      <c r="B311" s="9"/>
+      <c r="C311" s="9"/>
       <c r="D311" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E311" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="F311" s="8"/>
+      <c r="F311" s="9"/>
     </row>
     <row r="312" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A312" s="8" t="s">
+      <c r="A312" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="B312" s="8" t="s">
+      <c r="B312" s="9" t="s">
         <v>501</v>
       </c>
-      <c r="C312" s="8" t="s">
+      <c r="C312" s="9" t="s">
         <v>502</v>
       </c>
       <c r="D312" s="2" t="s">
@@ -6576,66 +6576,66 @@
       <c r="E312" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="F312" s="8" t="s">
+      <c r="F312" s="9" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="313" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A313" s="8"/>
-      <c r="B313" s="8"/>
-      <c r="C313" s="8"/>
+      <c r="A313" s="9"/>
+      <c r="B313" s="9"/>
+      <c r="C313" s="9"/>
       <c r="D313" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E313" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="F313" s="8"/>
+      <c r="F313" s="9"/>
     </row>
     <row r="314" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A314" s="8"/>
-      <c r="B314" s="8"/>
-      <c r="C314" s="8"/>
+      <c r="A314" s="9"/>
+      <c r="B314" s="9"/>
+      <c r="C314" s="9"/>
       <c r="D314" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E314" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="F314" s="8"/>
+      <c r="F314" s="9"/>
     </row>
     <row r="315" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A315" s="8"/>
-      <c r="B315" s="8"/>
-      <c r="C315" s="8"/>
+      <c r="A315" s="9"/>
+      <c r="B315" s="9"/>
+      <c r="C315" s="9"/>
       <c r="D315" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E315" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="F315" s="8"/>
+      <c r="F315" s="9"/>
     </row>
     <row r="316" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A316" s="8"/>
-      <c r="B316" s="8"/>
-      <c r="C316" s="8"/>
+      <c r="A316" s="9"/>
+      <c r="B316" s="9"/>
+      <c r="C316" s="9"/>
       <c r="D316" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E316" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="F316" s="8"/>
+      <c r="F316" s="9"/>
     </row>
     <row r="317" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A317" s="8" t="s">
+      <c r="A317" s="9" t="s">
         <v>508</v>
       </c>
-      <c r="B317" s="8" t="s">
+      <c r="B317" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="C317" s="8" t="s">
+      <c r="C317" s="9" t="s">
         <v>510</v>
       </c>
       <c r="D317" s="2" t="s">
@@ -6644,66 +6644,66 @@
       <c r="E317" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="F317" s="8" t="s">
+      <c r="F317" s="9" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="318" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A318" s="8"/>
-      <c r="B318" s="8"/>
-      <c r="C318" s="8"/>
+      <c r="A318" s="9"/>
+      <c r="B318" s="9"/>
+      <c r="C318" s="9"/>
       <c r="D318" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E318" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="F318" s="8"/>
+      <c r="F318" s="9"/>
     </row>
     <row r="319" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A319" s="8"/>
-      <c r="B319" s="8"/>
-      <c r="C319" s="8"/>
+      <c r="A319" s="9"/>
+      <c r="B319" s="9"/>
+      <c r="C319" s="9"/>
       <c r="D319" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E319" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="F319" s="8"/>
+      <c r="F319" s="9"/>
     </row>
     <row r="320" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A320" s="8"/>
-      <c r="B320" s="8"/>
-      <c r="C320" s="8"/>
+      <c r="A320" s="9"/>
+      <c r="B320" s="9"/>
+      <c r="C320" s="9"/>
       <c r="D320" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E320" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="F320" s="8"/>
+      <c r="F320" s="9"/>
     </row>
     <row r="321" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A321" s="8"/>
-      <c r="B321" s="8"/>
-      <c r="C321" s="8"/>
+      <c r="A321" s="9"/>
+      <c r="B321" s="9"/>
+      <c r="C321" s="9"/>
       <c r="D321" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E321" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="F321" s="8"/>
+      <c r="F321" s="9"/>
     </row>
     <row r="322" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A322" s="8" t="s">
+      <c r="A322" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="B322" s="8" t="s">
+      <c r="B322" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="C322" s="8" t="s">
+      <c r="C322" s="9" t="s">
         <v>518</v>
       </c>
       <c r="D322" s="2" t="s">
@@ -6712,66 +6712,66 @@
       <c r="E322" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="F322" s="8" t="s">
+      <c r="F322" s="9" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="323" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A323" s="8"/>
-      <c r="B323" s="8"/>
-      <c r="C323" s="8"/>
+      <c r="A323" s="9"/>
+      <c r="B323" s="9"/>
+      <c r="C323" s="9"/>
       <c r="D323" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E323" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="F323" s="8"/>
+      <c r="F323" s="9"/>
     </row>
     <row r="324" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A324" s="8"/>
-      <c r="B324" s="8"/>
-      <c r="C324" s="8"/>
+      <c r="A324" s="9"/>
+      <c r="B324" s="9"/>
+      <c r="C324" s="9"/>
       <c r="D324" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E324" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="F324" s="8"/>
+      <c r="F324" s="9"/>
     </row>
     <row r="325" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A325" s="8"/>
-      <c r="B325" s="8"/>
-      <c r="C325" s="8"/>
+      <c r="A325" s="9"/>
+      <c r="B325" s="9"/>
+      <c r="C325" s="9"/>
       <c r="D325" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E325" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="F325" s="8"/>
+      <c r="F325" s="9"/>
     </row>
     <row r="326" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A326" s="8"/>
-      <c r="B326" s="8"/>
-      <c r="C326" s="8"/>
+      <c r="A326" s="9"/>
+      <c r="B326" s="9"/>
+      <c r="C326" s="9"/>
       <c r="D326" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E326" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="F326" s="8"/>
+      <c r="F326" s="9"/>
     </row>
     <row r="327" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A327" s="8" t="s">
+      <c r="A327" s="9" t="s">
         <v>524</v>
       </c>
-      <c r="B327" s="8" t="s">
+      <c r="B327" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C327" s="8" t="s">
+      <c r="C327" s="9" t="s">
         <v>526</v>
       </c>
       <c r="D327" s="2" t="s">
@@ -6780,66 +6780,66 @@
       <c r="E327" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="F327" s="8" t="s">
+      <c r="F327" s="9" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="328" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A328" s="8"/>
-      <c r="B328" s="8"/>
-      <c r="C328" s="8"/>
+      <c r="A328" s="9"/>
+      <c r="B328" s="9"/>
+      <c r="C328" s="9"/>
       <c r="D328" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E328" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="F328" s="8"/>
+      <c r="F328" s="9"/>
     </row>
     <row r="329" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A329" s="8"/>
-      <c r="B329" s="8"/>
-      <c r="C329" s="8"/>
+      <c r="A329" s="9"/>
+      <c r="B329" s="9"/>
+      <c r="C329" s="9"/>
       <c r="D329" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E329" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="F329" s="8"/>
+      <c r="F329" s="9"/>
     </row>
     <row r="330" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A330" s="8"/>
-      <c r="B330" s="8"/>
-      <c r="C330" s="8"/>
+      <c r="A330" s="9"/>
+      <c r="B330" s="9"/>
+      <c r="C330" s="9"/>
       <c r="D330" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E330" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="F330" s="8"/>
+      <c r="F330" s="9"/>
     </row>
     <row r="331" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A331" s="8"/>
-      <c r="B331" s="8"/>
-      <c r="C331" s="8"/>
+      <c r="A331" s="9"/>
+      <c r="B331" s="9"/>
+      <c r="C331" s="9"/>
       <c r="D331" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E331" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="F331" s="8"/>
+      <c r="F331" s="9"/>
     </row>
     <row r="332" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A332" s="11">
+      <c r="A332" s="8">
         <v>19010007</v>
       </c>
-      <c r="B332" s="11" t="s">
+      <c r="B332" s="8" t="s">
         <v>534</v>
       </c>
-      <c r="C332" s="11" t="s">
+      <c r="C332" s="8" t="s">
         <v>535</v>
       </c>
       <c r="D332" s="6" t="s">
@@ -6848,66 +6848,66 @@
       <c r="E332" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="F332" s="11" t="s">
+      <c r="F332" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="333" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A333" s="11"/>
-      <c r="B333" s="11"/>
-      <c r="C333" s="11"/>
+      <c r="A333" s="8"/>
+      <c r="B333" s="8"/>
+      <c r="C333" s="8"/>
       <c r="D333" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E333" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="F333" s="11"/>
+      <c r="F333" s="8"/>
     </row>
     <row r="334" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A334" s="11"/>
-      <c r="B334" s="11"/>
-      <c r="C334" s="11"/>
+      <c r="A334" s="8"/>
+      <c r="B334" s="8"/>
+      <c r="C334" s="8"/>
       <c r="D334" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E334" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="F334" s="11"/>
+      <c r="F334" s="8"/>
     </row>
     <row r="335" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A335" s="11"/>
-      <c r="B335" s="11"/>
-      <c r="C335" s="11"/>
+      <c r="A335" s="8"/>
+      <c r="B335" s="8"/>
+      <c r="C335" s="8"/>
       <c r="D335" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E335" s="7" t="s">
         <v>539</v>
       </c>
-      <c r="F335" s="11"/>
+      <c r="F335" s="8"/>
     </row>
     <row r="336" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A336" s="11"/>
-      <c r="B336" s="11"/>
-      <c r="C336" s="11"/>
+      <c r="A336" s="8"/>
+      <c r="B336" s="8"/>
+      <c r="C336" s="8"/>
       <c r="D336" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E336" s="7" t="s">
         <v>540</v>
       </c>
-      <c r="F336" s="11"/>
+      <c r="F336" s="8"/>
     </row>
     <row r="337" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A337" s="11">
+      <c r="A337" s="8">
         <v>19010104</v>
       </c>
-      <c r="B337" s="11" t="s">
+      <c r="B337" s="8" t="s">
         <v>541</v>
       </c>
-      <c r="C337" s="11" t="s">
+      <c r="C337" s="8" t="s">
         <v>542</v>
       </c>
       <c r="D337" s="6" t="s">
@@ -6916,66 +6916,66 @@
       <c r="E337" s="7" t="s">
         <v>543</v>
       </c>
-      <c r="F337" s="11" t="s">
+      <c r="F337" s="8" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="338" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A338" s="11"/>
-      <c r="B338" s="11"/>
-      <c r="C338" s="11"/>
+      <c r="A338" s="8"/>
+      <c r="B338" s="8"/>
+      <c r="C338" s="8"/>
       <c r="D338" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E338" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="F338" s="11"/>
+      <c r="F338" s="8"/>
     </row>
     <row r="339" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A339" s="11"/>
-      <c r="B339" s="11"/>
-      <c r="C339" s="11"/>
+      <c r="A339" s="8"/>
+      <c r="B339" s="8"/>
+      <c r="C339" s="8"/>
       <c r="D339" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E339" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="F339" s="11"/>
+      <c r="F339" s="8"/>
     </row>
     <row r="340" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A340" s="11"/>
-      <c r="B340" s="11"/>
-      <c r="C340" s="11"/>
+      <c r="A340" s="8"/>
+      <c r="B340" s="8"/>
+      <c r="C340" s="8"/>
       <c r="D340" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E340" s="7" t="s">
         <v>546</v>
       </c>
-      <c r="F340" s="11"/>
+      <c r="F340" s="8"/>
     </row>
     <row r="341" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A341" s="11"/>
-      <c r="B341" s="11"/>
-      <c r="C341" s="11"/>
+      <c r="A341" s="8"/>
+      <c r="B341" s="8"/>
+      <c r="C341" s="8"/>
       <c r="D341" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E341" s="7" t="s">
         <v>547</v>
       </c>
-      <c r="F341" s="11"/>
+      <c r="F341" s="8"/>
     </row>
     <row r="342" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A342" s="11">
+      <c r="A342" s="8">
         <v>19010501</v>
       </c>
-      <c r="B342" s="11" t="s">
+      <c r="B342" s="8" t="s">
         <v>548</v>
       </c>
-      <c r="C342" s="11" t="s">
+      <c r="C342" s="8" t="s">
         <v>549</v>
       </c>
       <c r="D342" s="6" t="s">
@@ -6984,66 +6984,66 @@
       <c r="E342" s="7" t="s">
         <v>550</v>
       </c>
-      <c r="F342" s="11" t="s">
+      <c r="F342" s="8" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="343" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A343" s="11"/>
-      <c r="B343" s="11"/>
-      <c r="C343" s="11"/>
+      <c r="A343" s="8"/>
+      <c r="B343" s="8"/>
+      <c r="C343" s="8"/>
       <c r="D343" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E343" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="F343" s="11"/>
+      <c r="F343" s="8"/>
     </row>
     <row r="344" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A344" s="11"/>
-      <c r="B344" s="11"/>
-      <c r="C344" s="11"/>
+      <c r="A344" s="8"/>
+      <c r="B344" s="8"/>
+      <c r="C344" s="8"/>
       <c r="D344" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E344" s="7" t="s">
         <v>552</v>
       </c>
-      <c r="F344" s="11"/>
+      <c r="F344" s="8"/>
     </row>
     <row r="345" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A345" s="11"/>
-      <c r="B345" s="11"/>
-      <c r="C345" s="11"/>
+      <c r="A345" s="8"/>
+      <c r="B345" s="8"/>
+      <c r="C345" s="8"/>
       <c r="D345" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E345" s="7" t="s">
         <v>553</v>
       </c>
-      <c r="F345" s="11"/>
+      <c r="F345" s="8"/>
     </row>
     <row r="346" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A346" s="11"/>
-      <c r="B346" s="11"/>
-      <c r="C346" s="11"/>
+      <c r="A346" s="8"/>
+      <c r="B346" s="8"/>
+      <c r="C346" s="8"/>
       <c r="D346" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E346" s="7" t="s">
         <v>554</v>
       </c>
-      <c r="F346" s="11"/>
+      <c r="F346" s="8"/>
     </row>
     <row r="347" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A347" s="11">
+      <c r="A347" s="8">
         <v>19010693</v>
       </c>
-      <c r="B347" s="11" t="s">
+      <c r="B347" s="8" t="s">
         <v>555</v>
       </c>
-      <c r="C347" s="11" t="s">
+      <c r="C347" s="8" t="s">
         <v>556</v>
       </c>
       <c r="D347" s="6" t="s">
@@ -7052,66 +7052,66 @@
       <c r="E347" s="7" t="s">
         <v>557</v>
       </c>
-      <c r="F347" s="11" t="s">
+      <c r="F347" s="8" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="348" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A348" s="11"/>
-      <c r="B348" s="11"/>
-      <c r="C348" s="11"/>
+      <c r="A348" s="8"/>
+      <c r="B348" s="8"/>
+      <c r="C348" s="8"/>
       <c r="D348" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E348" s="7" t="s">
         <v>558</v>
       </c>
-      <c r="F348" s="11"/>
+      <c r="F348" s="8"/>
     </row>
     <row r="349" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A349" s="11"/>
-      <c r="B349" s="11"/>
-      <c r="C349" s="11"/>
+      <c r="A349" s="8"/>
+      <c r="B349" s="8"/>
+      <c r="C349" s="8"/>
       <c r="D349" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E349" s="7" t="s">
         <v>559</v>
       </c>
-      <c r="F349" s="11"/>
+      <c r="F349" s="8"/>
     </row>
     <row r="350" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A350" s="11"/>
-      <c r="B350" s="11"/>
-      <c r="C350" s="11"/>
+      <c r="A350" s="8"/>
+      <c r="B350" s="8"/>
+      <c r="C350" s="8"/>
       <c r="D350" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E350" s="7" t="s">
         <v>560</v>
       </c>
-      <c r="F350" s="11"/>
+      <c r="F350" s="8"/>
     </row>
     <row r="351" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A351" s="11"/>
-      <c r="B351" s="11"/>
-      <c r="C351" s="11"/>
+      <c r="A351" s="8"/>
+      <c r="B351" s="8"/>
+      <c r="C351" s="8"/>
       <c r="D351" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E351" s="7" t="s">
         <v>561</v>
       </c>
-      <c r="F351" s="11"/>
+      <c r="F351" s="8"/>
     </row>
     <row r="352" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A352" s="11">
+      <c r="A352" s="8">
         <v>19010792</v>
       </c>
-      <c r="B352" s="11" t="s">
+      <c r="B352" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="C352" s="11" t="s">
+      <c r="C352" s="8" t="s">
         <v>563</v>
       </c>
       <c r="D352" s="6" t="s">
@@ -7120,66 +7120,66 @@
       <c r="E352" s="7" t="s">
         <v>564</v>
       </c>
-      <c r="F352" s="11" t="s">
+      <c r="F352" s="8" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="353" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A353" s="11"/>
-      <c r="B353" s="11"/>
-      <c r="C353" s="11"/>
+      <c r="A353" s="8"/>
+      <c r="B353" s="8"/>
+      <c r="C353" s="8"/>
       <c r="D353" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E353" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="F353" s="11"/>
+      <c r="F353" s="8"/>
     </row>
     <row r="354" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A354" s="11"/>
-      <c r="B354" s="11"/>
-      <c r="C354" s="11"/>
+      <c r="A354" s="8"/>
+      <c r="B354" s="8"/>
+      <c r="C354" s="8"/>
       <c r="D354" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E354" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="F354" s="11"/>
+      <c r="F354" s="8"/>
     </row>
     <row r="355" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A355" s="11"/>
-      <c r="B355" s="11"/>
-      <c r="C355" s="11"/>
+      <c r="A355" s="8"/>
+      <c r="B355" s="8"/>
+      <c r="C355" s="8"/>
       <c r="D355" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E355" s="7" t="s">
         <v>567</v>
       </c>
-      <c r="F355" s="11"/>
+      <c r="F355" s="8"/>
     </row>
     <row r="356" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A356" s="11"/>
-      <c r="B356" s="11"/>
-      <c r="C356" s="11"/>
+      <c r="A356" s="8"/>
+      <c r="B356" s="8"/>
+      <c r="C356" s="8"/>
       <c r="D356" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E356" s="7" t="s">
         <v>568</v>
       </c>
-      <c r="F356" s="11"/>
+      <c r="F356" s="8"/>
     </row>
     <row r="357" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A357" s="11">
+      <c r="A357" s="8">
         <v>19010824</v>
       </c>
-      <c r="B357" s="11" t="s">
+      <c r="B357" s="8" t="s">
         <v>569</v>
       </c>
-      <c r="C357" s="11" t="s">
+      <c r="C357" s="8" t="s">
         <v>570</v>
       </c>
       <c r="D357" s="6" t="s">
@@ -7188,66 +7188,66 @@
       <c r="E357" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="F357" s="11" t="s">
+      <c r="F357" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="358" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A358" s="11"/>
-      <c r="B358" s="11"/>
-      <c r="C358" s="11"/>
+      <c r="A358" s="8"/>
+      <c r="B358" s="8"/>
+      <c r="C358" s="8"/>
       <c r="D358" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E358" s="7" t="s">
         <v>572</v>
       </c>
-      <c r="F358" s="11"/>
+      <c r="F358" s="8"/>
     </row>
     <row r="359" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A359" s="11"/>
-      <c r="B359" s="11"/>
-      <c r="C359" s="11"/>
+      <c r="A359" s="8"/>
+      <c r="B359" s="8"/>
+      <c r="C359" s="8"/>
       <c r="D359" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E359" s="7" t="s">
         <v>573</v>
       </c>
-      <c r="F359" s="11"/>
+      <c r="F359" s="8"/>
     </row>
     <row r="360" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A360" s="11"/>
-      <c r="B360" s="11"/>
-      <c r="C360" s="11"/>
+      <c r="A360" s="8"/>
+      <c r="B360" s="8"/>
+      <c r="C360" s="8"/>
       <c r="D360" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E360" s="7" t="s">
         <v>574</v>
       </c>
-      <c r="F360" s="11"/>
+      <c r="F360" s="8"/>
     </row>
     <row r="361" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A361" s="11"/>
-      <c r="B361" s="11"/>
-      <c r="C361" s="11"/>
+      <c r="A361" s="8"/>
+      <c r="B361" s="8"/>
+      <c r="C361" s="8"/>
       <c r="D361" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E361" s="7" t="s">
         <v>575</v>
       </c>
-      <c r="F361" s="11"/>
+      <c r="F361" s="8"/>
     </row>
     <row r="362" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A362" s="11">
+      <c r="A362" s="8">
         <v>19010918</v>
       </c>
-      <c r="B362" s="11" t="s">
+      <c r="B362" s="8" t="s">
         <v>576</v>
       </c>
-      <c r="C362" s="11" t="s">
+      <c r="C362" s="8" t="s">
         <v>577</v>
       </c>
       <c r="D362" s="6" t="s">
@@ -7256,66 +7256,66 @@
       <c r="E362" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="F362" s="11" t="s">
+      <c r="F362" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="363" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A363" s="11"/>
-      <c r="B363" s="11"/>
-      <c r="C363" s="11"/>
+      <c r="A363" s="8"/>
+      <c r="B363" s="8"/>
+      <c r="C363" s="8"/>
       <c r="D363" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E363" s="7" t="s">
         <v>579</v>
       </c>
-      <c r="F363" s="11"/>
+      <c r="F363" s="8"/>
     </row>
     <row r="364" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A364" s="11"/>
-      <c r="B364" s="11"/>
-      <c r="C364" s="11"/>
+      <c r="A364" s="8"/>
+      <c r="B364" s="8"/>
+      <c r="C364" s="8"/>
       <c r="D364" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E364" s="7" t="s">
         <v>580</v>
       </c>
-      <c r="F364" s="11"/>
+      <c r="F364" s="8"/>
     </row>
     <row r="365" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A365" s="11"/>
-      <c r="B365" s="11"/>
-      <c r="C365" s="11"/>
+      <c r="A365" s="8"/>
+      <c r="B365" s="8"/>
+      <c r="C365" s="8"/>
       <c r="D365" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E365" s="7" t="s">
         <v>581</v>
       </c>
-      <c r="F365" s="11"/>
+      <c r="F365" s="8"/>
     </row>
     <row r="366" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A366" s="11"/>
-      <c r="B366" s="11"/>
-      <c r="C366" s="11"/>
+      <c r="A366" s="8"/>
+      <c r="B366" s="8"/>
+      <c r="C366" s="8"/>
       <c r="D366" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E366" s="7" t="s">
         <v>582</v>
       </c>
-      <c r="F366" s="11"/>
+      <c r="F366" s="8"/>
     </row>
     <row r="367" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A367" s="11">
+      <c r="A367" s="8">
         <v>19010920</v>
       </c>
-      <c r="B367" s="11" t="s">
+      <c r="B367" s="8" t="s">
         <v>583</v>
       </c>
-      <c r="C367" s="11" t="s">
+      <c r="C367" s="8" t="s">
         <v>584</v>
       </c>
       <c r="D367" s="6" t="s">
@@ -7324,60 +7324,336 @@
       <c r="E367" s="7" t="s">
         <v>585</v>
       </c>
-      <c r="F367" s="11" t="s">
+      <c r="F367" s="8" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="368" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A368" s="11"/>
-      <c r="B368" s="11"/>
-      <c r="C368" s="11"/>
+      <c r="A368" s="8"/>
+      <c r="B368" s="8"/>
+      <c r="C368" s="8"/>
       <c r="D368" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E368" s="7" t="s">
         <v>586</v>
       </c>
-      <c r="F368" s="11"/>
+      <c r="F368" s="8"/>
     </row>
     <row r="369" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A369" s="11"/>
-      <c r="B369" s="11"/>
-      <c r="C369" s="11"/>
+      <c r="A369" s="8"/>
+      <c r="B369" s="8"/>
+      <c r="C369" s="8"/>
       <c r="D369" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E369" s="7" t="s">
         <v>587</v>
       </c>
-      <c r="F369" s="11"/>
+      <c r="F369" s="8"/>
     </row>
     <row r="370" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A370" s="11"/>
-      <c r="B370" s="11"/>
-      <c r="C370" s="11"/>
+      <c r="A370" s="8"/>
+      <c r="B370" s="8"/>
+      <c r="C370" s="8"/>
       <c r="D370" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E370" s="7" t="s">
         <v>588</v>
       </c>
-      <c r="F370" s="11"/>
+      <c r="F370" s="8"/>
     </row>
     <row r="371" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A371" s="11"/>
-      <c r="B371" s="11"/>
-      <c r="C371" s="11"/>
+      <c r="A371" s="8"/>
+      <c r="B371" s="8"/>
+      <c r="C371" s="8"/>
       <c r="D371" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E371" s="7" t="s">
         <v>589</v>
       </c>
-      <c r="F371" s="11"/>
+      <c r="F371" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="296">
+    <mergeCell ref="A317:A321"/>
+    <mergeCell ref="B317:B321"/>
+    <mergeCell ref="C317:C321"/>
+    <mergeCell ref="F317:F321"/>
+    <mergeCell ref="A322:A326"/>
+    <mergeCell ref="B322:B326"/>
+    <mergeCell ref="C322:C326"/>
+    <mergeCell ref="F322:F326"/>
+    <mergeCell ref="A327:A331"/>
+    <mergeCell ref="B327:B331"/>
+    <mergeCell ref="C327:C331"/>
+    <mergeCell ref="F327:F331"/>
+    <mergeCell ref="A302:A306"/>
+    <mergeCell ref="B302:B306"/>
+    <mergeCell ref="C302:C306"/>
+    <mergeCell ref="F302:F306"/>
+    <mergeCell ref="A307:A311"/>
+    <mergeCell ref="B307:B311"/>
+    <mergeCell ref="C307:C311"/>
+    <mergeCell ref="F307:F311"/>
+    <mergeCell ref="A312:A316"/>
+    <mergeCell ref="B312:B316"/>
+    <mergeCell ref="C312:C316"/>
+    <mergeCell ref="F312:F316"/>
+    <mergeCell ref="A287:A291"/>
+    <mergeCell ref="B287:B291"/>
+    <mergeCell ref="C287:C291"/>
+    <mergeCell ref="F287:F291"/>
+    <mergeCell ref="A292:A296"/>
+    <mergeCell ref="B292:B296"/>
+    <mergeCell ref="C292:C296"/>
+    <mergeCell ref="F292:F296"/>
+    <mergeCell ref="A297:A301"/>
+    <mergeCell ref="B297:B301"/>
+    <mergeCell ref="C297:C301"/>
+    <mergeCell ref="F297:F301"/>
+    <mergeCell ref="A272:A276"/>
+    <mergeCell ref="B272:B276"/>
+    <mergeCell ref="C272:C276"/>
+    <mergeCell ref="F272:F276"/>
+    <mergeCell ref="A277:A281"/>
+    <mergeCell ref="B277:B281"/>
+    <mergeCell ref="C277:C281"/>
+    <mergeCell ref="F277:F281"/>
+    <mergeCell ref="A282:A286"/>
+    <mergeCell ref="B282:B286"/>
+    <mergeCell ref="C282:C286"/>
+    <mergeCell ref="F282:F286"/>
+    <mergeCell ref="A257:A261"/>
+    <mergeCell ref="B257:B261"/>
+    <mergeCell ref="C257:C261"/>
+    <mergeCell ref="F257:F261"/>
+    <mergeCell ref="A262:A266"/>
+    <mergeCell ref="B262:B266"/>
+    <mergeCell ref="C262:C266"/>
+    <mergeCell ref="F262:F266"/>
+    <mergeCell ref="A267:A271"/>
+    <mergeCell ref="B267:B271"/>
+    <mergeCell ref="C267:C271"/>
+    <mergeCell ref="F267:F271"/>
+    <mergeCell ref="A242:A246"/>
+    <mergeCell ref="B242:B246"/>
+    <mergeCell ref="C242:C246"/>
+    <mergeCell ref="F242:F246"/>
+    <mergeCell ref="A247:A251"/>
+    <mergeCell ref="B247:B251"/>
+    <mergeCell ref="C247:C251"/>
+    <mergeCell ref="F247:F251"/>
+    <mergeCell ref="A252:A256"/>
+    <mergeCell ref="B252:B256"/>
+    <mergeCell ref="C252:C256"/>
+    <mergeCell ref="F252:F256"/>
+    <mergeCell ref="A227:A231"/>
+    <mergeCell ref="B227:B231"/>
+    <mergeCell ref="C227:C231"/>
+    <mergeCell ref="F227:F231"/>
+    <mergeCell ref="A232:A236"/>
+    <mergeCell ref="B232:B236"/>
+    <mergeCell ref="C232:C236"/>
+    <mergeCell ref="F232:F236"/>
+    <mergeCell ref="A237:A241"/>
+    <mergeCell ref="B237:B241"/>
+    <mergeCell ref="C237:C241"/>
+    <mergeCell ref="F237:F241"/>
+    <mergeCell ref="A212:A216"/>
+    <mergeCell ref="B212:B216"/>
+    <mergeCell ref="C212:C216"/>
+    <mergeCell ref="F212:F216"/>
+    <mergeCell ref="A217:A221"/>
+    <mergeCell ref="B217:B221"/>
+    <mergeCell ref="C217:C221"/>
+    <mergeCell ref="F217:F221"/>
+    <mergeCell ref="A222:A226"/>
+    <mergeCell ref="B222:B226"/>
+    <mergeCell ref="C222:C226"/>
+    <mergeCell ref="F222:F226"/>
+    <mergeCell ref="A197:A201"/>
+    <mergeCell ref="B197:B201"/>
+    <mergeCell ref="C197:C201"/>
+    <mergeCell ref="F197:F201"/>
+    <mergeCell ref="A202:A206"/>
+    <mergeCell ref="B202:B206"/>
+    <mergeCell ref="C202:C206"/>
+    <mergeCell ref="F202:F206"/>
+    <mergeCell ref="A207:A211"/>
+    <mergeCell ref="B207:B211"/>
+    <mergeCell ref="C207:C211"/>
+    <mergeCell ref="F207:F211"/>
+    <mergeCell ref="A182:A186"/>
+    <mergeCell ref="B182:B186"/>
+    <mergeCell ref="C182:C186"/>
+    <mergeCell ref="F182:F186"/>
+    <mergeCell ref="A187:A191"/>
+    <mergeCell ref="B187:B191"/>
+    <mergeCell ref="C187:C191"/>
+    <mergeCell ref="F187:F191"/>
+    <mergeCell ref="A192:A196"/>
+    <mergeCell ref="B192:B196"/>
+    <mergeCell ref="C192:C196"/>
+    <mergeCell ref="F192:F196"/>
+    <mergeCell ref="A167:A171"/>
+    <mergeCell ref="B167:B171"/>
+    <mergeCell ref="C167:C171"/>
+    <mergeCell ref="F167:F171"/>
+    <mergeCell ref="A172:A176"/>
+    <mergeCell ref="B172:B176"/>
+    <mergeCell ref="C172:C176"/>
+    <mergeCell ref="F172:F176"/>
+    <mergeCell ref="A177:A181"/>
+    <mergeCell ref="B177:B181"/>
+    <mergeCell ref="C177:C181"/>
+    <mergeCell ref="F177:F181"/>
+    <mergeCell ref="A152:A156"/>
+    <mergeCell ref="B152:B156"/>
+    <mergeCell ref="C152:C156"/>
+    <mergeCell ref="F152:F156"/>
+    <mergeCell ref="A157:A161"/>
+    <mergeCell ref="B157:B161"/>
+    <mergeCell ref="C157:C161"/>
+    <mergeCell ref="F157:F161"/>
+    <mergeCell ref="A162:A166"/>
+    <mergeCell ref="B162:B166"/>
+    <mergeCell ref="C162:C166"/>
+    <mergeCell ref="F162:F166"/>
+    <mergeCell ref="A137:A141"/>
+    <mergeCell ref="B137:B141"/>
+    <mergeCell ref="C137:C141"/>
+    <mergeCell ref="F137:F141"/>
+    <mergeCell ref="A142:A146"/>
+    <mergeCell ref="B142:B146"/>
+    <mergeCell ref="C142:C146"/>
+    <mergeCell ref="F142:F146"/>
+    <mergeCell ref="A147:A151"/>
+    <mergeCell ref="B147:B151"/>
+    <mergeCell ref="C147:C151"/>
+    <mergeCell ref="F147:F151"/>
+    <mergeCell ref="A122:A126"/>
+    <mergeCell ref="B122:B126"/>
+    <mergeCell ref="C122:C126"/>
+    <mergeCell ref="F122:F126"/>
+    <mergeCell ref="A127:A131"/>
+    <mergeCell ref="B127:B131"/>
+    <mergeCell ref="C127:C131"/>
+    <mergeCell ref="F127:F131"/>
+    <mergeCell ref="A132:A136"/>
+    <mergeCell ref="B132:B136"/>
+    <mergeCell ref="C132:C136"/>
+    <mergeCell ref="F132:F136"/>
+    <mergeCell ref="A107:A111"/>
+    <mergeCell ref="B107:B111"/>
+    <mergeCell ref="C107:C111"/>
+    <mergeCell ref="F107:F111"/>
+    <mergeCell ref="A112:A116"/>
+    <mergeCell ref="B112:B116"/>
+    <mergeCell ref="C112:C116"/>
+    <mergeCell ref="F112:F116"/>
+    <mergeCell ref="A117:A121"/>
+    <mergeCell ref="B117:B121"/>
+    <mergeCell ref="C117:C121"/>
+    <mergeCell ref="F117:F121"/>
+    <mergeCell ref="A92:A96"/>
+    <mergeCell ref="B92:B96"/>
+    <mergeCell ref="C92:C96"/>
+    <mergeCell ref="F92:F96"/>
+    <mergeCell ref="A97:A101"/>
+    <mergeCell ref="B97:B101"/>
+    <mergeCell ref="C97:C101"/>
+    <mergeCell ref="F97:F101"/>
+    <mergeCell ref="A102:A106"/>
+    <mergeCell ref="B102:B106"/>
+    <mergeCell ref="C102:C106"/>
+    <mergeCell ref="F102:F106"/>
+    <mergeCell ref="A77:A81"/>
+    <mergeCell ref="B77:B81"/>
+    <mergeCell ref="C77:C81"/>
+    <mergeCell ref="F77:F81"/>
+    <mergeCell ref="A82:A86"/>
+    <mergeCell ref="B82:B86"/>
+    <mergeCell ref="C82:C86"/>
+    <mergeCell ref="F82:F86"/>
+    <mergeCell ref="A87:A91"/>
+    <mergeCell ref="B87:B91"/>
+    <mergeCell ref="C87:C91"/>
+    <mergeCell ref="F87:F91"/>
+    <mergeCell ref="A62:A66"/>
+    <mergeCell ref="B62:B66"/>
+    <mergeCell ref="C62:C66"/>
+    <mergeCell ref="F62:F66"/>
+    <mergeCell ref="A67:A71"/>
+    <mergeCell ref="B67:B71"/>
+    <mergeCell ref="C67:C71"/>
+    <mergeCell ref="F67:F71"/>
+    <mergeCell ref="A72:A76"/>
+    <mergeCell ref="B72:B76"/>
+    <mergeCell ref="C72:C76"/>
+    <mergeCell ref="F72:F76"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="C47:C51"/>
+    <mergeCell ref="F47:F51"/>
+    <mergeCell ref="A52:A56"/>
+    <mergeCell ref="B52:B56"/>
+    <mergeCell ref="C52:C56"/>
+    <mergeCell ref="F52:F56"/>
+    <mergeCell ref="A57:A61"/>
+    <mergeCell ref="B57:B61"/>
+    <mergeCell ref="C57:C61"/>
+    <mergeCell ref="F57:F61"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="C32:C36"/>
+    <mergeCell ref="F32:F36"/>
+    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="B37:B41"/>
+    <mergeCell ref="C37:C41"/>
+    <mergeCell ref="F37:F41"/>
+    <mergeCell ref="A42:A46"/>
+    <mergeCell ref="B42:B46"/>
+    <mergeCell ref="C42:C46"/>
+    <mergeCell ref="F42:F46"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="F17:F21"/>
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="B22:B26"/>
+    <mergeCell ref="C22:C26"/>
+    <mergeCell ref="F22:F26"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="C27:C31"/>
+    <mergeCell ref="F27:F31"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="F2:F6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="F7:F11"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="F12:F16"/>
+    <mergeCell ref="A332:A336"/>
+    <mergeCell ref="B332:B336"/>
+    <mergeCell ref="C332:C336"/>
+    <mergeCell ref="F332:F336"/>
+    <mergeCell ref="A337:A341"/>
+    <mergeCell ref="B337:B341"/>
+    <mergeCell ref="C337:C341"/>
+    <mergeCell ref="F337:F341"/>
+    <mergeCell ref="A342:A346"/>
+    <mergeCell ref="B342:B346"/>
+    <mergeCell ref="C342:C346"/>
+    <mergeCell ref="F342:F346"/>
     <mergeCell ref="A362:A366"/>
     <mergeCell ref="B362:B366"/>
     <mergeCell ref="C362:C366"/>
@@ -7398,282 +7674,6 @@
     <mergeCell ref="B357:B361"/>
     <mergeCell ref="C357:C361"/>
     <mergeCell ref="F357:F361"/>
-    <mergeCell ref="A332:A336"/>
-    <mergeCell ref="B332:B336"/>
-    <mergeCell ref="C332:C336"/>
-    <mergeCell ref="F332:F336"/>
-    <mergeCell ref="A337:A341"/>
-    <mergeCell ref="B337:B341"/>
-    <mergeCell ref="C337:C341"/>
-    <mergeCell ref="F337:F341"/>
-    <mergeCell ref="A342:A346"/>
-    <mergeCell ref="B342:B346"/>
-    <mergeCell ref="C342:C346"/>
-    <mergeCell ref="F342:F346"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="F2:F6"/>
-    <mergeCell ref="A7:A11"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="F7:F11"/>
-    <mergeCell ref="A12:A16"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="F12:F16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="B17:B21"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="F17:F21"/>
-    <mergeCell ref="A22:A26"/>
-    <mergeCell ref="B22:B26"/>
-    <mergeCell ref="C22:C26"/>
-    <mergeCell ref="F22:F26"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="B27:B31"/>
-    <mergeCell ref="C27:C31"/>
-    <mergeCell ref="F27:F31"/>
-    <mergeCell ref="A32:A36"/>
-    <mergeCell ref="B32:B36"/>
-    <mergeCell ref="C32:C36"/>
-    <mergeCell ref="F32:F36"/>
-    <mergeCell ref="A37:A41"/>
-    <mergeCell ref="B37:B41"/>
-    <mergeCell ref="C37:C41"/>
-    <mergeCell ref="F37:F41"/>
-    <mergeCell ref="A42:A46"/>
-    <mergeCell ref="B42:B46"/>
-    <mergeCell ref="C42:C46"/>
-    <mergeCell ref="F42:F46"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="C47:C51"/>
-    <mergeCell ref="F47:F51"/>
-    <mergeCell ref="A52:A56"/>
-    <mergeCell ref="B52:B56"/>
-    <mergeCell ref="C52:C56"/>
-    <mergeCell ref="F52:F56"/>
-    <mergeCell ref="A57:A61"/>
-    <mergeCell ref="B57:B61"/>
-    <mergeCell ref="C57:C61"/>
-    <mergeCell ref="F57:F61"/>
-    <mergeCell ref="A62:A66"/>
-    <mergeCell ref="B62:B66"/>
-    <mergeCell ref="C62:C66"/>
-    <mergeCell ref="F62:F66"/>
-    <mergeCell ref="A67:A71"/>
-    <mergeCell ref="B67:B71"/>
-    <mergeCell ref="C67:C71"/>
-    <mergeCell ref="F67:F71"/>
-    <mergeCell ref="A72:A76"/>
-    <mergeCell ref="B72:B76"/>
-    <mergeCell ref="C72:C76"/>
-    <mergeCell ref="F72:F76"/>
-    <mergeCell ref="A77:A81"/>
-    <mergeCell ref="B77:B81"/>
-    <mergeCell ref="C77:C81"/>
-    <mergeCell ref="F77:F81"/>
-    <mergeCell ref="A82:A86"/>
-    <mergeCell ref="B82:B86"/>
-    <mergeCell ref="C82:C86"/>
-    <mergeCell ref="F82:F86"/>
-    <mergeCell ref="A87:A91"/>
-    <mergeCell ref="B87:B91"/>
-    <mergeCell ref="C87:C91"/>
-    <mergeCell ref="F87:F91"/>
-    <mergeCell ref="A92:A96"/>
-    <mergeCell ref="B92:B96"/>
-    <mergeCell ref="C92:C96"/>
-    <mergeCell ref="F92:F96"/>
-    <mergeCell ref="A97:A101"/>
-    <mergeCell ref="B97:B101"/>
-    <mergeCell ref="C97:C101"/>
-    <mergeCell ref="F97:F101"/>
-    <mergeCell ref="A102:A106"/>
-    <mergeCell ref="B102:B106"/>
-    <mergeCell ref="C102:C106"/>
-    <mergeCell ref="F102:F106"/>
-    <mergeCell ref="A107:A111"/>
-    <mergeCell ref="B107:B111"/>
-    <mergeCell ref="C107:C111"/>
-    <mergeCell ref="F107:F111"/>
-    <mergeCell ref="A112:A116"/>
-    <mergeCell ref="B112:B116"/>
-    <mergeCell ref="C112:C116"/>
-    <mergeCell ref="F112:F116"/>
-    <mergeCell ref="A117:A121"/>
-    <mergeCell ref="B117:B121"/>
-    <mergeCell ref="C117:C121"/>
-    <mergeCell ref="F117:F121"/>
-    <mergeCell ref="A122:A126"/>
-    <mergeCell ref="B122:B126"/>
-    <mergeCell ref="C122:C126"/>
-    <mergeCell ref="F122:F126"/>
-    <mergeCell ref="A127:A131"/>
-    <mergeCell ref="B127:B131"/>
-    <mergeCell ref="C127:C131"/>
-    <mergeCell ref="F127:F131"/>
-    <mergeCell ref="A132:A136"/>
-    <mergeCell ref="B132:B136"/>
-    <mergeCell ref="C132:C136"/>
-    <mergeCell ref="F132:F136"/>
-    <mergeCell ref="A137:A141"/>
-    <mergeCell ref="B137:B141"/>
-    <mergeCell ref="C137:C141"/>
-    <mergeCell ref="F137:F141"/>
-    <mergeCell ref="A142:A146"/>
-    <mergeCell ref="B142:B146"/>
-    <mergeCell ref="C142:C146"/>
-    <mergeCell ref="F142:F146"/>
-    <mergeCell ref="A147:A151"/>
-    <mergeCell ref="B147:B151"/>
-    <mergeCell ref="C147:C151"/>
-    <mergeCell ref="F147:F151"/>
-    <mergeCell ref="A152:A156"/>
-    <mergeCell ref="B152:B156"/>
-    <mergeCell ref="C152:C156"/>
-    <mergeCell ref="F152:F156"/>
-    <mergeCell ref="A157:A161"/>
-    <mergeCell ref="B157:B161"/>
-    <mergeCell ref="C157:C161"/>
-    <mergeCell ref="F157:F161"/>
-    <mergeCell ref="A162:A166"/>
-    <mergeCell ref="B162:B166"/>
-    <mergeCell ref="C162:C166"/>
-    <mergeCell ref="F162:F166"/>
-    <mergeCell ref="A167:A171"/>
-    <mergeCell ref="B167:B171"/>
-    <mergeCell ref="C167:C171"/>
-    <mergeCell ref="F167:F171"/>
-    <mergeCell ref="A172:A176"/>
-    <mergeCell ref="B172:B176"/>
-    <mergeCell ref="C172:C176"/>
-    <mergeCell ref="F172:F176"/>
-    <mergeCell ref="A177:A181"/>
-    <mergeCell ref="B177:B181"/>
-    <mergeCell ref="C177:C181"/>
-    <mergeCell ref="F177:F181"/>
-    <mergeCell ref="A182:A186"/>
-    <mergeCell ref="B182:B186"/>
-    <mergeCell ref="C182:C186"/>
-    <mergeCell ref="F182:F186"/>
-    <mergeCell ref="A187:A191"/>
-    <mergeCell ref="B187:B191"/>
-    <mergeCell ref="C187:C191"/>
-    <mergeCell ref="F187:F191"/>
-    <mergeCell ref="A192:A196"/>
-    <mergeCell ref="B192:B196"/>
-    <mergeCell ref="C192:C196"/>
-    <mergeCell ref="F192:F196"/>
-    <mergeCell ref="A197:A201"/>
-    <mergeCell ref="B197:B201"/>
-    <mergeCell ref="C197:C201"/>
-    <mergeCell ref="F197:F201"/>
-    <mergeCell ref="A202:A206"/>
-    <mergeCell ref="B202:B206"/>
-    <mergeCell ref="C202:C206"/>
-    <mergeCell ref="F202:F206"/>
-    <mergeCell ref="A207:A211"/>
-    <mergeCell ref="B207:B211"/>
-    <mergeCell ref="C207:C211"/>
-    <mergeCell ref="F207:F211"/>
-    <mergeCell ref="A212:A216"/>
-    <mergeCell ref="B212:B216"/>
-    <mergeCell ref="C212:C216"/>
-    <mergeCell ref="F212:F216"/>
-    <mergeCell ref="A217:A221"/>
-    <mergeCell ref="B217:B221"/>
-    <mergeCell ref="C217:C221"/>
-    <mergeCell ref="F217:F221"/>
-    <mergeCell ref="A222:A226"/>
-    <mergeCell ref="B222:B226"/>
-    <mergeCell ref="C222:C226"/>
-    <mergeCell ref="F222:F226"/>
-    <mergeCell ref="A227:A231"/>
-    <mergeCell ref="B227:B231"/>
-    <mergeCell ref="C227:C231"/>
-    <mergeCell ref="F227:F231"/>
-    <mergeCell ref="A232:A236"/>
-    <mergeCell ref="B232:B236"/>
-    <mergeCell ref="C232:C236"/>
-    <mergeCell ref="F232:F236"/>
-    <mergeCell ref="A237:A241"/>
-    <mergeCell ref="B237:B241"/>
-    <mergeCell ref="C237:C241"/>
-    <mergeCell ref="F237:F241"/>
-    <mergeCell ref="A242:A246"/>
-    <mergeCell ref="B242:B246"/>
-    <mergeCell ref="C242:C246"/>
-    <mergeCell ref="F242:F246"/>
-    <mergeCell ref="A247:A251"/>
-    <mergeCell ref="B247:B251"/>
-    <mergeCell ref="C247:C251"/>
-    <mergeCell ref="F247:F251"/>
-    <mergeCell ref="A252:A256"/>
-    <mergeCell ref="B252:B256"/>
-    <mergeCell ref="C252:C256"/>
-    <mergeCell ref="F252:F256"/>
-    <mergeCell ref="A257:A261"/>
-    <mergeCell ref="B257:B261"/>
-    <mergeCell ref="C257:C261"/>
-    <mergeCell ref="F257:F261"/>
-    <mergeCell ref="A262:A266"/>
-    <mergeCell ref="B262:B266"/>
-    <mergeCell ref="C262:C266"/>
-    <mergeCell ref="F262:F266"/>
-    <mergeCell ref="A267:A271"/>
-    <mergeCell ref="B267:B271"/>
-    <mergeCell ref="C267:C271"/>
-    <mergeCell ref="F267:F271"/>
-    <mergeCell ref="A272:A276"/>
-    <mergeCell ref="B272:B276"/>
-    <mergeCell ref="C272:C276"/>
-    <mergeCell ref="F272:F276"/>
-    <mergeCell ref="A277:A281"/>
-    <mergeCell ref="B277:B281"/>
-    <mergeCell ref="C277:C281"/>
-    <mergeCell ref="F277:F281"/>
-    <mergeCell ref="A282:A286"/>
-    <mergeCell ref="B282:B286"/>
-    <mergeCell ref="C282:C286"/>
-    <mergeCell ref="F282:F286"/>
-    <mergeCell ref="A287:A291"/>
-    <mergeCell ref="B287:B291"/>
-    <mergeCell ref="C287:C291"/>
-    <mergeCell ref="F287:F291"/>
-    <mergeCell ref="A292:A296"/>
-    <mergeCell ref="B292:B296"/>
-    <mergeCell ref="C292:C296"/>
-    <mergeCell ref="F292:F296"/>
-    <mergeCell ref="A297:A301"/>
-    <mergeCell ref="B297:B301"/>
-    <mergeCell ref="C297:C301"/>
-    <mergeCell ref="F297:F301"/>
-    <mergeCell ref="A302:A306"/>
-    <mergeCell ref="B302:B306"/>
-    <mergeCell ref="C302:C306"/>
-    <mergeCell ref="F302:F306"/>
-    <mergeCell ref="A307:A311"/>
-    <mergeCell ref="B307:B311"/>
-    <mergeCell ref="C307:C311"/>
-    <mergeCell ref="F307:F311"/>
-    <mergeCell ref="A312:A316"/>
-    <mergeCell ref="B312:B316"/>
-    <mergeCell ref="C312:C316"/>
-    <mergeCell ref="F312:F316"/>
-    <mergeCell ref="A317:A321"/>
-    <mergeCell ref="B317:B321"/>
-    <mergeCell ref="C317:C321"/>
-    <mergeCell ref="F317:F321"/>
-    <mergeCell ref="A322:A326"/>
-    <mergeCell ref="B322:B326"/>
-    <mergeCell ref="C322:C326"/>
-    <mergeCell ref="F322:F326"/>
-    <mergeCell ref="A327:A331"/>
-    <mergeCell ref="B327:B331"/>
-    <mergeCell ref="C327:C331"/>
-    <mergeCell ref="F327:F331"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
